--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7829,45 +7829,44 @@
         </is>
       </c>
     </row>
-    <row r="197"/>
-    <row r="198">
-      <c r="A198" s="1" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="B198" s="1" t="inlineStr">
-        <is>
-          <t>Vertical Jump</t>
-        </is>
-      </c>
-      <c r="C198" s="1" t="inlineStr">
-        <is>
-          <t>Glutes, Quads, Calves</t>
-        </is>
-      </c>
-      <c r="D198" s="1" t="inlineStr">
-        <is>
-          <t>Hamstrings, Midline</t>
-        </is>
-      </c>
-      <c r="E198" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F198" s="1" t="inlineStr"/>
-      <c r="G198" s="1" t="inlineStr">
-        <is>
-          <t>Every rep fast and sharp. Land soft in athletic stance.</t>
-        </is>
-      </c>
-      <c r="H198" s="1" t="inlineStr">
-        <is>
-          <t>Stop if reps get slow.</t>
-        </is>
-      </c>
-    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="B197" s="1" t="inlineStr">
+        <is>
+          <t>2km Time Trial</t>
+        </is>
+      </c>
+      <c r="C197" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D197" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E197" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F197" s="1" t="inlineStr">
+        <is>
+          <t>session format, not an individual movement — no meaningful muscle group. A TEST, not a dose (Sam, D14 2026-07-29): it lives outside the 55 conditioning rows and has no conditioning-sheet entry.</t>
+        </is>
+      </c>
+      <c r="G197" s="1" t="inlineStr">
+        <is>
+          <t>Try to run this at the same pace for the entire 2km</t>
+        </is>
+      </c>
+    </row>
+    <row r="198"/>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
@@ -7876,17 +7875,17 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>Pogo Hops</t>
+          <t>Vertical Jump</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Glutes, Quads, Calves</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>Quads, Midline</t>
+          <t>Hamstrings, Midline</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
@@ -7894,17 +7893,17 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F199" s="1" t="inlineStr">
-        <is>
-          <t>takes over when lower niggle (your spec)</t>
-        </is>
-      </c>
+      <c r="F199" s="1" t="inlineStr"/>
       <c r="G199" s="1" t="inlineStr">
         <is>
-          <t>Stand tall, jump and then bounce off the balls of your feet.</t>
-        </is>
-      </c>
-      <c r="H199" s="1" t="inlineStr"/>
+          <t>Every rep fast and sharp. Land soft in athletic stance.</t>
+        </is>
+      </c>
+      <c r="H199" s="1" t="inlineStr">
+        <is>
+          <t>Stop if reps get slow.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -7914,17 +7913,17 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>Lateral Jump</t>
+          <t>Pogo Hops</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Outer hip</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t>Quads, Calves, Midline</t>
+          <t>Quads, Midline</t>
         </is>
       </c>
       <c r="E200" s="1" t="inlineStr">
@@ -7934,12 +7933,12 @@
       </c>
       <c r="F200" s="1" t="inlineStr">
         <is>
-          <t>your spec: beginner friendly</t>
+          <t>takes over when lower niggle (your spec)</t>
         </is>
       </c>
       <c r="G200" s="1" t="inlineStr">
         <is>
-          <t>Jump off outside leg to the side, turn in air and land in a squat.</t>
+          <t>Stand tall, jump and then bounce off the balls of your feet.</t>
         </is>
       </c>
       <c r="H200" s="1" t="inlineStr"/>
@@ -7952,32 +7951,32 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>Kneeling Jump</t>
+          <t>Lateral Jump</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Quads</t>
+          <t>Glutes, Outer hip</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Midline</t>
+          <t>Quads, Calves, Midline</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F201" s="1" t="inlineStr">
         <is>
-          <t>your spec: consistent+</t>
+          <t>your spec: beginner friendly</t>
         </is>
       </c>
       <c r="G201" s="1" t="inlineStr">
         <is>
-          <t>Start in kneeling position, jump onto feet, land in a squat.</t>
+          <t>Jump off outside leg to the side, turn in air and land in a squat.</t>
         </is>
       </c>
       <c r="H201" s="1" t="inlineStr"/>
@@ -7990,17 +7989,17 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>RFE Split Squat Jump</t>
+          <t>Kneeling Jump</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>Quads, Glutes</t>
+          <t>Glutes, Quads</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Calves, Midline</t>
+          <t>Hamstrings, Midline</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
@@ -8008,21 +8007,17 @@
           <t>2+ years</t>
         </is>
       </c>
-      <c r="F202" s="3" t="inlineStr">
-        <is>
-          <t>FLAG — gate proposed, confirm</t>
+      <c r="F202" s="1" t="inlineStr">
+        <is>
+          <t>your spec: consistent+</t>
         </is>
       </c>
       <c r="G202" s="1" t="inlineStr">
         <is>
-          <t>Back foot on bench, slight lean forward, jump straight up off the front leg.</t>
-        </is>
-      </c>
-      <c r="H202" s="1" t="inlineStr">
-        <is>
-          <t>Land soft and controlled.</t>
-        </is>
-      </c>
+          <t>Start in kneeling position, jump onto feet, land in a squat.</t>
+        </is>
+      </c>
+      <c r="H202" s="1" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -8032,33 +8027,37 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>Explosive Push-up</t>
+          <t>RFE Split Squat Jump</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>Chest, Triceps</t>
+          <t>Quads, Glutes</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Midline</t>
+          <t>Hamstrings, Calves, Midline</t>
         </is>
       </c>
       <c r="E203" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F203" s="1" t="inlineStr"/>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>FLAG — gate proposed, confirm</t>
+        </is>
+      </c>
       <c r="G203" s="1" t="inlineStr">
         <is>
-          <t>Explode up, hands leave the floor. Land soft.</t>
+          <t>Back foot on bench, slight lean forward, jump straight up off the front leg.</t>
         </is>
       </c>
       <c r="H203" s="1" t="inlineStr">
         <is>
-          <t>Stop when reps slow. Sore wrists? Elevate hands on box.</t>
+          <t>Land soft and controlled.</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8069,7 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>Speed Bench</t>
+          <t>Explosive Push-up</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
@@ -8080,27 +8079,23 @@
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Lats</t>
+          <t>Shoulders, Midline</t>
         </is>
       </c>
       <c r="E204" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>FLAG — gate proposed, confirm</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F204" s="1" t="inlineStr"/>
       <c r="G204" s="1" t="inlineStr">
         <is>
-          <t>Light load, explosive intent, pause at chest.</t>
+          <t>Explode up, hands leave the floor. Land soft.</t>
         </is>
       </c>
       <c r="H204" s="1" t="inlineStr">
         <is>
-          <t>Drive hard, fast lockout.</t>
+          <t>Stop when reps slow. Sore wrists? Elevate hands on box.</t>
         </is>
       </c>
     </row>
@@ -8112,35 +8107,77 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
+          <t>Speed Bench</t>
+        </is>
+      </c>
+      <c r="C205" s="1" t="inlineStr">
+        <is>
+          <t>Chest, Triceps</t>
+        </is>
+      </c>
+      <c r="D205" s="1" t="inlineStr">
+        <is>
+          <t>Shoulders, Lats</t>
+        </is>
+      </c>
+      <c r="E205" s="1" t="inlineStr">
+        <is>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>FLAG — gate proposed, confirm</t>
+        </is>
+      </c>
+      <c r="G205" s="1" t="inlineStr">
+        <is>
+          <t>Light load, explosive intent, pause at chest.</t>
+        </is>
+      </c>
+      <c r="H205" s="1" t="inlineStr">
+        <is>
+          <t>Drive hard, fast lockout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B206" s="1" t="inlineStr">
+        <is>
           <t>Speed Trap Bar Deadlift</t>
         </is>
       </c>
-      <c r="C205" s="1" t="inlineStr">
+      <c r="C206" s="1" t="inlineStr">
         <is>
           <t>Glutes, Hamstrings</t>
         </is>
       </c>
-      <c r="D205" s="1" t="inlineStr">
+      <c r="D206" s="1" t="inlineStr">
         <is>
           <t>Quads, Upper back, Grip</t>
         </is>
       </c>
-      <c r="E205" s="1" t="inlineStr">
+      <c r="E206" s="1" t="inlineStr">
         <is>
           <t>2+ years</t>
         </is>
       </c>
-      <c r="F205" s="3" t="inlineStr">
+      <c r="F206" s="3" t="inlineStr">
         <is>
           <t>FLAG — gate proposed, confirm</t>
         </is>
       </c>
-      <c r="G205" s="1" t="inlineStr">
+      <c r="G206" s="1" t="inlineStr">
         <is>
           <t>Wrap band around each side of bar, stand on band, get tight, explode up, control down.</t>
         </is>
       </c>
-      <c r="H205" s="1" t="inlineStr"/>
+      <c r="H206" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H206"/>
+  <dimension ref="A1:H205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3777,7 +3777,6 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" s="1" t="inlineStr">
         <is>
           <t>Use V grip on pulldown machine.</t>
@@ -6226,17 +6225,17 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>Easy cardio (zone 1)</t>
+          <t>Breathing reset</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>Light Skipping</t>
+          <t>90/90 Breathing</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
@@ -6252,12 +6251,12 @@
       <c r="F156" s="1" t="inlineStr"/>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t>Soft ground contacts, stay light.</t>
+          <t>Knees and hips at 90, exhale fully.</t>
         </is>
       </c>
       <c r="H156" s="1" t="inlineStr">
         <is>
-          <t>Easy rhythm, not intensity.</t>
+          <t>Pause at the bottom of each breath.</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6268,7 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>90/90 Breathing</t>
+          <t>Crocodile Breathing</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -6290,12 +6289,12 @@
       <c r="F157" s="1" t="inlineStr"/>
       <c r="G157" s="1" t="inlineStr">
         <is>
-          <t>Knees and hips at 90, exhale fully.</t>
+          <t>Face down, breathe into the belly.</t>
         </is>
       </c>
       <c r="H157" s="1" t="inlineStr">
         <is>
-          <t>Pause at the bottom of each breath.</t>
+          <t>Feel the floor push back on the exhale.</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6306,7 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>Crocodile Breathing</t>
+          <t>Box Breathing</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -6328,12 +6327,12 @@
       <c r="F158" s="1" t="inlineStr"/>
       <c r="G158" s="1" t="inlineStr">
         <is>
-          <t>Face down, breathe into the belly.</t>
+          <t>Four counts in, hold, out, hold.</t>
         </is>
       </c>
       <c r="H158" s="1" t="inlineStr">
         <is>
-          <t>Feel the floor push back on the exhale.</t>
+          <t>Stay relaxed, find the rhythm.</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6344,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>Box Breathing</t>
+          <t>Child's Pose with Breathing</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -6366,24 +6365,24 @@
       <c r="F159" s="1" t="inlineStr"/>
       <c r="G159" s="1" t="inlineStr">
         <is>
-          <t>Four counts in, hold, out, hold.</t>
+          <t>Sink back onto the heels, arms long.</t>
         </is>
       </c>
       <c r="H159" s="1" t="inlineStr">
         <is>
-          <t>Stay relaxed, find the rhythm.</t>
+          <t>Slow breaths into the back.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>Breathing reset</t>
+          <t>Conditioning</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>Child's Pose with Breathing</t>
+          <t>Sprint Intervals</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -6398,18 +6397,22 @@
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F160" s="1" t="inlineStr"/>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F160" s="1" t="inlineStr">
+        <is>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+        </is>
+      </c>
       <c r="G160" s="1" t="inlineStr">
         <is>
-          <t>Sink back onto the heels, arms long.</t>
+          <t>Drive through the ground, arms straight.</t>
         </is>
       </c>
       <c r="H160" s="1" t="inlineStr">
         <is>
-          <t>Slow breaths into the back.</t>
+          <t>Full recovery between efforts.</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6424,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>Sprint Intervals</t>
+          <t>Hill Sprints</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -6446,12 +6449,12 @@
       </c>
       <c r="G161" s="1" t="inlineStr">
         <is>
-          <t>Drive through the ground, arms straight.</t>
+          <t>Drive the knees, lean into the hill.</t>
         </is>
       </c>
       <c r="H161" s="1" t="inlineStr">
         <is>
-          <t>Full recovery between efforts.</t>
+          <t>Walk back for full recovery.</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6466,7 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>Hill Sprints</t>
+          <t>Quality Sprints</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -6488,12 +6491,12 @@
       </c>
       <c r="G162" s="1" t="inlineStr">
         <is>
-          <t>Drive the knees, lean into the hill.</t>
+          <t>Max intent every rep, full recovery between.</t>
         </is>
       </c>
       <c r="H162" s="1" t="inlineStr">
         <is>
-          <t>Walk back for full recovery.</t>
+          <t>If speed drops, the set is done.</t>
         </is>
       </c>
     </row>
@@ -6505,7 +6508,7 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>Quality Sprints</t>
+          <t>MAS Training</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -6530,14 +6533,10 @@
       </c>
       <c r="G163" s="1" t="inlineStr">
         <is>
-          <t>Max intent every rep, full recovery between.</t>
-        </is>
-      </c>
-      <c r="H163" s="1" t="inlineStr">
-        <is>
-          <t>If speed drops, the set is done.</t>
-        </is>
-      </c>
+          <t>PENDING — Stage B</t>
+        </is>
+      </c>
+      <c r="H163" s="1" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
@@ -6547,7 +6546,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>MAS Training</t>
+          <t>Flying Sprints</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -6567,7 +6566,7 @@
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
       <c r="G164" s="1" t="inlineStr">
@@ -6585,7 +6584,7 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>Flying Sprints</t>
+          <t>MAS 15:15 Blocks</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -6623,7 +6622,7 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>MAS 15:15 Blocks</t>
+          <t>Tabata Intervals</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -6638,12 +6637,12 @@
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
       <c r="G166" s="1" t="inlineStr">
@@ -6661,7 +6660,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>Tabata Intervals</t>
+          <t>Inverse Tabata</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -6699,7 +6698,7 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>Inverse Tabata</t>
+          <t>Max Effort Sprint Accumulation</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -6737,7 +6736,7 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>Max Effort Sprint Accumulation</t>
+          <t>Free Sprint Session</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -6752,12 +6751,12 @@
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
       <c r="G169" s="1" t="inlineStr">
@@ -6775,7 +6774,7 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>Free Sprint Session</t>
+          <t>Long Run</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -6790,20 +6789,24 @@
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
       <c r="G170" s="1" t="inlineStr">
         <is>
-          <t>PENDING — Stage B</t>
-        </is>
-      </c>
-      <c r="H170" s="1" t="inlineStr"/>
+          <t>Steady aerobic pace, find your rhythm.</t>
+        </is>
+      </c>
+      <c r="H170" s="1" t="inlineStr">
+        <is>
+          <t>Settle in, breathe steadily.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
@@ -6813,7 +6816,7 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>Long Run</t>
+          <t>6x1km</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -6838,14 +6841,10 @@
       </c>
       <c r="G171" s="1" t="inlineStr">
         <is>
-          <t>Steady aerobic pace, find your rhythm.</t>
-        </is>
-      </c>
-      <c r="H171" s="1" t="inlineStr">
-        <is>
-          <t>Settle in, breathe steadily.</t>
-        </is>
-      </c>
+          <t>PENDING — Stage B</t>
+        </is>
+      </c>
+      <c r="H171" s="1" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
@@ -6855,7 +6854,7 @@
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>6x1km</t>
+          <t>1km Repeat Intervals</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -6893,7 +6892,7 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>1km Repeat Intervals</t>
+          <t>4x4 VO2</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -6931,7 +6930,7 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>4x4 VO2</t>
+          <t>200m/400m Repeat Runs</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -6946,12 +6945,12 @@
       </c>
       <c r="E174" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F174" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ sprint-adjacent speed endurance at high impact — the training-age ladder is a rough fit for a session format.</t>
         </is>
       </c>
       <c r="G174" s="1" t="inlineStr">
@@ -6969,7 +6968,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>200m/400m Repeat Runs</t>
+          <t>Footy Fartlek</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -6984,12 +6983,12 @@
       </c>
       <c r="E175" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F175" s="1" t="inlineStr">
         <is>
-          <t>⚑ sprint-adjacent speed endurance at high impact — the training-age ladder is a rough fit for a session format.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
       <c r="G175" s="1" t="inlineStr">
@@ -7007,7 +7006,7 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>Footy Fartlek</t>
+          <t>Hard Row Intervals</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -7045,7 +7044,7 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>Hard Row Intervals</t>
+          <t>Hard SkiErg Intervals</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -7083,7 +7082,7 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>Hard SkiErg Intervals</t>
+          <t>Hard Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -7121,7 +7120,7 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>Hard Assault Bike Intervals</t>
+          <t>Erg EMOM</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -7146,7 +7145,7 @@
       </c>
       <c r="G179" s="1" t="inlineStr">
         <is>
-          <t>PENDING — Stage B</t>
+          <t>Hit X number of calories every minute, the faster you do them the more rest you get.</t>
         </is>
       </c>
       <c r="H179" s="1" t="inlineStr"/>
@@ -7159,7 +7158,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>Erg EMOM</t>
+          <t>Tempo Run</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -7184,10 +7183,14 @@
       </c>
       <c r="G180" s="1" t="inlineStr">
         <is>
-          <t>Hit X number of calories every minute, the faster you do them the more rest you get.</t>
-        </is>
-      </c>
-      <c r="H180" s="1" t="inlineStr"/>
+          <t>Hold the pace, settle into the rhythm.</t>
+        </is>
+      </c>
+      <c r="H180" s="1" t="inlineStr">
+        <is>
+          <t>Controlled breathing throughout.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
@@ -7197,7 +7200,7 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>Tempo Run</t>
+          <t>Long Nasal Run</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -7222,14 +7225,10 @@
       </c>
       <c r="G181" s="1" t="inlineStr">
         <is>
-          <t>Hold the pace, settle into the rhythm.</t>
-        </is>
-      </c>
-      <c r="H181" s="1" t="inlineStr">
-        <is>
-          <t>Controlled breathing throughout.</t>
-        </is>
-      </c>
+          <t>PENDING — Stage B</t>
+        </is>
+      </c>
+      <c r="H181" s="1" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
@@ -7239,7 +7238,7 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>Long Nasal Run</t>
+          <t>30:30 Tempo Blocks</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -7277,7 +7276,7 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>30:30 Tempo Blocks</t>
+          <t>Tempo Intervals (1min on / 1min easy)</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -7315,7 +7314,7 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>Tempo Intervals (1min on / 1min easy)</t>
+          <t>Cruise Intervals</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -7353,7 +7352,7 @@
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>Cruise Intervals</t>
+          <t>Bike/Row/Ski Tempo Intervals</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -7391,7 +7390,7 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>Bike/Row/Ski Tempo Intervals</t>
+          <t>Air Bike Sprints</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -7416,10 +7415,14 @@
       </c>
       <c r="G186" s="1" t="inlineStr">
         <is>
-          <t>PENDING — Stage B</t>
-        </is>
-      </c>
-      <c r="H186" s="1" t="inlineStr"/>
+          <t>Explosive effort.</t>
+        </is>
+      </c>
+      <c r="H186" s="1" t="inlineStr">
+        <is>
+          <t>Recover fully between sprints.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
@@ -7429,7 +7432,7 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>Air Bike Sprints</t>
+          <t>Row Intervals</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -7454,12 +7457,12 @@
       </c>
       <c r="G187" s="1" t="inlineStr">
         <is>
-          <t>Explosive effort.</t>
+          <t>Full catch, explosive drive.</t>
         </is>
       </c>
       <c r="H187" s="1" t="inlineStr">
         <is>
-          <t>Recover fully between sprints.</t>
+          <t>Maintain power, recover completely.</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7474,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>Row Intervals</t>
+          <t>SkiErg Intervals</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -7496,14 +7499,10 @@
       </c>
       <c r="G188" s="1" t="inlineStr">
         <is>
-          <t>Full catch, explosive drive.</t>
-        </is>
-      </c>
-      <c r="H188" s="1" t="inlineStr">
-        <is>
-          <t>Maintain power, recover completely.</t>
-        </is>
-      </c>
+          <t>PENDING — Stage B</t>
+        </is>
+      </c>
+      <c r="H188" s="1" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
@@ -7513,7 +7512,7 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>SkiErg Intervals</t>
+          <t>Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -7551,7 +7550,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>Assault Bike Intervals</t>
+          <t>Flush Run</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -7576,10 +7575,14 @@
       </c>
       <c r="G190" s="1" t="inlineStr">
         <is>
-          <t>PENDING — Stage B</t>
-        </is>
-      </c>
-      <c r="H190" s="1" t="inlineStr"/>
+          <t>Easy jog, nothing above zone one or two.</t>
+        </is>
+      </c>
+      <c r="H190" s="1" t="inlineStr">
+        <is>
+          <t>Move and loosen up.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
@@ -7589,7 +7592,7 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>Flush Run</t>
+          <t>Easy Bike</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -7614,12 +7617,12 @@
       </c>
       <c r="G191" s="1" t="inlineStr">
         <is>
-          <t>Easy jog, nothing above zone one or two.</t>
+          <t>Conversational pace, legs turning over.</t>
         </is>
       </c>
       <c r="H191" s="1" t="inlineStr">
         <is>
-          <t>Move and loosen up.</t>
+          <t>This is recovery, not training.</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7634,7 @@
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>Easy Bike</t>
+          <t>Easy Row</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -7656,12 +7659,12 @@
       </c>
       <c r="G192" s="1" t="inlineStr">
         <is>
-          <t>Conversational pace, legs turning over.</t>
+          <t>Controlled rhythm, long strokes.</t>
         </is>
       </c>
       <c r="H192" s="1" t="inlineStr">
         <is>
-          <t>This is recovery, not training.</t>
+          <t>This is active recovery, not training.</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7676,7 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>Easy Row</t>
+          <t>Easy Ski</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -7698,12 +7701,12 @@
       </c>
       <c r="G193" s="1" t="inlineStr">
         <is>
-          <t>Controlled rhythm, long strokes.</t>
+          <t>Smooth technique, conversational pace.</t>
         </is>
       </c>
       <c r="H193" s="1" t="inlineStr">
         <is>
-          <t>This is active recovery, not training.</t>
+          <t>Focus on form, not intensity.</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7718,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>Easy Ski</t>
+          <t>Easy Swim</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -7740,14 +7743,10 @@
       </c>
       <c r="G194" s="1" t="inlineStr">
         <is>
-          <t>Smooth technique, conversational pace.</t>
-        </is>
-      </c>
-      <c r="H194" s="1" t="inlineStr">
-        <is>
-          <t>Focus on form, not intensity.</t>
-        </is>
-      </c>
+          <t>PENDING — Stage B</t>
+        </is>
+      </c>
+      <c r="H194" s="1" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -7757,7 +7756,7 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>Easy Swim</t>
+          <t>Light Circuits</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -7782,10 +7781,14 @@
       </c>
       <c r="G195" s="1" t="inlineStr">
         <is>
-          <t>PENDING — Stage B</t>
-        </is>
-      </c>
-      <c r="H195" s="1" t="inlineStr"/>
+          <t>Low intensity rounds, controlled transitions.</t>
+        </is>
+      </c>
+      <c r="H195" s="1" t="inlineStr">
+        <is>
+          <t>This is recovery, not intensity.</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -7795,7 +7798,7 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>Light Circuits</t>
+          <t>2km Time Trial</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
@@ -7815,58 +7818,54 @@
       </c>
       <c r="F196" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>session format, not an individual movement — no meaningful muscle group. A TEST, not a dose (Sam, D14 2026-07-29): it lives outside the 55 conditioning rows and has no conditioning-sheet entry.</t>
         </is>
       </c>
       <c r="G196" s="1" t="inlineStr">
         <is>
-          <t>Low intensity rounds, controlled transitions.</t>
-        </is>
-      </c>
-      <c r="H196" s="1" t="inlineStr">
-        <is>
-          <t>This is recovery, not intensity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="1" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="B197" s="1" t="inlineStr">
-        <is>
-          <t>2km Time Trial</t>
-        </is>
-      </c>
-      <c r="C197" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D197" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E197" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F197" s="1" t="inlineStr">
-        <is>
-          <t>session format, not an individual movement — no meaningful muscle group. A TEST, not a dose (Sam, D14 2026-07-29): it lives outside the 55 conditioning rows and has no conditioning-sheet entry.</t>
-        </is>
-      </c>
-      <c r="G197" s="1" t="inlineStr">
-        <is>
           <t>Try to run this at the same pace for the entire 2km</t>
         </is>
       </c>
     </row>
-    <row r="198"/>
+    <row r="197"/>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B198" s="1" t="inlineStr">
+        <is>
+          <t>Vertical Jump</t>
+        </is>
+      </c>
+      <c r="C198" s="1" t="inlineStr">
+        <is>
+          <t>Glutes, Quads, Calves</t>
+        </is>
+      </c>
+      <c r="D198" s="1" t="inlineStr">
+        <is>
+          <t>Hamstrings, Midline</t>
+        </is>
+      </c>
+      <c r="E198" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F198" s="1" t="inlineStr"/>
+      <c r="G198" s="1" t="inlineStr">
+        <is>
+          <t>Every rep fast and sharp. Land soft in athletic stance.</t>
+        </is>
+      </c>
+      <c r="H198" s="1" t="inlineStr">
+        <is>
+          <t>Stop if reps get slow.</t>
+        </is>
+      </c>
+    </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
@@ -7875,17 +7874,17 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>Vertical Jump</t>
+          <t>Pogo Hops</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Quads, Calves</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Midline</t>
+          <t>Quads, Midline</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
@@ -7893,17 +7892,17 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F199" s="1" t="inlineStr"/>
+      <c r="F199" s="1" t="inlineStr">
+        <is>
+          <t>takes over when lower niggle (your spec)</t>
+        </is>
+      </c>
       <c r="G199" s="1" t="inlineStr">
         <is>
-          <t>Every rep fast and sharp. Land soft in athletic stance.</t>
-        </is>
-      </c>
-      <c r="H199" s="1" t="inlineStr">
-        <is>
-          <t>Stop if reps get slow.</t>
-        </is>
-      </c>
+          <t>Stand tall, jump and then bounce off the balls of your feet.</t>
+        </is>
+      </c>
+      <c r="H199" s="1" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -7913,17 +7912,17 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>Pogo Hops</t>
+          <t>Lateral Jump</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Glutes, Outer hip</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t>Quads, Midline</t>
+          <t>Quads, Calves, Midline</t>
         </is>
       </c>
       <c r="E200" s="1" t="inlineStr">
@@ -7933,12 +7932,12 @@
       </c>
       <c r="F200" s="1" t="inlineStr">
         <is>
-          <t>takes over when lower niggle (your spec)</t>
+          <t>your spec: beginner friendly</t>
         </is>
       </c>
       <c r="G200" s="1" t="inlineStr">
         <is>
-          <t>Stand tall, jump and then bounce off the balls of your feet.</t>
+          <t>Jump off outside leg to the side, turn in air and land in a squat.</t>
         </is>
       </c>
       <c r="H200" s="1" t="inlineStr"/>
@@ -7951,32 +7950,32 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>Lateral Jump</t>
+          <t>Kneeling Jump</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Outer hip</t>
+          <t>Glutes, Quads</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>Quads, Calves, Midline</t>
+          <t>Hamstrings, Midline</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F201" s="1" t="inlineStr">
         <is>
-          <t>your spec: beginner friendly</t>
+          <t>your spec: consistent+</t>
         </is>
       </c>
       <c r="G201" s="1" t="inlineStr">
         <is>
-          <t>Jump off outside leg to the side, turn in air and land in a squat.</t>
+          <t>Start in kneeling position, jump onto feet, land in a squat.</t>
         </is>
       </c>
       <c r="H201" s="1" t="inlineStr"/>
@@ -7989,17 +7988,17 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>Kneeling Jump</t>
+          <t>RFE Split Squat Jump</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Quads</t>
+          <t>Quads, Glutes</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Midline</t>
+          <t>Hamstrings, Calves, Midline</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
@@ -8007,17 +8006,21 @@
           <t>2+ years</t>
         </is>
       </c>
-      <c r="F202" s="1" t="inlineStr">
-        <is>
-          <t>your spec: consistent+</t>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>FLAG — gate proposed, confirm</t>
         </is>
       </c>
       <c r="G202" s="1" t="inlineStr">
         <is>
-          <t>Start in kneeling position, jump onto feet, land in a squat.</t>
-        </is>
-      </c>
-      <c r="H202" s="1" t="inlineStr"/>
+          <t>Back foot on bench, slight lean forward, jump straight up off the front leg.</t>
+        </is>
+      </c>
+      <c r="H202" s="1" t="inlineStr">
+        <is>
+          <t>Land soft and controlled.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -8027,37 +8030,33 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>RFE Split Squat Jump</t>
+          <t>Explosive Push-up</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>Quads, Glutes</t>
+          <t>Chest, Triceps</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Calves, Midline</t>
+          <t>Shoulders, Midline</t>
         </is>
       </c>
       <c r="E203" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>FLAG — gate proposed, confirm</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F203" s="1" t="inlineStr"/>
       <c r="G203" s="1" t="inlineStr">
         <is>
-          <t>Back foot on bench, slight lean forward, jump straight up off the front leg.</t>
+          <t>Explode up, hands leave the floor. Land soft.</t>
         </is>
       </c>
       <c r="H203" s="1" t="inlineStr">
         <is>
-          <t>Land soft and controlled.</t>
+          <t>Stop when reps slow. Sore wrists? Elevate hands on box.</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8068,7 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>Explosive Push-up</t>
+          <t>Speed Bench</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
@@ -8079,23 +8078,27 @@
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Midline</t>
+          <t>Shoulders, Lats</t>
         </is>
       </c>
       <c r="E204" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F204" s="1" t="inlineStr"/>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>FLAG — gate proposed, confirm</t>
+        </is>
+      </c>
       <c r="G204" s="1" t="inlineStr">
         <is>
-          <t>Explode up, hands leave the floor. Land soft.</t>
+          <t>Light load, explosive intent, pause at chest.</t>
         </is>
       </c>
       <c r="H204" s="1" t="inlineStr">
         <is>
-          <t>Stop when reps slow. Sore wrists? Elevate hands on box.</t>
+          <t>Drive hard, fast lockout.</t>
         </is>
       </c>
     </row>
@@ -8107,17 +8110,17 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>Speed Bench</t>
+          <t>Speed Trap Bar Deadlift</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>Chest, Triceps</t>
+          <t>Glutes, Hamstrings</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Lats</t>
+          <t>Quads, Upper back, Grip</t>
         </is>
       </c>
       <c r="E205" s="1" t="inlineStr">
@@ -8132,52 +8135,10 @@
       </c>
       <c r="G205" s="1" t="inlineStr">
         <is>
-          <t>Light load, explosive intent, pause at chest.</t>
-        </is>
-      </c>
-      <c r="H205" s="1" t="inlineStr">
-        <is>
-          <t>Drive hard, fast lockout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="1" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="B206" s="1" t="inlineStr">
-        <is>
-          <t>Speed Trap Bar Deadlift</t>
-        </is>
-      </c>
-      <c r="C206" s="1" t="inlineStr">
-        <is>
-          <t>Glutes, Hamstrings</t>
-        </is>
-      </c>
-      <c r="D206" s="1" t="inlineStr">
-        <is>
-          <t>Quads, Upper back, Grip</t>
-        </is>
-      </c>
-      <c r="E206" s="1" t="inlineStr">
-        <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F206" s="3" t="inlineStr">
-        <is>
-          <t>FLAG — gate proposed, confirm</t>
-        </is>
-      </c>
-      <c r="G206" s="1" t="inlineStr">
-        <is>
           <t>Wrap band around each side of bar, stand on band, get tight, explode up, control down.</t>
         </is>
       </c>
-      <c r="H206" s="1" t="inlineStr"/>
+      <c r="H205" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="R223e84657cf44f7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Rd1b544c9eb764f14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9122,6 +9122,32 @@
         <x:v>Don't round the spine.</x:v>
       </x:c>
     </x:row>
+    <x:row r="217" ht="90" customHeight="1">
+      <x:c r="A217" s="5" t="str">
+        <x:v>Mobility</x:v>
+      </x:c>
+      <x:c r="B217" s="5" t="str">
+        <x:v>Horse Stance Hold</x:v>
+      </x:c>
+      <x:c r="C217" s="5" t="str">
+        <x:v>Groin, Quads, Glutes</x:v>
+      </x:c>
+      <x:c r="D217" s="5" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E217" s="5" t="str">
+        <x:v>everyone</x:v>
+      </x:c>
+      <x:c r="F217" s="5" t="str">
+        <x:v>2 × 60-second total holds. Bodyweight; use a higher or narrower stance as the beginner regression. Progress depth, stance width or duration before optional dumbbell load.</x:v>
+      </x:c>
+      <x:c r="G217" s="5" t="str">
+        <x:v>Take a wide stance and sink straight down between your feet.</x:v>
+      </x:c>
+      <x:c r="H217" s="5" t="str">
+        <x:v>Push knees over toes and keep your torso tall.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="R1fe7015252624050"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Rf85d991d96a94cd3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,7 +433,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
-        <x:v>CHANGE LOG — Sam 2026-07-27: MetCon row DELETED (the conditioning ruling retiring the name wins); Single-Arm Pulldown row ADDED (Lats / Upper back, Midline / everyone); 3 casing typos corrected as authorised edits (Suitcase Carry + Skull Crushers 'Everyone' -&gt; 'everyone', Chin-Up Negative (Slow) secondary 'midline' -&gt; 'Midline'). CHANGE LOG — 2026-07-28 cue reconciliation: renamed from MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx; primaryCue/secondaryCue columns added, making this the single authored source for coaching cues. 175 rows carry Sam-authored cues as shipped; 23 conditioning rows read "PENDING — Stage B" (unruled, NOT blessed — Sam 2026-07-28). Muscle/experience cells are untouched. CHANGE LOG — 2026-09-01 identity merge: Single-Arm Pulldown retired as a current row and retained only as a legacy read alias; cues, equipment, progression and history resolve to Single-Arm Lat Pulldown.</x:v>
+        <x:v>CHANGE LOG — Sam 2026-07-27: MetCon row DELETED (the conditioning ruling retiring the name wins); Single-Arm Pulldown row ADDED (Lats / Upper back, Midline / everyone); 3 casing typos corrected as authorised edits (Suitcase Carry + Skull Crushers 'Everyone' -&gt; 'everyone', Chin-Up Negative (Slow) secondary 'midline' -&gt; 'Midline'). CHANGE LOG — 2026-07-28 cue reconciliation: renamed from MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx; primaryCue/secondaryCue columns added, making this the single authored source for coaching cues. 175 rows carry Sam-authored cues as shipped; 23 conditioning rows read "PENDING — Stage B" (unruled, NOT blessed — Sam 2026-07-28). Muscle/experience cells are untouched. CHANGE LOG — 2026-09-01 identity merge: Single-Arm Pulldown retired as a current row and retained only as a legacy read alias; cues, equipment, progression and history resolve to Single-Arm Lat Pulldown. CHANGE LOG — 2026-09-01: Seated Good Morning (Barbell) retired as a current row and retained only as legacy saved-data ingress. Seated Good Morning is the one identity; bodyweight is available to everyone, while dumbbell and barbell variants require 1+ years.</x:v>
       </x:c>
       <x:c r="B5"/>
       <x:c r="C5"/>
@@ -5328,7 +5328,7 @@
         <x:v>everyone</x:v>
       </x:c>
       <x:c r="F208" s="5" t="str">
-        <x:v>Lower for 5 seconds. Bodyweight mobility; never a main lift.</x:v>
+        <x:v>Lower for 5 seconds. Bodyweight for everyone; dumbbell and barbell variants require 1+ years. Log total external load. Mobility only; never a main lift.</x:v>
       </x:c>
       <x:c r="G208" s="5" t="str">
         <x:v>Sit wide, brace, and hinge forward from the hips.</x:v>
@@ -5496,52 +5496,36 @@
         <x:v>Mobility</x:v>
       </x:c>
       <x:c r="B215" s="5" t="str">
-        <x:v>Seated Good Morning (Barbell)</x:v>
+        <x:v>Horse Stance Hold</x:v>
       </x:c>
       <x:c r="C215" s="5" t="str">
-        <x:v>Low back, Groin</x:v>
+        <x:v>Groin, Quads, Glutes</x:v>
       </x:c>
       <x:c r="D215" s="5" t="str">
-        <x:v>Hamstrings, Glutes, Midline, Upper back</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="E215" s="5" t="str">
-        <x:v>1+ years</x:v>
+        <x:v>everyone</x:v>
       </x:c>
       <x:c r="F215" s="5" t="str">
-        <x:v>Lower for 5 seconds. Start with an empty bar; log total external load. Mobility only; excluded the day before a game.</x:v>
+        <x:v>2 × 60-second total holds. Bodyweight; use a higher or narrower stance as the beginner regression. Progress depth, stance width or duration before optional dumbbell load.</x:v>
       </x:c>
       <x:c r="G215" s="5" t="str">
-        <x:v>Sit wide, brace, and hinge forward from the hips.</x:v>
+        <x:v>Take a wide stance and sink straight down between your feet.</x:v>
       </x:c>
       <x:c r="H215" s="5" t="str">
-        <x:v>Don't round the spine.</x:v>
+        <x:v>Push knees over toes and keep your torso tall.</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="70" customHeight="1">
-      <x:c r="A216" s="5" t="str">
-        <x:v>Mobility</x:v>
-      </x:c>
-      <x:c r="B216" s="5" t="str">
-        <x:v>Horse Stance Hold</x:v>
-      </x:c>
-      <x:c r="C216" s="5" t="str">
-        <x:v>Groin, Quads, Glutes</x:v>
-      </x:c>
-      <x:c r="D216" s="5" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="E216" s="5" t="str">
-        <x:v>everyone</x:v>
-      </x:c>
-      <x:c r="F216" s="5" t="str">
-        <x:v>2 × 60-second total holds. Bodyweight; use a higher or narrower stance as the beginner regression. Progress depth, stance width or duration before optional dumbbell load.</x:v>
-      </x:c>
-      <x:c r="G216" s="5" t="str">
-        <x:v>Take a wide stance and sink straight down between your feet.</x:v>
-      </x:c>
-      <x:c r="H216" s="5" t="str">
-        <x:v>Push knees over toes and keep your torso tall.</x:v>
-      </x:c>
+      <x:c r="A216" s="5"/>
+      <x:c r="B216" s="5"/>
+      <x:c r="C216" s="5"/>
+      <x:c r="D216" s="5"/>
+      <x:c r="E216" s="5"/>
+      <x:c r="F216" s="5"/>
+      <x:c r="G216" s="5"/>
+      <x:c r="H216" s="5"/>
     </x:row>
     <x:row r="217" ht="90" customHeight="1">
       <x:c r="A217" s="5"/>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Rf85d991d96a94cd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Rd4cc36d77d894aea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,7 +433,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
-        <x:v>CHANGE LOG — Sam 2026-07-27: MetCon row DELETED (the conditioning ruling retiring the name wins); Single-Arm Pulldown row ADDED (Lats / Upper back, Midline / everyone); 3 casing typos corrected as authorised edits (Suitcase Carry + Skull Crushers 'Everyone' -&gt; 'everyone', Chin-Up Negative (Slow) secondary 'midline' -&gt; 'Midline'). CHANGE LOG — 2026-07-28 cue reconciliation: renamed from MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx; primaryCue/secondaryCue columns added, making this the single authored source for coaching cues. 175 rows carry Sam-authored cues as shipped; 23 conditioning rows read "PENDING — Stage B" (unruled, NOT blessed — Sam 2026-07-28). Muscle/experience cells are untouched. CHANGE LOG — 2026-09-01 identity merge: Single-Arm Pulldown retired as a current row and retained only as a legacy read alias; cues, equipment, progression and history resolve to Single-Arm Lat Pulldown. CHANGE LOG — 2026-09-01: Seated Good Morning (Barbell) retired as a current row and retained only as legacy saved-data ingress. Seated Good Morning is the one identity; bodyweight is available to everyone, while dumbbell and barbell variants require 1+ years.</x:v>
+        <x:v>CHANGE LOG — Sam 2026-07-27: MetCon row DELETED (the conditioning ruling retiring the name wins); Single-Arm Pulldown row ADDED (Lats / Upper back, Midline / everyone); 3 casing typos corrected as authorised edits (Suitcase Carry + Skull Crushers 'Everyone' -&gt; 'everyone', Chin-Up Negative (Slow) secondary 'midline' -&gt; 'Midline'). CHANGE LOG — 2026-07-28 cue reconciliation: renamed from MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx; primaryCue/secondaryCue columns added, making this the single authored source for coaching cues. 175 rows carry Sam-authored cues as shipped; 23 conditioning rows read "PENDING — Stage B" (unruled, NOT blessed — Sam 2026-07-28). Muscle/experience cells are untouched. CHANGE LOG — 2026-09-01 identity merge: Single-Arm Pulldown retired as a current row and retained only as a legacy read alias; cues, equipment, progression and history resolve to Single-Arm Lat Pulldown. CHANGE LOG — 2026-09-01: Seated Good Morning (Barbell) retired as a current row and retained only as legacy saved-data ingress. Seated Good Morning is the one identity; bodyweight is available to everyone, while dumbbell and barbell variants require 1+ years.; Sam 2026-09-02: SL 45° Back Extension Hold and Swiss Ball Hamstring Curl moved from Hamstring (light) into Lower prehab; the separate authored pool was retired.</x:v>
       </x:c>
       <x:c r="B5"/>
       <x:c r="C5"/>
@@ -3311,7 +3311,7 @@
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="1" t="str">
-        <x:v>Hamstring (light)</x:v>
+        <x:v>Lower prehab</x:v>
       </x:c>
       <x:c r="B125" s="1" t="str">
         <x:v>Swiss Ball Hamstring Curl</x:v>
@@ -5365,7 +5365,7 @@
     </x:row>
     <x:row r="210" ht="70" customHeight="1">
       <x:c r="A210" s="5" t="str">
-        <x:v>Hamstring (light)</x:v>
+        <x:v>Lower prehab</x:v>
       </x:c>
       <x:c r="B210" s="5" t="str">
         <x:v>SL 45° Back Extension Hold</x:v>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Rd4cc36d77d894aea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="R4733d448f61a412d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5518,14 +5518,30 @@
       </x:c>
     </x:row>
     <x:row r="216" ht="70" customHeight="1">
-      <x:c r="A216" s="5"/>
-      <x:c r="B216" s="5"/>
-      <x:c r="C216" s="5"/>
-      <x:c r="D216" s="5"/>
-      <x:c r="E216" s="5"/>
-      <x:c r="F216" s="5"/>
-      <x:c r="G216" s="5"/>
-      <x:c r="H216" s="5"/>
+      <x:c r="A216" s="5" t="str">
+        <x:v>Mobility</x:v>
+      </x:c>
+      <x:c r="B216" s="5" t="str">
+        <x:v>Bench Thoracic Extension</x:v>
+      </x:c>
+      <x:c r="C216" s="5" t="str">
+        <x:v>Lats, Upper back</x:v>
+      </x:c>
+      <x:c r="D216" s="5" t="str">
+        <x:v>Triceps, Chest, Midline</x:v>
+      </x:c>
+      <x:c r="E216" s="5" t="str">
+        <x:v>everyone</x:v>
+      </x:c>
+      <x:c r="F216" s="5" t="str">
+        <x:v>Slow reps. Pause 3 seconds at the bottom. Bodyweight only; use a comfortable range near games.</x:v>
+      </x:c>
+      <x:c r="G216" s="5" t="str">
+        <x:v>Place elbows on the bench and sit your hips back.</x:v>
+      </x:c>
+      <x:c r="H216" s="5" t="str">
+        <x:v>Sink your chest without arching through the lower back.</x:v>
+      </x:c>
     </x:row>
     <x:row r="217" ht="90" customHeight="1">
       <x:c r="A217" s="5"/>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="R4733d448f61a412d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Rf8f1d2c807e34470"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5152,7 +5152,7 @@
         <x:v>2+ years</x:v>
       </x:c>
       <x:c r="F201" s="1" t="str">
-        <x:v>FLAG — gate proposed, confirm</x:v>
+        <x:v>Auto lower power. Bench; 2+ years. Not in-season or near games.</x:v>
       </x:c>
       <x:c r="G201" s="1" t="str">
         <x:v>Back foot on bench, slight lean forward, jump straight up off the front leg.</x:v>
@@ -5544,14 +5544,30 @@
       </x:c>
     </x:row>
     <x:row r="217" ht="90" customHeight="1">
-      <x:c r="A217" s="5"/>
-      <x:c r="B217" s="5"/>
-      <x:c r="C217" s="5"/>
-      <x:c r="D217" s="5"/>
-      <x:c r="E217" s="5"/>
-      <x:c r="F217" s="5"/>
-      <x:c r="G217" s="5"/>
-      <x:c r="H217" s="5"/>
+      <x:c r="A217" s="5" t="str">
+        <x:v>Mobility</x:v>
+      </x:c>
+      <x:c r="B217" s="5" t="str">
+        <x:v>Sleeper Stretch</x:v>
+      </x:c>
+      <x:c r="C217" s="5" t="str">
+        <x:v>Shoulders</x:v>
+      </x:c>
+      <x:c r="D217" s="5" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E217" s="5" t="str">
+        <x:v>everyone</x:v>
+      </x:c>
+      <x:c r="F217" s="5" t="str">
+        <x:v>Gentle pressure from the opposite hand; no external loading or bouncing. Use short, comfortable holds near games and avoid aggressive holds before throwing, pressing or contact.</x:v>
+      </x:c>
+      <x:c r="G217" s="5" t="str">
+        <x:v>Lie on the target shoulder and gently lower the forearm.</x:v>
+      </x:c>
+      <x:c r="H217" s="5" t="str">
+        <x:v>Stop at a mild stretch behind the shoulder, never the front.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Rf8f1d2c807e34470"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Rd47f9b569f604df7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5569,6 +5569,32 @@
         <x:v>Stop at a mild stretch behind the shoulder, never the front.</x:v>
       </x:c>
     </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="5" t="str">
+        <x:v>Mobility</x:v>
+      </x:c>
+      <x:c r="B218" s="5" t="str">
+        <x:v>Foam Roller Thoracic Extension</x:v>
+      </x:c>
+      <x:c r="C218" s="5" t="str">
+        <x:v>Lats, Upper back</x:v>
+      </x:c>
+      <x:c r="D218" s="5" t="str">
+        <x:v>Chest, Triceps, Shoulders, Midline</x:v>
+      </x:c>
+      <x:c r="E218" s="5" t="str">
+        <x:v>everyone</x:v>
+      </x:c>
+      <x:c r="F218" s="5" t="str">
+        <x:v>Pause 5 seconds overhead. Foam roller required. Hold one light dumbbell or weight plate in both hands; record total load. Beginners may use no weight. Mobility only; the weight assists the stretch.</x:v>
+      </x:c>
+      <x:c r="G218" s="5" t="str">
+        <x:v>Reach the weight overhead as your upper back extends.</x:v>
+      </x:c>
+      <x:c r="H218" s="5" t="str">
+        <x:v>Keep ribs tucked and avoid arching through the lower back.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Rd47f9b569f604df7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="R2165b7fe4e7e4596"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5595,6 +5595,32 @@
         <x:v>Keep ribs tucked and avoid arching through the lower back.</x:v>
       </x:c>
     </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="5" t="str">
+        <x:v>Upper pull vertical</x:v>
+      </x:c>
+      <x:c r="B219" s="5" t="str">
+        <x:v>Band-Assisted Pull-Up</x:v>
+      </x:c>
+      <x:c r="C219" s="5" t="str">
+        <x:v>Lats, Biceps, Upper back</x:v>
+      </x:c>
+      <x:c r="D219" s="5" t="str">
+        <x:v>Shoulders, Grip, Midline</x:v>
+      </x:c>
+      <x:c r="E219" s="5" t="str">
+        <x:v>everyone (regression)</x:v>
+      </x:c>
+      <x:c r="F219" s="5" t="str">
+        <x:v>Automatic regression and manual Swap from Pull-Ups only. Eligible for all complete beginners and female athletes at 1–2 years. Requires a resistance band plus a rack or pull-up bar. Record band strength or colour and support height; reduce assistance to progress. Inherits Pull-Up sets, reps and role. All phases; suitable near games.</x:v>
+      </x:c>
+      <x:c r="G219" s="5" t="str">
+        <x:v>Stand firmly on the band and pull your chest toward the bar.</x:v>
+      </x:c>
+      <x:c r="H219" s="5" t="str">
+        <x:v>Lower under control until your elbows fully straighten.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="R2165b7fe4e7e4596"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="R96c1c2d09ec24480"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5621,6 +5621,58 @@
         <x:v>Lower under control until your elbows fully straighten.</x:v>
       </x:c>
     </x:row>
+    <x:row r="220" ht="72" customHeight="1">
+      <x:c r="A220" s="5" t="str">
+        <x:v>Upper push horizontal</x:v>
+      </x:c>
+      <x:c r="B220" s="5" t="str">
+        <x:v>Incline Push-Up</x:v>
+      </x:c>
+      <x:c r="C220" s="5" t="str">
+        <x:v>Chest, Triceps, Shoulders</x:v>
+      </x:c>
+      <x:c r="D220" s="5" t="str">
+        <x:v>Midline, Glutes</x:v>
+      </x:c>
+      <x:c r="E220" s="5" t="str">
+        <x:v>everyone (regression)</x:v>
+      </x:c>
+      <x:c r="F220" s="5" t="str">
+        <x:v>Automatic regression and manual Swap from Push-ups only. Eligible for all complete beginners and female athletes at 1–2 years. Requires a bench or plyo box. Bodyweight only; record support height in the session note and lower it to progress. Inherits Push-ups sets, reps and role. All phases; suitable near games.</x:v>
+      </x:c>
+      <x:c r="G220" s="5" t="str">
+        <x:v>Keep a straight body line and lower your chest to the support.</x:v>
+      </x:c>
+      <x:c r="H220" s="5" t="str">
+        <x:v>Press away without letting your hips sag or shoulders shrug.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="72" customHeight="1">
+      <x:c r="A221" s="5" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="B221" s="5" t="str">
+        <x:v>Single-Leg Hop and Stick</x:v>
+      </x:c>
+      <x:c r="C221" s="5" t="str">
+        <x:v>Glutes, Quads, Calves</x:v>
+      </x:c>
+      <x:c r="D221" s="5" t="str">
+        <x:v>Hamstrings, Groin, Midline, Feet</x:v>
+      </x:c>
+      <x:c r="E221" s="5" t="str">
+        <x:v>2+ years</x:v>
+      </x:c>
+      <x:c r="F221" s="5" t="str">
+        <x:v>Automatic lower power and manual Add/Swap for 2+ years only. Bodyweight; 2 × 5 per side with 120 seconds rest. All phases and in-season at low volume; never automatic at G-1. Progress hop distance only while the landing stays controlled.</x:v>
+      </x:c>
+      <x:c r="G221" s="5" t="str">
+        <x:v>Hop forward from one leg and freeze the landing.</x:v>
+      </x:c>
+      <x:c r="H221" s="5" t="str">
+        <x:v>Land quietly, absorb through the hip, and hold your balance.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="R96c1c2d09ec24480"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Raa44463d67934fa0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -381,9 +381,11 @@
     <x:col min="6" max="6" width="50" customWidth="1"/>
     <x:col min="7" max="7" width="60" customWidth="1"/>
     <x:col min="8" max="8" width="60" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="4" t="str">
         <x:v>AUTHORED FINAL — Sam sign-off 2026-07-25. Source of truth for the D11 muscle-block build. Changes require Sam.</x:v>
       </x:c>
@@ -394,8 +396,14 @@
       <x:c r="F1"/>
       <x:c r="G1"/>
       <x:c r="H1"/>
-    </x:row>
-    <x:row r="2">
+      <x:c r="I1" s="5" t="str">
+        <x:v>MOVEMENT PLANES — 2026-09-02</x:v>
+      </x:c>
+      <x:c r="J1" s="5" t="str">
+        <x:v>Blank = unanswered</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="1" t="str">
         <x:v>EXPERIENCE VALUES: everyone · everyone (regression) · 1+ years · 2+ years · advanced only</x:v>
       </x:c>
@@ -406,6 +414,12 @@
       <x:c r="F2" s="1"/>
       <x:c r="G2"/>
       <x:c r="H2"/>
+      <x:c r="I2" s="5" t="str">
+        <x:v>sagittal · frontal · transverse</x:v>
+      </x:c>
+      <x:c r="J2" s="5" t="str">
+        <x:v>multiplanar · not_applicable</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1" t="str">
@@ -418,6 +432,8 @@
       <x:c r="F3" s="1"/>
       <x:c r="G3"/>
       <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1" t="str">
@@ -430,6 +446,8 @@
       <x:c r="F4" s="1"/>
       <x:c r="G4"/>
       <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
@@ -442,6 +460,8 @@
       <x:c r="F5"/>
       <x:c r="G5"/>
       <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="2" t="str">
@@ -468,6 +488,12 @@
       <x:c r="H6" s="2" t="str">
         <x:v>secondaryCue</x:v>
       </x:c>
+      <x:c r="I6" s="5" t="str">
+        <x:v>Primary Plane</x:v>
+      </x:c>
+      <x:c r="J6" s="5" t="str">
+        <x:v>Secondary Plane(s)</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="1" t="str">
@@ -492,6 +518,10 @@
       <x:c r="H7" s="1" t="str">
         <x:v>Own the bottom position.</x:v>
       </x:c>
+      <x:c r="I7" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J7" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="1" t="str">
@@ -518,6 +548,10 @@
       <x:c r="H8" s="1" t="str">
         <x:v>Stay tall through the midline.</x:v>
       </x:c>
+      <x:c r="I8" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J8" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="1" t="str">
@@ -542,6 +576,10 @@
       <x:c r="H9" s="1" t="str">
         <x:v>Explode off the box.</x:v>
       </x:c>
+      <x:c r="I9" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J9" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="1" t="str">
@@ -564,6 +602,10 @@
         <x:v>High box to minimise soreness, slight pause at box, stay tight through midline.</x:v>
       </x:c>
       <x:c r="H10" s="1" t="str"/>
+      <x:c r="I10" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J10" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="1" t="str">
@@ -588,6 +630,12 @@
       <x:c r="H11" s="1" t="str">
         <x:v>Steady and deliberate.</x:v>
       </x:c>
+      <x:c r="I11" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="1" t="str">
@@ -612,6 +660,12 @@
       <x:c r="H12" s="1" t="str">
         <x:v>Control the descent, no bouncing.</x:v>
       </x:c>
+      <x:c r="I12" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="1" t="str">
@@ -636,6 +690,12 @@
       <x:c r="H13" s="1" t="str">
         <x:v>Front knee tracks over the toe.</x:v>
       </x:c>
+      <x:c r="I13" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="1" t="str">
@@ -660,6 +720,12 @@
       <x:c r="H14" s="1" t="str">
         <x:v>Don’t bounce with leg on ground.</x:v>
       </x:c>
+      <x:c r="I14" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J14" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="1" t="str">
@@ -684,6 +750,10 @@
       <x:c r="H15" s="1" t="str">
         <x:v>Smooth tempo, no rushing.</x:v>
       </x:c>
+      <x:c r="I15" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J15" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="1" t="str">
@@ -708,6 +778,10 @@
       <x:c r="H16" s="1" t="str">
         <x:v>Push through the whole foot.</x:v>
       </x:c>
+      <x:c r="I16" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J16" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="1" t="str">
@@ -732,6 +806,10 @@
       <x:c r="H17" s="1" t="str">
         <x:v>Control on the way down.</x:v>
       </x:c>
+      <x:c r="I17" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J17" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="1" t="str">
@@ -756,6 +834,12 @@
       <x:c r="H18" s="1" t="str">
         <x:v>Keep the knee tracking straight.</x:v>
       </x:c>
+      <x:c r="I18" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J18" t="str">
+        <x:v>frontal, transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="1" t="str">
@@ -776,6 +860,10 @@
         <x:v>Sit back into hips, knees follow toes, chest tall.</x:v>
       </x:c>
       <x:c r="H19" s="1" t="str"/>
+      <x:c r="I19" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J19" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="1" t="str">
@@ -802,6 +890,10 @@
       <x:c r="H20" s="1" t="str">
         <x:v>Flat back from start to lockout.</x:v>
       </x:c>
+      <x:c r="I20" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J20" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="1" t="str">
@@ -826,6 +918,10 @@
       <x:c r="H21" s="1" t="str">
         <x:v>Hips and shoulders rise together.</x:v>
       </x:c>
+      <x:c r="I21" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J21" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="1" t="str">
@@ -852,6 +948,10 @@
       <x:c r="H22" s="1" t="str">
         <x:v>Feel the hamstrings load on the way down.</x:v>
       </x:c>
+      <x:c r="I22" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J22" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="1" t="str">
@@ -876,6 +976,12 @@
       <x:c r="H23" s="1" t="str">
         <x:v>Balance and control over speed.</x:v>
       </x:c>
+      <x:c r="I23" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J23" t="str">
+        <x:v>frontal, transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="1" t="str">
@@ -900,6 +1006,10 @@
       <x:c r="H24" s="1" t="str">
         <x:v>Ribs down, no overextending.</x:v>
       </x:c>
+      <x:c r="I24" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J24" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="1" t="str">
@@ -924,6 +1034,10 @@
       <x:c r="H25" s="1" t="str">
         <x:v>Power from hips, don’t lift with arms.</x:v>
       </x:c>
+      <x:c r="I25" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J25" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="1" t="str">
@@ -946,6 +1060,10 @@
         <x:v>Keep spine neutral, don’t arch low back, lift hips, squeeze glutes, add weight to hips if you can.</x:v>
       </x:c>
       <x:c r="H26" s="1" t="str"/>
+      <x:c r="I26" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J26" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="1" t="str">
@@ -970,6 +1088,10 @@
       <x:c r="H27" s="1" t="str">
         <x:v>Bar to chest, press hard to lockout.</x:v>
       </x:c>
+      <x:c r="I27" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J27" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="1" t="str">
@@ -994,6 +1116,12 @@
       <x:c r="H28" s="1" t="str">
         <x:v>Press through the palms.</x:v>
       </x:c>
+      <x:c r="I28" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J28" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="1" t="str">
@@ -1018,6 +1146,12 @@
       <x:c r="H29" s="1" t="str">
         <x:v>Triceps do the work.</x:v>
       </x:c>
+      <x:c r="I29" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J29" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="1" t="str">
@@ -1042,6 +1176,10 @@
       <x:c r="H30" s="1" t="str">
         <x:v>Control the dumbbells down and drive.</x:v>
       </x:c>
+      <x:c r="I30" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J30" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="1" t="str">
@@ -1066,6 +1204,12 @@
       <x:c r="H31" s="1" t="str">
         <x:v>Drive up and together.</x:v>
       </x:c>
+      <x:c r="I31" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J31" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="1" t="str">
@@ -1090,6 +1234,12 @@
       <x:c r="H32" s="1" t="str">
         <x:v>Chest to floor, full lockout.</x:v>
       </x:c>
+      <x:c r="I32" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J32" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="1" t="str">
@@ -1114,6 +1264,10 @@
       <x:c r="H33" s="1" t="str">
         <x:v>Control the descent.</x:v>
       </x:c>
+      <x:c r="I33" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J33" t="str"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="1" t="str">
@@ -1140,6 +1294,10 @@
       <x:c r="H34" s="1" t="str">
         <x:v>Brace hard through the midline.</x:v>
       </x:c>
+      <x:c r="I34" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J34" t="str"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="1" t="str">
@@ -1166,6 +1324,10 @@
       <x:c r="H35" s="1" t="str">
         <x:v>Don't let the torso rotate.</x:v>
       </x:c>
+      <x:c r="I35" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J35" t="str"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="1" t="str">
@@ -1190,6 +1352,12 @@
       <x:c r="H36" s="1" t="str">
         <x:v>Press hard and finish strong.</x:v>
       </x:c>
+      <x:c r="I36" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J36" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="1" t="str">
@@ -1216,6 +1384,12 @@
       <x:c r="H37" s="1" t="str">
         <x:v>Stable base, strong finish.</x:v>
       </x:c>
+      <x:c r="I37" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J37" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="1" t="str">
@@ -1240,6 +1414,12 @@
       <x:c r="H38" s="1" t="str">
         <x:v>No arching through the lower back.</x:v>
       </x:c>
+      <x:c r="I38" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="1" t="str">
@@ -1264,6 +1444,12 @@
       <x:c r="H39" s="1" t="str">
         <x:v>Ribs down, control the descent.</x:v>
       </x:c>
+      <x:c r="I39" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="1" t="str">
@@ -1288,6 +1474,12 @@
       <x:c r="H40" s="1" t="str">
         <x:v>Fight the rotation, ribs stay down.</x:v>
       </x:c>
+      <x:c r="I40" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="1" t="str">
@@ -1312,6 +1504,8 @@
       <x:c r="H41" s="1" t="str">
         <x:v>Full lockout, reset quickly.</x:v>
       </x:c>
+      <x:c r="I41"/>
+      <x:c r="J41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="1" t="str">
@@ -1338,6 +1532,12 @@
       <x:c r="H42" s="1" t="str">
         <x:v>Stay tight through midline. Can be done seated on a bench, or with dumbbells.</x:v>
       </x:c>
+      <x:c r="I42" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="1" t="str">
@@ -1362,6 +1562,12 @@
       <x:c r="H43" s="1" t="str">
         <x:v>Squeeze the shoulder blades at the top.</x:v>
       </x:c>
+      <x:c r="I43" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="1" t="str">
@@ -1388,6 +1594,12 @@
       <x:c r="H44" s="1" t="str">
         <x:v>Retract and hold for a beat.</x:v>
       </x:c>
+      <x:c r="I44" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="1" t="str">
@@ -1412,6 +1624,12 @@
       <x:c r="H45" s="1" t="str">
         <x:v>Keep the hips and shoulders square.</x:v>
       </x:c>
+      <x:c r="I45" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="1" t="str">
@@ -1436,6 +1654,12 @@
       <x:c r="H46" s="1" t="str">
         <x:v>Slow on the return.</x:v>
       </x:c>
+      <x:c r="I46" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="1" t="str">
@@ -1460,6 +1684,12 @@
       <x:c r="H47" s="1" t="str">
         <x:v>Squeeze the rear delts, slow return.</x:v>
       </x:c>
+      <x:c r="I47" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="1" t="str">
@@ -1484,6 +1714,10 @@
       <x:c r="H48" s="1" t="str">
         <x:v>Light weight, feel the squeeze.</x:v>
       </x:c>
+      <x:c r="I48" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J48" t="str"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="1" t="str">
@@ -1508,6 +1742,10 @@
       <x:c r="H49" s="1" t="str">
         <x:v>Elbows straight, controlled return.</x:v>
       </x:c>
+      <x:c r="I49" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J49" t="str"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="1" t="str">
@@ -1532,6 +1770,12 @@
       <x:c r="H50" s="1" t="str">
         <x:v>Initiate with the lats, not the arms. Add weight once bodyweight sets feel easy.</x:v>
       </x:c>
+      <x:c r="I50" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J50" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="1" t="str">
@@ -1556,6 +1800,12 @@
       <x:c r="H51" s="1" t="str">
         <x:v>Control the lowering.</x:v>
       </x:c>
+      <x:c r="I51" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J51" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="1" t="str">
@@ -1580,6 +1830,12 @@
       <x:c r="H52" s="1" t="str">
         <x:v>Squeeze at the bottom, slow return.</x:v>
       </x:c>
+      <x:c r="I52" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J52" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="1" t="str">
@@ -1602,6 +1858,12 @@
         <x:v>Use V grip attachment, puff chest out as hands come down.</x:v>
       </x:c>
       <x:c r="H53" s="1" t="str"/>
+      <x:c r="I53" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J53" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="1" t="str">
@@ -1628,6 +1890,12 @@
       <x:c r="H54" s="1" t="str">
         <x:v>Stay tight through the midline; control the return to a full stretch.</x:v>
       </x:c>
+      <x:c r="I54" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J54" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="1" t="str">
@@ -1652,6 +1920,10 @@
       <x:c r="H55" s="1" t="str">
         <x:v>Land soft, absorb with the hips.</x:v>
       </x:c>
+      <x:c r="I55" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J55" t="str"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="1" t="str">
@@ -1676,6 +1948,10 @@
       <x:c r="H56" s="1" t="str">
         <x:v>Stick the landing.</x:v>
       </x:c>
+      <x:c r="I56" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J56" t="str"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="1" t="str">
@@ -1700,6 +1976,10 @@
       <x:c r="H57" s="1" t="str">
         <x:v>Land soft, reset between reps.</x:v>
       </x:c>
+      <x:c r="I57" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J57" t="str"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="1" t="str">
@@ -1726,6 +2006,12 @@
       <x:c r="H58" s="1" t="str">
         <x:v>Stick each landing before the next.</x:v>
       </x:c>
+      <x:c r="I58" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J58" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="1" t="str">
@@ -1752,6 +2038,12 @@
       <x:c r="H59" s="1" t="str">
         <x:v>Minimum ground contact time.</x:v>
       </x:c>
+      <x:c r="I59" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J59" t="str">
+        <x:v>frontal, transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="1" t="str">
@@ -1776,6 +2068,12 @@
       <x:c r="H60" s="1" t="str">
         <x:v>Breathe and keep moving. Weight shown is per hand.</x:v>
       </x:c>
+      <x:c r="I60" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J60" t="str">
+        <x:v>frontal, transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="1" t="str">
@@ -1800,6 +2098,12 @@
       <x:c r="H61" s="1" t="str">
         <x:v>Short steady steps, no leaning back.</x:v>
       </x:c>
+      <x:c r="I61" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J61" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="1" t="str">
@@ -1824,6 +2128,12 @@
       <x:c r="H62" s="1" t="str">
         <x:v>Don’t rest weight on thigh.</x:v>
       </x:c>
+      <x:c r="I62" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J62" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="1" t="str">
@@ -1848,6 +2158,12 @@
       <x:c r="H63" s="1" t="str">
         <x:v>Weight shown is per hand.</x:v>
       </x:c>
+      <x:c r="I63" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J63" t="str">
+        <x:v>frontal, transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="1" t="str">
@@ -1872,6 +2188,10 @@
       <x:c r="H64" s="1" t="str">
         <x:v>Squeeze at the top, controlled lower.</x:v>
       </x:c>
+      <x:c r="I64" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J64" t="str"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="1" t="str">
@@ -1898,6 +2218,10 @@
       <x:c r="H65" s="1" t="str">
         <x:v>Full range, elbows stay in place.</x:v>
       </x:c>
+      <x:c r="I65" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J65" t="str"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="1" t="str">
@@ -1922,6 +2246,10 @@
       <x:c r="H66" s="1" t="str">
         <x:v>No swinging, control the bar path.</x:v>
       </x:c>
+      <x:c r="I66" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J66" t="str"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="1" t="str">
@@ -1946,6 +2274,10 @@
       <x:c r="H67" s="1" t="str">
         <x:v>Smooth tempo, squeeze at the top.</x:v>
       </x:c>
+      <x:c r="I67" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J67" t="str"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="1" t="str">
@@ -1970,6 +2302,10 @@
       <x:c r="H68" s="1" t="str">
         <x:v>Control both directions.</x:v>
       </x:c>
+      <x:c r="I68" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J68" t="str"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="1" t="str">
@@ -1994,6 +2330,10 @@
       <x:c r="H69" s="1" t="str">
         <x:v>Slow curl, squeeze at the top.</x:v>
       </x:c>
+      <x:c r="I69" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J69" t="str"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="1" t="str">
@@ -2018,6 +2358,10 @@
       <x:c r="H70" s="1" t="str">
         <x:v>Control both directions, no momentum.</x:v>
       </x:c>
+      <x:c r="I70" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J70" t="str"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="1" t="str">
@@ -2044,6 +2388,10 @@
       <x:c r="H71" s="1" t="str">
         <x:v>Slow on the way down.</x:v>
       </x:c>
+      <x:c r="I71" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J71" t="str"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="1" t="str">
@@ -2068,6 +2416,10 @@
       <x:c r="H72" s="1" t="str">
         <x:v>Strict curl, no body swing.</x:v>
       </x:c>
+      <x:c r="I72" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J72" t="str"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="1" t="str">
@@ -2092,6 +2444,10 @@
       <x:c r="H73" s="1" t="str">
         <x:v>Constant tension, no jerking.</x:v>
       </x:c>
+      <x:c r="I73" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J73" t="str"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="1" t="str">
@@ -2116,6 +2472,10 @@
       <x:c r="H74" s="1" t="str">
         <x:v>Constant tension, no slack.</x:v>
       </x:c>
+      <x:c r="I74" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J74" t="str"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="1" t="str">
@@ -2140,6 +2500,10 @@
       <x:c r="H75" s="1" t="str">
         <x:v>Elbows stay pointed forward.</x:v>
       </x:c>
+      <x:c r="I75" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J75" t="str"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="1" t="str">
@@ -2166,6 +2530,10 @@
       <x:c r="H76" s="1" t="str">
         <x:v>Elbows stay fixed in place.</x:v>
       </x:c>
+      <x:c r="I76" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J76" t="str"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="1" t="str">
@@ -2190,6 +2558,10 @@
       <x:c r="H77" s="1" t="str">
         <x:v>Squeeze at the top, slow return.</x:v>
       </x:c>
+      <x:c r="I77" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J77" t="str"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="1" t="str">
@@ -2214,6 +2586,10 @@
       <x:c r="H78" s="1" t="str">
         <x:v>Empty the triceps by the final rep.</x:v>
       </x:c>
+      <x:c r="I78" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J78" t="str"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="1" t="str">
@@ -2238,6 +2614,10 @@
       <x:c r="H79" s="1" t="str">
         <x:v>No momentum, strict form.</x:v>
       </x:c>
+      <x:c r="I79" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J79" t="str"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="1" t="str">
@@ -2262,6 +2642,12 @@
       <x:c r="H80" s="1" t="str">
         <x:v>Light weight, pause at the top.</x:v>
       </x:c>
+      <x:c r="I80" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J80" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="1" t="str">
@@ -2286,6 +2672,10 @@
       <x:c r="H81" s="1" t="str">
         <x:v>Pause at the top, controlled lower.</x:v>
       </x:c>
+      <x:c r="I81" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J81" t="str"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="1" t="str">
@@ -2312,6 +2702,10 @@
       <x:c r="H82" s="1" t="str">
         <x:v>Fight gravity the whole way down.</x:v>
       </x:c>
+      <x:c r="I82" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J82" t="str"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="1" t="str">
@@ -2334,6 +2728,10 @@
         <x:v>Pad should be lower calf area, squeeze heels to butt.</x:v>
       </x:c>
       <x:c r="H83" s="1" t="str"/>
+      <x:c r="I83" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J83" t="str"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="1" t="str">
@@ -2356,6 +2754,10 @@
         <x:v>Drive feet to ceiling, lean back slightly if possible.</x:v>
       </x:c>
       <x:c r="H84" s="1" t="str"/>
+      <x:c r="I84" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J84" t="str"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="1" t="str">
@@ -2380,6 +2782,10 @@
       <x:c r="H85" s="1" t="str">
         <x:v>Pause high, lower slowly.</x:v>
       </x:c>
+      <x:c r="I85" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J85" t="str"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="1" t="str">
@@ -2406,6 +2812,10 @@
       <x:c r="H86" s="1" t="str">
         <x:v>Controlled reps, full range.</x:v>
       </x:c>
+      <x:c r="I86" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J86" t="str"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="1" t="str">
@@ -2428,6 +2838,12 @@
         <x:v>Upper back on bench, add weight to hips, one leg up, drive hips to sky, squeeze glutes.</x:v>
       </x:c>
       <x:c r="H87" s="1" t="str"/>
+      <x:c r="I87" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J87" t="str">
+        <x:v>frontal, transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="1" t="str">
@@ -2452,6 +2868,10 @@
         <x:v>Squeeze glutes at top, round slightly at bottom.</x:v>
       </x:c>
       <x:c r="H88" s="1" t="str"/>
+      <x:c r="I88" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J88" t="str"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="1" t="str">
@@ -2478,6 +2898,12 @@
       <x:c r="H89" s="1" t="str">
         <x:v>Fight gravity the whole way.</x:v>
       </x:c>
+      <x:c r="I89" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J89" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="str">
@@ -2502,6 +2928,12 @@
       <x:c r="H90" s="1" t="str">
         <x:v>Squeeze the rear delts.</x:v>
       </x:c>
+      <x:c r="I90" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J90" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="1" t="str">
@@ -2526,6 +2958,12 @@
       <x:c r="H91" s="1" t="str">
         <x:v>Squeeze the shoulder blades back.</x:v>
       </x:c>
+      <x:c r="I91" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J91" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="1" t="str">
@@ -2550,6 +2988,12 @@
       <x:c r="H92" s="1" t="str">
         <x:v>Scale with foot position.</x:v>
       </x:c>
+      <x:c r="I92" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J92" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="1" t="str">
@@ -2574,6 +3018,12 @@
       <x:c r="H93" s="1" t="str">
         <x:v>Hold tension, no dropping.</x:v>
       </x:c>
+      <x:c r="I93" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J93" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="1" t="str">
@@ -2598,6 +3048,12 @@
       <x:c r="H94" s="1" t="str">
         <x:v>Don’t let hips drop.</x:v>
       </x:c>
+      <x:c r="I94" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J94" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="1" t="str">
@@ -2622,6 +3078,10 @@
       <x:c r="H95" s="1" t="str">
         <x:v>Hold each squeeze for a beat.</x:v>
       </x:c>
+      <x:c r="I95" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J95" t="str"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="1" t="str">
@@ -2646,6 +3106,12 @@
       <x:c r="H96" s="1" t="str">
         <x:v>Heel down, chest up, push back through. Hold rack if needed.</x:v>
       </x:c>
+      <x:c r="I96" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J96" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="1" t="str">
@@ -2670,6 +3136,12 @@
       <x:c r="H97" s="1" t="str">
         <x:v>Knee tracks over toes, drive back to standing.</x:v>
       </x:c>
+      <x:c r="I97" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J97" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="1" t="str">
@@ -2694,6 +3166,12 @@
       <x:c r="H98" s="1" t="str">
         <x:v>Three-second lowering.</x:v>
       </x:c>
+      <x:c r="I98" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J98" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="1" t="str">
@@ -2718,6 +3196,10 @@
       <x:c r="H99" s="1" t="str">
         <x:v>Slow tempo, no bouncing.</x:v>
       </x:c>
+      <x:c r="I99" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J99" t="str"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="1" t="str">
@@ -2740,6 +3222,10 @@
         <x:v>Band behind knee, step back for tension, straighten knee and squeeze quads.</x:v>
       </x:c>
       <x:c r="H100" s="1" t="str"/>
+      <x:c r="I100" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J100" t="str"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="1" t="str">
@@ -2762,6 +3248,12 @@
         <x:v>Single or double leg, slight knee bend, drive heel into ground, keep hips high.</x:v>
       </x:c>
       <x:c r="H101" s="1" t="str"/>
+      <x:c r="I101" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J101" t="str">
+        <x:v>frontal, transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="1" t="str">
@@ -2784,6 +3276,10 @@
         <x:v>Band behind knees, tension on bands, sit back into a squat and hold.</x:v>
       </x:c>
       <x:c r="H102" s="1" t="str"/>
+      <x:c r="I102" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J102" t="str"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="1" t="str">
@@ -2806,6 +3302,12 @@
         <x:v>Drive knee forward, tap opposite heel on ground, knee tracks over toes.</x:v>
       </x:c>
       <x:c r="H103" s="1" t="str"/>
+      <x:c r="I103" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="1" t="str">
@@ -2828,6 +3330,12 @@
         <x:v>Sit back into athletic position, band around feet, push off outside leg, keep knees slightly pointed out.</x:v>
       </x:c>
       <x:c r="H104" s="1" t="str"/>
+      <x:c r="I104" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="1" t="str">
@@ -2852,6 +3360,10 @@
       <x:c r="H105" s="1" t="str">
         <x:v>Hips stay square, slight knee and hip bend.</x:v>
       </x:c>
+      <x:c r="I105" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J105" t="str"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="1" t="str">
@@ -2878,6 +3390,10 @@
       <x:c r="H106" s="1" t="str">
         <x:v>Opposite arm and leg, slow.</x:v>
       </x:c>
+      <x:c r="I106" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J106" t="str"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="1" t="str">
@@ -2902,6 +3418,10 @@
       <x:c r="H107" s="1" t="str">
         <x:v>Lower back stays glued to the floor.</x:v>
       </x:c>
+      <x:c r="I107" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J107" t="str"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="1" t="str">
@@ -2926,6 +3446,10 @@
       <x:c r="H108" s="1" t="str">
         <x:v>Slow extension, full exhale.</x:v>
       </x:c>
+      <x:c r="I108" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J108" t="str"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="1" t="str">
@@ -2950,6 +3474,10 @@
       <x:c r="H109" s="1" t="str">
         <x:v>Drive low back into hands slightly.</x:v>
       </x:c>
+      <x:c r="I109" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J109" t="str"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="1" t="str">
@@ -2976,6 +3504,10 @@
       <x:c r="H110" s="1" t="str">
         <x:v>Ribs down, slightly rounded back, no sagging at hips.</x:v>
       </x:c>
+      <x:c r="I110" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J110" t="str"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="1" t="str">
@@ -3000,6 +3532,10 @@
       <x:c r="H111" s="1" t="str">
         <x:v>No swinging.</x:v>
       </x:c>
+      <x:c r="I111" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J111" t="str"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="1" t="str">
@@ -3026,6 +3562,12 @@
       <x:c r="H112" s="1" t="str">
         <x:v>Slow and controlled.</x:v>
       </x:c>
+      <x:c r="I112" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J112" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="1" t="str">
@@ -3050,6 +3592,12 @@
       <x:c r="H113" s="1" t="str">
         <x:v>Breathe behind the brace.</x:v>
       </x:c>
+      <x:c r="I113" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J113" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="1" t="str">
@@ -3074,6 +3622,10 @@
         <x:v>Keep spine neutral, brace midline, squeeze butt, breathe.</x:v>
       </x:c>
       <x:c r="H114" s="1" t="str"/>
+      <x:c r="I114" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J114" t="str"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="1" t="str">
@@ -3096,6 +3648,10 @@
         <x:v>Stay tight, remember to breathe, low back pinned to floor.</x:v>
       </x:c>
       <x:c r="H115" s="1" t="str"/>
+      <x:c r="I115" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J115" t="str"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="1" t="str">
@@ -3118,6 +3674,10 @@
         <x:v>Spine stays neutral, resist rotation through midline.</x:v>
       </x:c>
       <x:c r="H116" s="1" t="str"/>
+      <x:c r="I116" t="str">
+        <x:v>multiplanar</x:v>
+      </x:c>
+      <x:c r="J116" t="str"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="1" t="str">
@@ -3142,6 +3702,10 @@
         <x:v>Control the way down, low back should be slightly rounded and roll over ground.</x:v>
       </x:c>
       <x:c r="H117" s="1" t="str"/>
+      <x:c r="I117" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J117" t="str"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="1" t="str">
@@ -3164,6 +3728,12 @@
         <x:v>Side plank, row band to top of belly, resist rolling forward.</x:v>
       </x:c>
       <x:c r="H118" s="1" t="str"/>
+      <x:c r="I118" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J118" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="1" t="str">
@@ -3188,6 +3758,12 @@
       <x:c r="H119" s="1" t="str">
         <x:v>Feet stay planted.</x:v>
       </x:c>
+      <x:c r="I119" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J119" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="1" t="str">
@@ -3212,6 +3788,12 @@
       <x:c r="H120" s="1" t="str">
         <x:v>Controlled rotation, not a throw.</x:v>
       </x:c>
+      <x:c r="I120" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J120" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="1" t="str">
@@ -3236,6 +3818,8 @@
       <x:c r="H121" s="1" t="str">
         <x:v>Slow and controlled arc.</x:v>
       </x:c>
+      <x:c r="I121"/>
+      <x:c r="J121"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="1" t="str">
@@ -3262,6 +3846,8 @@
       <x:c r="H122" s="1" t="str">
         <x:v>Press smooth, keep ribs down.</x:v>
       </x:c>
+      <x:c r="I122"/>
+      <x:c r="J122"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="1" t="str">
@@ -3286,6 +3872,8 @@
       <x:c r="H123" s="1" t="str">
         <x:v>Move slowly, no sagging hips.</x:v>
       </x:c>
+      <x:c r="I123"/>
+      <x:c r="J123"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="1" t="str">
@@ -3308,6 +3896,8 @@
         <x:v>dead hang from bar and relax, pull yourself higher only using your shoulder blades, don't bend arms</x:v>
       </x:c>
       <x:c r="H124" s="1" t="str"/>
+      <x:c r="I124"/>
+      <x:c r="J124"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="1" t="str">
@@ -3332,6 +3922,10 @@
       <x:c r="H125" s="1" t="str">
         <x:v>Curl heels into butt.</x:v>
       </x:c>
+      <x:c r="I125" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J125" t="str"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="1" t="str">
@@ -3356,6 +3950,8 @@
       <x:c r="H126" s="1" t="str">
         <x:v>Relax into the pressure.</x:v>
       </x:c>
+      <x:c r="I126"/>
+      <x:c r="J126"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="1" t="str">
@@ -3380,6 +3976,8 @@
       <x:c r="H127" s="1" t="str">
         <x:v>Open the ribs and breathe.</x:v>
       </x:c>
+      <x:c r="I127"/>
+      <x:c r="J127"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="1" t="str">
@@ -3404,6 +4002,8 @@
       <x:c r="H128" s="1" t="str">
         <x:v>Stack the legs to dial pressure.</x:v>
       </x:c>
+      <x:c r="I128"/>
+      <x:c r="J128"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="1" t="str">
@@ -3428,6 +4028,8 @@
       <x:c r="H129" s="1" t="str">
         <x:v>Roll under the armpit, breathe into it.</x:v>
       </x:c>
+      <x:c r="I129"/>
+      <x:c r="J129"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="1" t="str">
@@ -3452,6 +4054,8 @@
       <x:c r="H130" s="1" t="str">
         <x:v>Breathe through each hold.</x:v>
       </x:c>
+      <x:c r="I130"/>
+      <x:c r="J130"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="1" t="str">
@@ -3476,6 +4080,8 @@
       <x:c r="H131" s="1" t="str">
         <x:v>Hold 30-60 seconds per side.</x:v>
       </x:c>
+      <x:c r="I131"/>
+      <x:c r="J131"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="1" t="str">
@@ -3500,6 +4106,8 @@
       <x:c r="H132" s="1" t="str">
         <x:v>Stay tall, shift weight gently.</x:v>
       </x:c>
+      <x:c r="I132"/>
+      <x:c r="J132"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="1" t="str">
@@ -3524,6 +4132,8 @@
       <x:c r="H133" s="1" t="str">
         <x:v>Match each position to a breath.</x:v>
       </x:c>
+      <x:c r="I133"/>
+      <x:c r="J133"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="1" t="str">
@@ -3548,6 +4158,8 @@
       <x:c r="H134" s="1" t="str">
         <x:v>Then rotate and reach to the sky.</x:v>
       </x:c>
+      <x:c r="I134"/>
+      <x:c r="J134"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="1" t="str">
@@ -3572,6 +4184,8 @@
       <x:c r="H135" s="1" t="str">
         <x:v>Breathe and hold position.</x:v>
       </x:c>
+      <x:c r="I135"/>
+      <x:c r="J135"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="1" t="str">
@@ -3596,6 +4210,8 @@
       <x:c r="H136" s="1" t="str">
         <x:v>Tall through the midline, no arching.</x:v>
       </x:c>
+      <x:c r="I136"/>
+      <x:c r="J136"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="1" t="str">
@@ -3620,6 +4236,8 @@
       <x:c r="H137" s="1" t="str">
         <x:v>Follow the hand with the eyes.</x:v>
       </x:c>
+      <x:c r="I137"/>
+      <x:c r="J137"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="1" t="str">
@@ -3644,6 +4262,8 @@
       <x:c r="H138" s="1" t="str">
         <x:v>Sink in and breathe.</x:v>
       </x:c>
+      <x:c r="I138"/>
+      <x:c r="J138"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="1" t="str">
@@ -3668,6 +4288,8 @@
       <x:c r="H139" s="1" t="str">
         <x:v>Hold the end range, breathe.</x:v>
       </x:c>
+      <x:c r="I139"/>
+      <x:c r="J139"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="1" t="str">
@@ -3692,6 +4314,8 @@
       <x:c r="H140" s="1" t="str">
         <x:v>Big stretch through the chest, breathe slow.</x:v>
       </x:c>
+      <x:c r="I140"/>
+      <x:c r="J140"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="1" t="str">
@@ -3716,6 +4340,8 @@
       <x:c r="H141" s="1" t="str">
         <x:v>Sink the chest, breathe under the armpit, slight lean to one side.</x:v>
       </x:c>
+      <x:c r="I141"/>
+      <x:c r="J141"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="1" t="str">
@@ -3740,6 +4366,8 @@
       <x:c r="H142" s="1" t="str">
         <x:v>Breathe - let the spine decompress.</x:v>
       </x:c>
+      <x:c r="I142"/>
+      <x:c r="J142"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="1" t="str">
@@ -3766,6 +4394,8 @@
       <x:c r="H143" s="1" t="str">
         <x:v>Build tolerance gradually.</x:v>
       </x:c>
+      <x:c r="I143"/>
+      <x:c r="J143"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="1" t="str">
@@ -3790,6 +4420,8 @@
       <x:c r="H144" s="1" t="str">
         <x:v>Switch to bent-knee for the soleus.</x:v>
       </x:c>
+      <x:c r="I144"/>
+      <x:c r="J144"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="1" t="str">
@@ -3814,6 +4446,8 @@
         <x:v>Pin legs in 45 deg hyper, bend sideways slowly, don’t push too far, just enough to feel tension.</x:v>
       </x:c>
       <x:c r="H145" s="1" t="str"/>
+      <x:c r="I145"/>
+      <x:c r="J145"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="1" t="str">
@@ -3838,6 +4472,8 @@
         <x:v>Elevate front foot, body stays upright, drive hips to front heel, go slow and pause at bottom.</x:v>
       </x:c>
       <x:c r="H146" s="1" t="str"/>
+      <x:c r="I146"/>
+      <x:c r="J146"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="1" t="str">
@@ -3860,6 +4496,8 @@
         <x:v>Place blocks at level you’re comfortable with, fold forward, bend and straight one leg at a time, slowly.</x:v>
       </x:c>
       <x:c r="H147" s="1" t="str"/>
+      <x:c r="I147"/>
+      <x:c r="J147"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="1" t="str">
@@ -3882,6 +4520,8 @@
         <x:v>Upper back and butt against wall, feet together, knees towards ground, add weight to knee if too easy</x:v>
       </x:c>
       <x:c r="H148" s="1" t="str"/>
+      <x:c r="I148"/>
+      <x:c r="J148"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="1" t="str">
@@ -3904,6 +4544,8 @@
         <x:v>Keep back neutral, lift outside leg out and up, can use bent leg to start</x:v>
       </x:c>
       <x:c r="H149" s="1" t="str"/>
+      <x:c r="I149"/>
+      <x:c r="J149"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="1" t="str">
@@ -3926,6 +4568,8 @@
         <x:v>Tuck your chin and slowly roll down one segment at a time. Add small weight when easy</x:v>
       </x:c>
       <x:c r="H150" s="1" t="str"/>
+      <x:c r="I150"/>
+      <x:c r="J150"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="1" t="str">
@@ -3948,6 +4592,8 @@
         <x:v>Rest upper back on bench, dumbbell over, don't allow ribs to flare up, pause at end range</x:v>
       </x:c>
       <x:c r="H151" s="1" t="str"/>
+      <x:c r="I151"/>
+      <x:c r="J151"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="1" t="str">
@@ -3972,6 +4618,8 @@
       <x:c r="H152" s="1" t="str">
         <x:v>This is blood flow, not training.</x:v>
       </x:c>
+      <x:c r="I152"/>
+      <x:c r="J152"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="1" t="str">
@@ -3996,6 +4644,8 @@
       <x:c r="H153" s="1" t="str">
         <x:v>No holding the rails.</x:v>
       </x:c>
+      <x:c r="I153"/>
+      <x:c r="J153"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="1" t="str">
@@ -4020,6 +4670,8 @@
       <x:c r="H154" s="1" t="str">
         <x:v>Get outside and move.</x:v>
       </x:c>
+      <x:c r="I154"/>
+      <x:c r="J154"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="1" t="str">
@@ -4044,6 +4696,8 @@
       <x:c r="H155" s="1" t="str">
         <x:v>Pause at the bottom of each breath.</x:v>
       </x:c>
+      <x:c r="I155"/>
+      <x:c r="J155"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="1" t="str">
@@ -4068,6 +4722,8 @@
       <x:c r="H156" s="1" t="str">
         <x:v>Feel the floor push back on the exhale.</x:v>
       </x:c>
+      <x:c r="I156"/>
+      <x:c r="J156"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="1" t="str">
@@ -4092,6 +4748,8 @@
       <x:c r="H157" s="1" t="str">
         <x:v>Stay relaxed, find the rhythm.</x:v>
       </x:c>
+      <x:c r="I157"/>
+      <x:c r="J157"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="1" t="str">
@@ -4116,6 +4774,8 @@
       <x:c r="H158" s="1" t="str">
         <x:v>Slow breaths into the back.</x:v>
       </x:c>
+      <x:c r="I158"/>
+      <x:c r="J158"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="1" t="str">
@@ -4142,6 +4802,8 @@
       <x:c r="H159" s="1" t="str">
         <x:v>Full recovery between efforts.</x:v>
       </x:c>
+      <x:c r="I159"/>
+      <x:c r="J159"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="1" t="str">
@@ -4168,6 +4830,8 @@
       <x:c r="H160" s="1" t="str">
         <x:v>Walk back for full recovery.</x:v>
       </x:c>
+      <x:c r="I160"/>
+      <x:c r="J160"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="1" t="str">
@@ -4194,6 +4858,8 @@
       <x:c r="H161" s="1" t="str">
         <x:v>If speed drops, the set is done.</x:v>
       </x:c>
+      <x:c r="I161"/>
+      <x:c r="J161"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="1" t="str">
@@ -4218,6 +4884,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H162" s="1" t="str"/>
+      <x:c r="I162"/>
+      <x:c r="J162"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="1" t="str">
@@ -4242,6 +4910,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H163" s="1" t="str"/>
+      <x:c r="I163"/>
+      <x:c r="J163"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="1" t="str">
@@ -4266,6 +4936,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H164" s="1" t="str"/>
+      <x:c r="I164"/>
+      <x:c r="J164"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="1" t="str">
@@ -4290,6 +4962,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H165" s="1" t="str"/>
+      <x:c r="I165"/>
+      <x:c r="J165"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="1" t="str">
@@ -4314,6 +4988,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H166" s="1" t="str"/>
+      <x:c r="I166"/>
+      <x:c r="J166"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="1" t="str">
@@ -4338,6 +5014,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H167" s="1" t="str"/>
+      <x:c r="I167"/>
+      <x:c r="J167"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="1" t="str">
@@ -4362,6 +5040,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H168" s="1" t="str"/>
+      <x:c r="I168"/>
+      <x:c r="J168"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="1" t="str">
@@ -4388,6 +5068,8 @@
       <x:c r="H169" s="1" t="str">
         <x:v>Settle in, breathe steadily.</x:v>
       </x:c>
+      <x:c r="I169"/>
+      <x:c r="J169"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="1" t="str">
@@ -4412,6 +5094,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H170" s="1" t="str"/>
+      <x:c r="I170"/>
+      <x:c r="J170"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="1" t="str">
@@ -4436,6 +5120,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H171" s="1" t="str"/>
+      <x:c r="I171"/>
+      <x:c r="J171"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="1" t="str">
@@ -4460,6 +5146,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H172" s="1" t="str"/>
+      <x:c r="I172"/>
+      <x:c r="J172"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="1" t="str">
@@ -4484,6 +5172,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H173" s="1" t="str"/>
+      <x:c r="I173"/>
+      <x:c r="J173"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="1" t="str">
@@ -4508,6 +5198,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H174" s="1" t="str"/>
+      <x:c r="I174"/>
+      <x:c r="J174"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="1" t="str">
@@ -4532,6 +5224,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H175" s="1" t="str"/>
+      <x:c r="I175"/>
+      <x:c r="J175"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="1" t="str">
@@ -4556,6 +5250,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H176" s="1" t="str"/>
+      <x:c r="I176"/>
+      <x:c r="J176"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="1" t="str">
@@ -4580,6 +5276,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H177" s="1" t="str"/>
+      <x:c r="I177"/>
+      <x:c r="J177"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="1" t="str">
@@ -4604,6 +5302,8 @@
         <x:v>Hit X number of calories every minute, the faster you do them the more rest you get.</x:v>
       </x:c>
       <x:c r="H178" s="1" t="str"/>
+      <x:c r="I178"/>
+      <x:c r="J178"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="1" t="str">
@@ -4630,6 +5330,8 @@
       <x:c r="H179" s="1" t="str">
         <x:v>Controlled breathing throughout.</x:v>
       </x:c>
+      <x:c r="I179"/>
+      <x:c r="J179"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="1" t="str">
@@ -4654,6 +5356,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H180" s="1" t="str"/>
+      <x:c r="I180"/>
+      <x:c r="J180"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="1" t="str">
@@ -4678,6 +5382,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H181" s="1" t="str"/>
+      <x:c r="I181"/>
+      <x:c r="J181"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="1" t="str">
@@ -4702,6 +5408,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H182" s="1" t="str"/>
+      <x:c r="I182"/>
+      <x:c r="J182"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="1" t="str">
@@ -4726,6 +5434,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H183" s="1" t="str"/>
+      <x:c r="I183"/>
+      <x:c r="J183"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="1" t="str">
@@ -4750,6 +5460,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H184" s="1" t="str"/>
+      <x:c r="I184"/>
+      <x:c r="J184"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="1" t="str">
@@ -4776,6 +5488,8 @@
       <x:c r="H185" s="1" t="str">
         <x:v>Recover fully between sprints.</x:v>
       </x:c>
+      <x:c r="I185"/>
+      <x:c r="J185"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="1" t="str">
@@ -4802,6 +5516,8 @@
       <x:c r="H186" s="1" t="str">
         <x:v>Maintain power, recover completely.</x:v>
       </x:c>
+      <x:c r="I186"/>
+      <x:c r="J186"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="1" t="str">
@@ -4826,6 +5542,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H187" s="1" t="str"/>
+      <x:c r="I187"/>
+      <x:c r="J187"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="1" t="str">
@@ -4850,6 +5568,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H188" s="1" t="str"/>
+      <x:c r="I188"/>
+      <x:c r="J188"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="1" t="str">
@@ -4876,6 +5596,8 @@
       <x:c r="H189" s="1" t="str">
         <x:v>Move and loosen up.</x:v>
       </x:c>
+      <x:c r="I189"/>
+      <x:c r="J189"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="1" t="str">
@@ -4902,6 +5624,8 @@
       <x:c r="H190" s="1" t="str">
         <x:v>This is recovery, not training.</x:v>
       </x:c>
+      <x:c r="I190"/>
+      <x:c r="J190"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="1" t="str">
@@ -4928,6 +5652,8 @@
       <x:c r="H191" s="1" t="str">
         <x:v>This is active recovery, not training.</x:v>
       </x:c>
+      <x:c r="I191"/>
+      <x:c r="J191"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="1" t="str">
@@ -4954,6 +5680,8 @@
       <x:c r="H192" s="1" t="str">
         <x:v>Focus on form, not intensity.</x:v>
       </x:c>
+      <x:c r="I192"/>
+      <x:c r="J192"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="1" t="str">
@@ -4978,6 +5706,8 @@
         <x:v>PENDING — Stage B</x:v>
       </x:c>
       <x:c r="H193" s="1" t="str"/>
+      <x:c r="I193"/>
+      <x:c r="J193"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="1" t="str">
@@ -5004,6 +5734,8 @@
       <x:c r="H194" s="1" t="str">
         <x:v>This is recovery, not intensity.</x:v>
       </x:c>
+      <x:c r="I194"/>
+      <x:c r="J194"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="1" t="str">
@@ -5028,6 +5760,8 @@
         <x:v>Try to run this at the same pace for the entire 2km</x:v>
       </x:c>
       <x:c r="H195" s="1" t="str"/>
+      <x:c r="I195"/>
+      <x:c r="J195"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="1"/>
@@ -5038,6 +5772,8 @@
       <x:c r="F196" s="1"/>
       <x:c r="G196" s="1"/>
       <x:c r="H196"/>
+      <x:c r="I196"/>
+      <x:c r="J196"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" t="str">
@@ -5062,6 +5798,8 @@
       <x:c r="H197" t="str">
         <x:v>Stop if reps get slow.</x:v>
       </x:c>
+      <x:c r="I197"/>
+      <x:c r="J197"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="1" t="str">
@@ -5086,6 +5824,8 @@
         <x:v>Stand tall, jump and then bounce off the balls of your feet.</x:v>
       </x:c>
       <x:c r="H198" s="1" t="str"/>
+      <x:c r="I198"/>
+      <x:c r="J198"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="1" t="str">
@@ -5110,6 +5850,8 @@
         <x:v>Jump off outside leg to the side, turn in air and land in a squat.</x:v>
       </x:c>
       <x:c r="H199" s="1" t="str"/>
+      <x:c r="I199"/>
+      <x:c r="J199"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="1" t="str">
@@ -5134,6 +5876,8 @@
         <x:v>Start in kneeling position, jump onto feet, land in a squat.</x:v>
       </x:c>
       <x:c r="H200" s="1" t="str"/>
+      <x:c r="I200"/>
+      <x:c r="J200"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="1" t="str">
@@ -5160,6 +5904,12 @@
       <x:c r="H201" s="1" t="str">
         <x:v>Land soft and controlled.</x:v>
       </x:c>
+      <x:c r="I201" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J201" t="str">
+        <x:v>frontal, transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="1" t="str">
@@ -5184,6 +5934,8 @@
       <x:c r="H202" s="1" t="str">
         <x:v>Stop when reps slow. Sore wrists? Elevate hands on box.</x:v>
       </x:c>
+      <x:c r="I202"/>
+      <x:c r="J202"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="1" t="str">
@@ -5210,6 +5962,8 @@
       <x:c r="H203" s="1" t="str">
         <x:v>Drive hard, fast lockout.</x:v>
       </x:c>
+      <x:c r="I203"/>
+      <x:c r="J203"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="1" t="str">
@@ -5234,6 +5988,8 @@
         <x:v>Wrap band around each side of bar, stand on band, get tight, explode up, control down.</x:v>
       </x:c>
       <x:c r="H204" s="1" t="str"/>
+      <x:c r="I204"/>
+      <x:c r="J204"/>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="1" t="str">
@@ -5260,6 +6016,10 @@
       <x:c r="H205" s="1" t="str">
         <x:v>Pause at the top.</x:v>
       </x:c>
+      <x:c r="I205" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J205" t="str"/>
     </x:row>
     <x:row r="206" ht="70" customHeight="1">
       <x:c r="A206" s="5" t="str">
@@ -5284,6 +6044,10 @@
         <x:v>Stand tall, lift one knee to 90 degrees, then straighten your leg.</x:v>
       </x:c>
       <x:c r="H206" s="5" t="str"/>
+      <x:c r="I206" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J206" t="str"/>
     </x:row>
     <x:row r="207" ht="70" customHeight="1">
       <x:c r="A207" s="5" t="str">
@@ -5310,6 +6074,8 @@
       <x:c r="H207" s="5" t="str">
         <x:v>Keep the chest open and hold.</x:v>
       </x:c>
+      <x:c r="I207"/>
+      <x:c r="J207"/>
     </x:row>
     <x:row r="208" ht="70" customHeight="1">
       <x:c r="A208" s="5" t="str">
@@ -5336,6 +6102,8 @@
       <x:c r="H208" s="5" t="str">
         <x:v>Don't round the spine.</x:v>
       </x:c>
+      <x:c r="I208"/>
+      <x:c r="J208"/>
     </x:row>
     <x:row r="209" ht="70" customHeight="1">
       <x:c r="A209" s="5" t="str">
@@ -5362,6 +6130,12 @@
       <x:c r="H209" s="5" t="str">
         <x:v>Keep the hips square and finish without arching the lower back.</x:v>
       </x:c>
+      <x:c r="I209" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J209" t="str">
+        <x:v>frontal, transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="210" ht="70" customHeight="1">
       <x:c r="A210" s="5" t="str">
@@ -5388,6 +6162,12 @@
       <x:c r="H210" s="5" t="str">
         <x:v>Keep the hips square and avoid hanging through the lower back.</x:v>
       </x:c>
+      <x:c r="I210" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J210" t="str">
+        <x:v>frontal, transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="211" ht="70" customHeight="1">
       <x:c r="A211" s="5" t="str">
@@ -5414,6 +6194,10 @@
       <x:c r="H211" s="5" t="str">
         <x:v>Keep knees, hips, and shoulders in one straight line.</x:v>
       </x:c>
+      <x:c r="I211" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J211" t="str"/>
     </x:row>
     <x:row r="212" ht="70" customHeight="1">
       <x:c r="A212" s="5" t="str">
@@ -5438,6 +6222,8 @@
         <x:v>Load the outside hip, rotate hard, and throw through the wall.</x:v>
       </x:c>
       <x:c r="H212" s="5" t="str"/>
+      <x:c r="I212"/>
+      <x:c r="J212"/>
     </x:row>
     <x:row r="213" ht="70" customHeight="1">
       <x:c r="A213" s="5" t="str">
@@ -5464,6 +6250,8 @@
       <x:c r="H213" s="5" t="str">
         <x:v>Finish athletically with the hips and knees softly bent.</x:v>
       </x:c>
+      <x:c r="I213"/>
+      <x:c r="J213"/>
     </x:row>
     <x:row r="214" ht="70" customHeight="1">
       <x:c r="A214" s="5" t="str">
@@ -5490,6 +6278,8 @@
       <x:c r="H214" s="5" t="str">
         <x:v>Reset before each explosive repetition.</x:v>
       </x:c>
+      <x:c r="I214"/>
+      <x:c r="J214"/>
     </x:row>
     <x:row r="215" ht="70" customHeight="1">
       <x:c r="A215" s="5" t="str">
@@ -5516,6 +6306,8 @@
       <x:c r="H215" s="5" t="str">
         <x:v>Push knees over toes and keep your torso tall.</x:v>
       </x:c>
+      <x:c r="I215"/>
+      <x:c r="J215"/>
     </x:row>
     <x:row r="216" ht="70" customHeight="1">
       <x:c r="A216" s="5" t="str">
@@ -5542,6 +6334,8 @@
       <x:c r="H216" s="5" t="str">
         <x:v>Sink your chest without arching through the lower back.</x:v>
       </x:c>
+      <x:c r="I216"/>
+      <x:c r="J216"/>
     </x:row>
     <x:row r="217" ht="90" customHeight="1">
       <x:c r="A217" s="5" t="str">
@@ -5568,6 +6362,8 @@
       <x:c r="H217" s="5" t="str">
         <x:v>Stop at a mild stretch behind the shoulder, never the front.</x:v>
       </x:c>
+      <x:c r="I217"/>
+      <x:c r="J217"/>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="5" t="str">
@@ -5594,6 +6390,8 @@
       <x:c r="H218" s="5" t="str">
         <x:v>Keep ribs tucked and avoid arching through the lower back.</x:v>
       </x:c>
+      <x:c r="I218"/>
+      <x:c r="J218"/>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="5" t="str">
@@ -5620,6 +6418,12 @@
       <x:c r="H219" s="5" t="str">
         <x:v>Lower under control until your elbows fully straighten.</x:v>
       </x:c>
+      <x:c r="I219" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J219" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="220" ht="72" customHeight="1">
       <x:c r="A220" s="5" t="str">
@@ -5646,6 +6450,12 @@
       <x:c r="H220" s="5" t="str">
         <x:v>Press away without letting your hips sag or shoulders shrug.</x:v>
       </x:c>
+      <x:c r="I220" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J220" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="221" ht="72" customHeight="1">
       <x:c r="A221" s="5" t="str">
@@ -5672,6 +6482,8 @@
       <x:c r="H221" s="5" t="str">
         <x:v>Land quietly, absorb through the hip, and hold your balance.</x:v>
       </x:c>
+      <x:c r="I221"/>
+      <x:c r="J221"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Raa44463d67934fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Rdc46445d78374de4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6485,6 +6485,36 @@
       <x:c r="I221"/>
       <x:c r="J221"/>
     </x:row>
+    <x:row r="222" ht="72" customHeight="1">
+      <x:c r="A222" s="5" t="str">
+        <x:v>Shoulder health</x:v>
+      </x:c>
+      <x:c r="B222" s="5" t="str">
+        <x:v>Banded 90/90 External Rotation</x:v>
+      </x:c>
+      <x:c r="C222" s="5" t="str">
+        <x:v>Shoulders</x:v>
+      </x:c>
+      <x:c r="D222" s="5" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E222" s="5" t="str">
+        <x:v>everyone</x:v>
+      </x:c>
+      <x:c r="F222" s="5" t="str">
+        <x:v>Band resistance. 2 × 15–20 per arm with 20 seconds rest. Automatic in Shoulder health and upper-body warm-up slots; manual Add/Swap; not automatic in Primer. All phases and suitable at G-1 when pain-free.</x:v>
+      </x:c>
+      <x:c r="G222" s="5" t="str">
+        <x:v>Keep your elbow level with your shoulder and rotate your forearm upward.</x:v>
+      </x:c>
+      <x:c r="H222" s="5" t="str">
+        <x:v>Keep ribs down; avoid shrugging or forcing the range.</x:v>
+      </x:c>
+      <x:c r="I222" s="5" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J222" s="5"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Rdc46445d78374de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Rc12a52bbaf874db2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -73,7 +73,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0"/>
@@ -81,6 +81,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -6515,6 +6518,36 @@
       </x:c>
       <x:c r="J222" s="5"/>
     </x:row>
+    <x:row r="223" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A223" s="5" t="str">
+        <x:v>Accessories lower</x:v>
+      </x:c>
+      <x:c r="B223" s="5" t="str">
+        <x:v>T-Bar Tib Raises</x:v>
+      </x:c>
+      <x:c r="C223" s="5" t="str">
+        <x:v>Calves</x:v>
+      </x:c>
+      <x:c r="D223" s="5" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E223" s="5" t="str">
+        <x:v>everyone</x:v>
+      </x:c>
+      <x:c r="F223" s="5" t="str">
+        <x:v>Tibialis anterior (shin). Requires a tib bar and compatible plates. Uses the Tib Raises dose: 2 × 15–20 reps with 30 seconds rest. Begin empty or light, record total external load, and retain full ankle range. Automatic progression from Tib Raises when available; manual Add/Swap. All phases; familiar light loading is suitable at G-1.</x:v>
+      </x:c>
+      <x:c r="G223" s="5" t="str">
+        <x:v>Pull your toes toward your shins through the full range.</x:v>
+      </x:c>
+      <x:c r="H223" s="5" t="str">
+        <x:v>Keep knees still, pause at the top, and lower under control.</x:v>
+      </x:c>
+      <x:c r="I223" s="6" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J223" s="6"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="Rdc46445d78374de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="R1592cfa65e4f47f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1504,8 +1504,12 @@
       <x:c r="H41" s="1" t="str">
         <x:v>Full lockout, reset quickly.</x:v>
       </x:c>
-      <x:c r="I41"/>
-      <x:c r="J41"/>
+      <x:c r="I41" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="1" t="str">
@@ -3896,8 +3900,12 @@
         <x:v>dead hang from bar and relax, pull yourself higher only using your shoulder blades, don't bend arms</x:v>
       </x:c>
       <x:c r="H124" s="1" t="str"/>
-      <x:c r="I124"/>
-      <x:c r="J124"/>
+      <x:c r="I124" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J124" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="1" t="str">
@@ -5798,8 +5806,10 @@
       <x:c r="H197" t="str">
         <x:v>Stop if reps get slow.</x:v>
       </x:c>
-      <x:c r="I197"/>
-      <x:c r="J197"/>
+      <x:c r="I197" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J197" t="str"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="1" t="str">
@@ -5824,8 +5834,10 @@
         <x:v>Stand tall, jump and then bounce off the balls of your feet.</x:v>
       </x:c>
       <x:c r="H198" s="1" t="str"/>
-      <x:c r="I198"/>
-      <x:c r="J198"/>
+      <x:c r="I198" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J198" t="str"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="1" t="str">
@@ -5850,8 +5862,12 @@
         <x:v>Jump off outside leg to the side, turn in air and land in a squat.</x:v>
       </x:c>
       <x:c r="H199" s="1" t="str"/>
-      <x:c r="I199"/>
-      <x:c r="J199"/>
+      <x:c r="I199" t="str">
+        <x:v>frontal</x:v>
+      </x:c>
+      <x:c r="J199" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="1" t="str">
@@ -5876,8 +5892,10 @@
         <x:v>Start in kneeling position, jump onto feet, land in a squat.</x:v>
       </x:c>
       <x:c r="H200" s="1" t="str"/>
-      <x:c r="I200"/>
-      <x:c r="J200"/>
+      <x:c r="I200" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J200" t="str"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="1" t="str">
@@ -5934,8 +5952,12 @@
       <x:c r="H202" s="1" t="str">
         <x:v>Stop when reps slow. Sore wrists? Elevate hands on box.</x:v>
       </x:c>
-      <x:c r="I202"/>
-      <x:c r="J202"/>
+      <x:c r="I202" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J202" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="1" t="str">
@@ -6222,8 +6244,12 @@
         <x:v>Load the outside hip, rotate hard, and throw through the wall.</x:v>
       </x:c>
       <x:c r="H212" s="5" t="str"/>
-      <x:c r="I212"/>
-      <x:c r="J212"/>
+      <x:c r="I212" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J212" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="213" ht="70" customHeight="1">
       <x:c r="A213" s="5" t="str">
@@ -6250,8 +6276,10 @@
       <x:c r="H213" s="5" t="str">
         <x:v>Finish athletically with the hips and knees softly bent.</x:v>
       </x:c>
-      <x:c r="I213"/>
-      <x:c r="J213"/>
+      <x:c r="I213" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J213" t="str"/>
     </x:row>
     <x:row r="214" ht="70" customHeight="1">
       <x:c r="A214" s="5" t="str">
@@ -6278,8 +6306,12 @@
       <x:c r="H214" s="5" t="str">
         <x:v>Reset before each explosive repetition.</x:v>
       </x:c>
-      <x:c r="I214"/>
-      <x:c r="J214"/>
+      <x:c r="I214" t="str">
+        <x:v>transverse</x:v>
+      </x:c>
+      <x:c r="J214" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
     </x:row>
     <x:row r="215" ht="70" customHeight="1">
       <x:c r="A215" s="5" t="str">
@@ -6482,8 +6514,12 @@
       <x:c r="H221" s="5" t="str">
         <x:v>Land quietly, absorb through the hip, and hold your balance.</x:v>
       </x:c>
-      <x:c r="I221"/>
-      <x:c r="J221"/>
+      <x:c r="I221" t="str">
+        <x:v>sagittal</x:v>
+      </x:c>
+      <x:c r="J221" t="str">
+        <x:v>frontal, transverse</x:v>
+      </x:c>
     </x:row>
     <x:row r="222" ht="72" customHeight="1">
       <x:c r="A222" s="5" t="str">

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="R1592cfa65e4f47f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" r:id="R1436b8cd7dc548a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -383,6 +383,7 @@
     <x:col min="8" max="8" width="60" customWidth="1"/>
     <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -402,6 +403,9 @@
       <x:c r="J1" s="5" t="str">
         <x:v>Blank = unanswered</x:v>
       </x:c>
+      <x:c r="K1" s="5" t="str">
+        <x:v>ACCESSORY AFFINITY — 2026-09-02</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="1" t="str">
@@ -420,6 +424,9 @@
       <x:c r="J2" s="5" t="str">
         <x:v>multiplanar · not_applicable</x:v>
       </x:c>
+      <x:c r="K2" s="5" t="str">
+        <x:v>push · pull · both</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1" t="str">
@@ -434,6 +441,7 @@
       <x:c r="H3"/>
       <x:c r="I3"/>
       <x:c r="J3"/>
+      <x:c r="K3" s="5"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1" t="str">
@@ -448,6 +456,7 @@
       <x:c r="H4"/>
       <x:c r="I4"/>
       <x:c r="J4"/>
+      <x:c r="K4" s="5"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
@@ -462,6 +471,7 @@
       <x:c r="H5"/>
       <x:c r="I5"/>
       <x:c r="J5"/>
+      <x:c r="K5" s="5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="2" t="str">
@@ -494,6 +504,9 @@
       <x:c r="J6" s="5" t="str">
         <x:v>Secondary Plane(s)</x:v>
       </x:c>
+      <x:c r="K6" s="5" t="str">
+        <x:v>Accessory Affinity</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="1" t="str">
@@ -522,6 +535,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J7" t="str"/>
+      <x:c r="K7" s="5"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="1" t="str">
@@ -552,6 +566,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J8" t="str"/>
+      <x:c r="K8" s="5"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="1" t="str">
@@ -580,6 +595,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J9" t="str"/>
+      <x:c r="K9" s="5"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="1" t="str">
@@ -606,6 +622,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J10" t="str"/>
+      <x:c r="K10" s="5"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="1" t="str">
@@ -636,6 +653,7 @@
       <x:c r="J11" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K11" s="5"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="1" t="str">
@@ -666,6 +684,7 @@
       <x:c r="J12" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K12" s="5"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="1" t="str">
@@ -696,6 +715,7 @@
       <x:c r="J13" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K13" s="5"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="1" t="str">
@@ -726,6 +746,7 @@
       <x:c r="J14" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K14" s="5"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="1" t="str">
@@ -754,6 +775,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J15" t="str"/>
+      <x:c r="K15" s="5"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="1" t="str">
@@ -782,6 +804,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J16" t="str"/>
+      <x:c r="K16" s="5"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="1" t="str">
@@ -810,6 +833,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J17" t="str"/>
+      <x:c r="K17" s="5"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="1" t="str">
@@ -840,6 +864,7 @@
       <x:c r="J18" t="str">
         <x:v>frontal, transverse</x:v>
       </x:c>
+      <x:c r="K18" s="5"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="1" t="str">
@@ -864,6 +889,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J19" t="str"/>
+      <x:c r="K19" s="5"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="1" t="str">
@@ -894,6 +920,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J20" t="str"/>
+      <x:c r="K20" s="5"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="1" t="str">
@@ -922,6 +949,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J21" t="str"/>
+      <x:c r="K21" s="5"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="1" t="str">
@@ -952,6 +980,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J22" t="str"/>
+      <x:c r="K22" s="5"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="1" t="str">
@@ -982,6 +1011,7 @@
       <x:c r="J23" t="str">
         <x:v>frontal, transverse</x:v>
       </x:c>
+      <x:c r="K23" s="5"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="1" t="str">
@@ -1010,6 +1040,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J24" t="str"/>
+      <x:c r="K24" s="5"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="1" t="str">
@@ -1038,6 +1069,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J25" t="str"/>
+      <x:c r="K25" s="5"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="1" t="str">
@@ -1064,6 +1096,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J26" t="str"/>
+      <x:c r="K26" s="5"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="1" t="str">
@@ -1092,6 +1125,7 @@
         <x:v>transverse</x:v>
       </x:c>
       <x:c r="J27" t="str"/>
+      <x:c r="K27" s="5"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="1" t="str">
@@ -1122,6 +1156,7 @@
       <x:c r="J28" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K28" s="5"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="1" t="str">
@@ -1152,6 +1187,7 @@
       <x:c r="J29" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K29" s="5"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="1" t="str">
@@ -1180,6 +1216,7 @@
         <x:v>transverse</x:v>
       </x:c>
       <x:c r="J30" t="str"/>
+      <x:c r="K30" s="5"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="1" t="str">
@@ -1210,6 +1247,7 @@
       <x:c r="J31" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K31" s="5"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="1" t="str">
@@ -1240,6 +1278,7 @@
       <x:c r="J32" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K32" s="5"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="1" t="str">
@@ -1268,6 +1307,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J33" t="str"/>
+      <x:c r="K33" s="5"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="1" t="str">
@@ -1298,6 +1338,7 @@
         <x:v>transverse</x:v>
       </x:c>
       <x:c r="J34" t="str"/>
+      <x:c r="K34" s="5"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="1" t="str">
@@ -1328,6 +1369,7 @@
         <x:v>transverse</x:v>
       </x:c>
       <x:c r="J35" t="str"/>
+      <x:c r="K35" s="5"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="1" t="str">
@@ -1358,6 +1400,7 @@
       <x:c r="J36" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K36" s="5"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="1" t="str">
@@ -1390,6 +1433,7 @@
       <x:c r="J37" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K37" s="5"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="1" t="str">
@@ -1420,6 +1464,7 @@
       <x:c r="J38" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K38" s="5"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="1" t="str">
@@ -1450,6 +1495,7 @@
       <x:c r="J39" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K39" s="5"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="1" t="str">
@@ -1480,6 +1526,7 @@
       <x:c r="J40" t="str">
         <x:v>transverse</x:v>
       </x:c>
+      <x:c r="K40" s="5"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="1" t="str">
@@ -1510,6 +1557,7 @@
       <x:c r="J41" t="str">
         <x:v>transverse</x:v>
       </x:c>
+      <x:c r="K41" s="5"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="1" t="str">
@@ -1542,6 +1590,7 @@
       <x:c r="J42" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K42" s="5"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="1" t="str">
@@ -1572,6 +1621,7 @@
       <x:c r="J43" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K43" s="5"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="1" t="str">
@@ -1604,6 +1654,7 @@
       <x:c r="J44" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K44" s="5"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="1" t="str">
@@ -1634,6 +1685,7 @@
       <x:c r="J45" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K45" s="5"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="1" t="str">
@@ -1664,6 +1716,7 @@
       <x:c r="J46" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K46" s="5"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="1" t="str">
@@ -1694,6 +1747,9 @@
       <x:c r="J47" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K47" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="1" t="str">
@@ -1722,6 +1778,9 @@
         <x:v>transverse</x:v>
       </x:c>
       <x:c r="J48" t="str"/>
+      <x:c r="K48" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="1" t="str">
@@ -1750,6 +1809,9 @@
         <x:v>transverse</x:v>
       </x:c>
       <x:c r="J49" t="str"/>
+      <x:c r="K49" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="1" t="str">
@@ -1780,6 +1842,7 @@
       <x:c r="J50" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K50" s="5"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="1" t="str">
@@ -1810,6 +1873,7 @@
       <x:c r="J51" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K51" s="5"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="1" t="str">
@@ -1840,6 +1904,7 @@
       <x:c r="J52" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K52" s="5"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="1" t="str">
@@ -1868,6 +1933,7 @@
       <x:c r="J53" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K53" s="5"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="1" t="str">
@@ -1900,6 +1966,7 @@
       <x:c r="J54" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K54" s="5"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="1" t="str">
@@ -1928,6 +1995,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J55" t="str"/>
+      <x:c r="K55" s="5"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="1" t="str">
@@ -1956,6 +2024,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J56" t="str"/>
+      <x:c r="K56" s="5"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="1" t="str">
@@ -1984,6 +2053,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J57" t="str"/>
+      <x:c r="K57" s="5"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="1" t="str">
@@ -2016,6 +2086,7 @@
       <x:c r="J58" t="str">
         <x:v>transverse</x:v>
       </x:c>
+      <x:c r="K58" s="5"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="1" t="str">
@@ -2048,6 +2119,7 @@
       <x:c r="J59" t="str">
         <x:v>frontal, transverse</x:v>
       </x:c>
+      <x:c r="K59" s="5"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="1" t="str">
@@ -2078,6 +2150,7 @@
       <x:c r="J60" t="str">
         <x:v>frontal, transverse</x:v>
       </x:c>
+      <x:c r="K60" s="5"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="1" t="str">
@@ -2108,6 +2181,7 @@
       <x:c r="J61" t="str">
         <x:v>transverse</x:v>
       </x:c>
+      <x:c r="K61" s="5"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="1" t="str">
@@ -2138,6 +2212,7 @@
       <x:c r="J62" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K62" s="5"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="1" t="str">
@@ -2168,6 +2243,7 @@
       <x:c r="J63" t="str">
         <x:v>frontal, transverse</x:v>
       </x:c>
+      <x:c r="K63" s="5"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="1" t="str">
@@ -2196,6 +2272,9 @@
         <x:v>frontal</x:v>
       </x:c>
       <x:c r="J64" t="str"/>
+      <x:c r="K64" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="1" t="str">
@@ -2226,6 +2305,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J65" t="str"/>
+      <x:c r="K65" s="5" t="str">
+        <x:v>push</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="1" t="str">
@@ -2254,6 +2336,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J66" t="str"/>
+      <x:c r="K66" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="1" t="str">
@@ -2282,6 +2367,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J67" t="str"/>
+      <x:c r="K67" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="1" t="str">
@@ -2310,6 +2398,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J68" t="str"/>
+      <x:c r="K68" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="1" t="str">
@@ -2338,6 +2429,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J69" t="str"/>
+      <x:c r="K69" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="1" t="str">
@@ -2366,6 +2460,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J70" t="str"/>
+      <x:c r="K70" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="1" t="str">
@@ -2396,6 +2493,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J71" t="str"/>
+      <x:c r="K71" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="1" t="str">
@@ -2424,6 +2524,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J72" t="str"/>
+      <x:c r="K72" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="1" t="str">
@@ -2452,6 +2555,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J73" t="str"/>
+      <x:c r="K73" s="5" t="str">
+        <x:v>push</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="1" t="str">
@@ -2480,6 +2586,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J74" t="str"/>
+      <x:c r="K74" s="5" t="str">
+        <x:v>push</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="1" t="str">
@@ -2508,6 +2617,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J75" t="str"/>
+      <x:c r="K75" s="5" t="str">
+        <x:v>push</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="1" t="str">
@@ -2538,6 +2650,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J76" t="str"/>
+      <x:c r="K76" s="5" t="str">
+        <x:v>push</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="1" t="str">
@@ -2566,6 +2681,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J77" t="str"/>
+      <x:c r="K77" s="5" t="str">
+        <x:v>push</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="1" t="str">
@@ -2594,6 +2712,9 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J78" t="str"/>
+      <x:c r="K78" s="5" t="str">
+        <x:v>push</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="1" t="str">
@@ -2622,6 +2743,9 @@
         <x:v>frontal</x:v>
       </x:c>
       <x:c r="J79" t="str"/>
+      <x:c r="K79" s="5" t="str">
+        <x:v>push</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="1" t="str">
@@ -2652,6 +2776,9 @@
       <x:c r="J80" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K80" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="1" t="str">
@@ -2680,6 +2807,9 @@
         <x:v>frontal</x:v>
       </x:c>
       <x:c r="J81" t="str"/>
+      <x:c r="K81" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="1" t="str">
@@ -2710,6 +2840,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J82" t="str"/>
+      <x:c r="K82" s="5"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="1" t="str">
@@ -2736,6 +2867,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J83" t="str"/>
+      <x:c r="K83" s="5"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="1" t="str">
@@ -2762,6 +2894,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J84" t="str"/>
+      <x:c r="K84" s="5"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="1" t="str">
@@ -2790,6 +2923,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J85" t="str"/>
+      <x:c r="K85" s="5"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="1" t="str">
@@ -2820,6 +2954,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J86" t="str"/>
+      <x:c r="K86" s="5"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="1" t="str">
@@ -2848,6 +2983,7 @@
       <x:c r="J87" t="str">
         <x:v>frontal, transverse</x:v>
       </x:c>
+      <x:c r="K87" s="5"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="1" t="str">
@@ -2876,6 +3012,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J88" t="str"/>
+      <x:c r="K88" s="5"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="1" t="str">
@@ -2908,6 +3045,7 @@
       <x:c r="J89" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K89" s="5"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="str">
@@ -2938,6 +3076,9 @@
       <x:c r="J90" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K90" s="5" t="str">
+        <x:v>pull</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="1" t="str">
@@ -2968,6 +3109,7 @@
       <x:c r="J91" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K91" s="5"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="1" t="str">
@@ -2998,6 +3140,7 @@
       <x:c r="J92" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K92" s="5"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="1" t="str">
@@ -3028,6 +3171,7 @@
       <x:c r="J93" t="str">
         <x:v>transverse</x:v>
       </x:c>
+      <x:c r="K93" s="5"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="1" t="str">
@@ -3058,6 +3202,7 @@
       <x:c r="J94" t="str">
         <x:v>transverse</x:v>
       </x:c>
+      <x:c r="K94" s="5"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="1" t="str">
@@ -3086,6 +3231,7 @@
         <x:v>frontal</x:v>
       </x:c>
       <x:c r="J95" t="str"/>
+      <x:c r="K95" s="5"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="1" t="str">
@@ -3116,6 +3262,7 @@
       <x:c r="J96" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K96" s="5"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="1" t="str">
@@ -3146,6 +3293,7 @@
       <x:c r="J97" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K97" s="5"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="1" t="str">
@@ -3176,6 +3324,7 @@
       <x:c r="J98" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K98" s="5"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="1" t="str">
@@ -3204,6 +3353,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J99" t="str"/>
+      <x:c r="K99" s="5"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="1" t="str">
@@ -3230,6 +3380,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J100" t="str"/>
+      <x:c r="K100" s="5"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="1" t="str">
@@ -3258,6 +3409,7 @@
       <x:c r="J101" t="str">
         <x:v>frontal, transverse</x:v>
       </x:c>
+      <x:c r="K101" s="5"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="1" t="str">
@@ -3284,6 +3436,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J102" t="str"/>
+      <x:c r="K102" s="5"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="1" t="str">
@@ -3312,6 +3465,7 @@
       <x:c r="J103" t="str">
         <x:v>frontal</x:v>
       </x:c>
+      <x:c r="K103" s="5"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="1" t="str">
@@ -3340,6 +3494,7 @@
       <x:c r="J104" t="str">
         <x:v>transverse</x:v>
       </x:c>
+      <x:c r="K104" s="5"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="1" t="str">
@@ -3368,6 +3523,7 @@
         <x:v>transverse</x:v>
       </x:c>
       <x:c r="J105" t="str"/>
+      <x:c r="K105" s="5"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="1" t="str">
@@ -3398,6 +3554,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J106" t="str"/>
+      <x:c r="K106" s="5"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="1" t="str">
@@ -3426,6 +3583,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J107" t="str"/>
+      <x:c r="K107" s="5"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="1" t="str">
@@ -3454,6 +3612,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J108" t="str"/>
+      <x:c r="K108" s="5"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="1" t="str">
@@ -3482,6 +3641,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J109" t="str"/>
+      <x:c r="K109" s="5"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="1" t="str">
@@ -3512,6 +3672,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J110" t="str"/>
+      <x:c r="K110" s="5"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="1" t="str">
@@ -3540,6 +3701,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J111" t="str"/>
+      <x:c r="K111" s="5"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="1" t="str">
@@ -3572,6 +3734,7 @@
       <x:c r="J112" t="str">
         <x:v>transverse</x:v>
       </x:c>
+      <x:c r="K112" s="5"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="1" t="str">
@@ -3602,6 +3765,7 @@
       <x:c r="J113" t="str">
         <x:v>transverse</x:v>
       </x:c>
+      <x:c r="K113" s="5"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="1" t="str">
@@ -3630,6 +3794,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J114" t="str"/>
+      <x:c r="K114" s="5"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="1" t="str">
@@ -3656,6 +3821,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J115" t="str"/>
+      <x:c r="K115" s="5"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="1" t="str">
@@ -3682,6 +3848,7 @@
         <x:v>multiplanar</x:v>
       </x:c>
       <x:c r="J116" t="str"/>
+      <x:c r="K116" s="5"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="1" t="str">
@@ -3710,6 +3877,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J117" t="str"/>
+      <x:c r="K117" s="5"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="1" t="str">
@@ -3738,6 +3906,7 @@
       <x:c r="J118" t="str">
         <x:v>transverse</x:v>
       </x:c>
+      <x:c r="K118" s="5"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="1" t="str">
@@ -3768,6 +3937,7 @@
       <x:c r="J119" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K119" s="5"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="1" t="str">
@@ -3798,6 +3968,7 @@
       <x:c r="J120" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K120" s="5"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="1" t="str">
@@ -3824,6 +3995,7 @@
       </x:c>
       <x:c r="I121"/>
       <x:c r="J121"/>
+      <x:c r="K121" s="5"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="1" t="str">
@@ -3852,6 +4024,7 @@
       </x:c>
       <x:c r="I122"/>
       <x:c r="J122"/>
+      <x:c r="K122" s="5"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="1" t="str">
@@ -3878,6 +4051,7 @@
       </x:c>
       <x:c r="I123"/>
       <x:c r="J123"/>
+      <x:c r="K123" s="5"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="1" t="str">
@@ -3906,6 +4080,7 @@
       <x:c r="J124" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K124" s="5"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="1" t="str">
@@ -3934,6 +4109,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J125" t="str"/>
+      <x:c r="K125" s="5"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="1" t="str">
@@ -3960,6 +4136,7 @@
       </x:c>
       <x:c r="I126"/>
       <x:c r="J126"/>
+      <x:c r="K126" s="5"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="1" t="str">
@@ -3986,6 +4163,7 @@
       </x:c>
       <x:c r="I127"/>
       <x:c r="J127"/>
+      <x:c r="K127" s="5"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="1" t="str">
@@ -4012,6 +4190,7 @@
       </x:c>
       <x:c r="I128"/>
       <x:c r="J128"/>
+      <x:c r="K128" s="5"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="1" t="str">
@@ -4038,6 +4217,7 @@
       </x:c>
       <x:c r="I129"/>
       <x:c r="J129"/>
+      <x:c r="K129" s="5"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="1" t="str">
@@ -4064,6 +4244,7 @@
       </x:c>
       <x:c r="I130"/>
       <x:c r="J130"/>
+      <x:c r="K130" s="5"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="1" t="str">
@@ -4090,6 +4271,7 @@
       </x:c>
       <x:c r="I131"/>
       <x:c r="J131"/>
+      <x:c r="K131" s="5"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="1" t="str">
@@ -4116,6 +4298,7 @@
       </x:c>
       <x:c r="I132"/>
       <x:c r="J132"/>
+      <x:c r="K132" s="5"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="1" t="str">
@@ -4142,6 +4325,7 @@
       </x:c>
       <x:c r="I133"/>
       <x:c r="J133"/>
+      <x:c r="K133" s="5"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="1" t="str">
@@ -4168,6 +4352,7 @@
       </x:c>
       <x:c r="I134"/>
       <x:c r="J134"/>
+      <x:c r="K134" s="5"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="1" t="str">
@@ -4194,6 +4379,7 @@
       </x:c>
       <x:c r="I135"/>
       <x:c r="J135"/>
+      <x:c r="K135" s="5"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="1" t="str">
@@ -4220,6 +4406,7 @@
       </x:c>
       <x:c r="I136"/>
       <x:c r="J136"/>
+      <x:c r="K136" s="5"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="1" t="str">
@@ -4246,6 +4433,7 @@
       </x:c>
       <x:c r="I137"/>
       <x:c r="J137"/>
+      <x:c r="K137" s="5"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="1" t="str">
@@ -4272,6 +4460,7 @@
       </x:c>
       <x:c r="I138"/>
       <x:c r="J138"/>
+      <x:c r="K138" s="5"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="1" t="str">
@@ -4298,6 +4487,7 @@
       </x:c>
       <x:c r="I139"/>
       <x:c r="J139"/>
+      <x:c r="K139" s="5"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="1" t="str">
@@ -4324,6 +4514,7 @@
       </x:c>
       <x:c r="I140"/>
       <x:c r="J140"/>
+      <x:c r="K140" s="5"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="1" t="str">
@@ -4350,6 +4541,7 @@
       </x:c>
       <x:c r="I141"/>
       <x:c r="J141"/>
+      <x:c r="K141" s="5"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="1" t="str">
@@ -4376,6 +4568,7 @@
       </x:c>
       <x:c r="I142"/>
       <x:c r="J142"/>
+      <x:c r="K142" s="5"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="1" t="str">
@@ -4404,6 +4597,7 @@
       </x:c>
       <x:c r="I143"/>
       <x:c r="J143"/>
+      <x:c r="K143" s="5"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="1" t="str">
@@ -4430,6 +4624,7 @@
       </x:c>
       <x:c r="I144"/>
       <x:c r="J144"/>
+      <x:c r="K144" s="5"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="1" t="str">
@@ -4456,6 +4651,7 @@
       <x:c r="H145" s="1" t="str"/>
       <x:c r="I145"/>
       <x:c r="J145"/>
+      <x:c r="K145" s="5"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="1" t="str">
@@ -4482,6 +4678,7 @@
       <x:c r="H146" s="1" t="str"/>
       <x:c r="I146"/>
       <x:c r="J146"/>
+      <x:c r="K146" s="5"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="1" t="str">
@@ -4506,6 +4703,7 @@
       <x:c r="H147" s="1" t="str"/>
       <x:c r="I147"/>
       <x:c r="J147"/>
+      <x:c r="K147" s="5"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="1" t="str">
@@ -4530,6 +4728,7 @@
       <x:c r="H148" s="1" t="str"/>
       <x:c r="I148"/>
       <x:c r="J148"/>
+      <x:c r="K148" s="5"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="1" t="str">
@@ -4554,6 +4753,7 @@
       <x:c r="H149" s="1" t="str"/>
       <x:c r="I149"/>
       <x:c r="J149"/>
+      <x:c r="K149" s="5"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="1" t="str">
@@ -4578,6 +4778,7 @@
       <x:c r="H150" s="1" t="str"/>
       <x:c r="I150"/>
       <x:c r="J150"/>
+      <x:c r="K150" s="5"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="1" t="str">
@@ -4602,6 +4803,7 @@
       <x:c r="H151" s="1" t="str"/>
       <x:c r="I151"/>
       <x:c r="J151"/>
+      <x:c r="K151" s="5"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="1" t="str">
@@ -4628,6 +4830,7 @@
       </x:c>
       <x:c r="I152"/>
       <x:c r="J152"/>
+      <x:c r="K152" s="5"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="1" t="str">
@@ -4654,6 +4857,7 @@
       </x:c>
       <x:c r="I153"/>
       <x:c r="J153"/>
+      <x:c r="K153" s="5"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="1" t="str">
@@ -4680,6 +4884,7 @@
       </x:c>
       <x:c r="I154"/>
       <x:c r="J154"/>
+      <x:c r="K154" s="5"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="1" t="str">
@@ -4706,6 +4911,7 @@
       </x:c>
       <x:c r="I155"/>
       <x:c r="J155"/>
+      <x:c r="K155" s="5"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="1" t="str">
@@ -4732,6 +4938,7 @@
       </x:c>
       <x:c r="I156"/>
       <x:c r="J156"/>
+      <x:c r="K156" s="5"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="1" t="str">
@@ -4758,6 +4965,7 @@
       </x:c>
       <x:c r="I157"/>
       <x:c r="J157"/>
+      <x:c r="K157" s="5"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="1" t="str">
@@ -4784,6 +4992,7 @@
       </x:c>
       <x:c r="I158"/>
       <x:c r="J158"/>
+      <x:c r="K158" s="5"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="1" t="str">
@@ -4812,6 +5021,7 @@
       </x:c>
       <x:c r="I159"/>
       <x:c r="J159"/>
+      <x:c r="K159" s="5"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="1" t="str">
@@ -4840,6 +5050,7 @@
       </x:c>
       <x:c r="I160"/>
       <x:c r="J160"/>
+      <x:c r="K160" s="5"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="1" t="str">
@@ -4868,6 +5079,7 @@
       </x:c>
       <x:c r="I161"/>
       <x:c r="J161"/>
+      <x:c r="K161" s="5"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="1" t="str">
@@ -4894,6 +5106,7 @@
       <x:c r="H162" s="1" t="str"/>
       <x:c r="I162"/>
       <x:c r="J162"/>
+      <x:c r="K162" s="5"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="1" t="str">
@@ -4920,6 +5133,7 @@
       <x:c r="H163" s="1" t="str"/>
       <x:c r="I163"/>
       <x:c r="J163"/>
+      <x:c r="K163" s="5"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="1" t="str">
@@ -4946,6 +5160,7 @@
       <x:c r="H164" s="1" t="str"/>
       <x:c r="I164"/>
       <x:c r="J164"/>
+      <x:c r="K164" s="5"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="1" t="str">
@@ -4972,6 +5187,7 @@
       <x:c r="H165" s="1" t="str"/>
       <x:c r="I165"/>
       <x:c r="J165"/>
+      <x:c r="K165" s="5"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="1" t="str">
@@ -4998,6 +5214,7 @@
       <x:c r="H166" s="1" t="str"/>
       <x:c r="I166"/>
       <x:c r="J166"/>
+      <x:c r="K166" s="5"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="1" t="str">
@@ -5024,6 +5241,7 @@
       <x:c r="H167" s="1" t="str"/>
       <x:c r="I167"/>
       <x:c r="J167"/>
+      <x:c r="K167" s="5"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="1" t="str">
@@ -5050,6 +5268,7 @@
       <x:c r="H168" s="1" t="str"/>
       <x:c r="I168"/>
       <x:c r="J168"/>
+      <x:c r="K168" s="5"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="1" t="str">
@@ -5078,6 +5297,7 @@
       </x:c>
       <x:c r="I169"/>
       <x:c r="J169"/>
+      <x:c r="K169" s="5"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="1" t="str">
@@ -5104,6 +5324,7 @@
       <x:c r="H170" s="1" t="str"/>
       <x:c r="I170"/>
       <x:c r="J170"/>
+      <x:c r="K170" s="5"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="1" t="str">
@@ -5130,6 +5351,7 @@
       <x:c r="H171" s="1" t="str"/>
       <x:c r="I171"/>
       <x:c r="J171"/>
+      <x:c r="K171" s="5"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="1" t="str">
@@ -5156,6 +5378,7 @@
       <x:c r="H172" s="1" t="str"/>
       <x:c r="I172"/>
       <x:c r="J172"/>
+      <x:c r="K172" s="5"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="1" t="str">
@@ -5182,6 +5405,7 @@
       <x:c r="H173" s="1" t="str"/>
       <x:c r="I173"/>
       <x:c r="J173"/>
+      <x:c r="K173" s="5"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="1" t="str">
@@ -5208,6 +5432,7 @@
       <x:c r="H174" s="1" t="str"/>
       <x:c r="I174"/>
       <x:c r="J174"/>
+      <x:c r="K174" s="5"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="1" t="str">
@@ -5234,6 +5459,7 @@
       <x:c r="H175" s="1" t="str"/>
       <x:c r="I175"/>
       <x:c r="J175"/>
+      <x:c r="K175" s="5"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="1" t="str">
@@ -5260,6 +5486,7 @@
       <x:c r="H176" s="1" t="str"/>
       <x:c r="I176"/>
       <x:c r="J176"/>
+      <x:c r="K176" s="5"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="1" t="str">
@@ -5286,6 +5513,7 @@
       <x:c r="H177" s="1" t="str"/>
       <x:c r="I177"/>
       <x:c r="J177"/>
+      <x:c r="K177" s="5"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="1" t="str">
@@ -5312,6 +5540,7 @@
       <x:c r="H178" s="1" t="str"/>
       <x:c r="I178"/>
       <x:c r="J178"/>
+      <x:c r="K178" s="5"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="1" t="str">
@@ -5340,6 +5569,7 @@
       </x:c>
       <x:c r="I179"/>
       <x:c r="J179"/>
+      <x:c r="K179" s="5"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="1" t="str">
@@ -5366,6 +5596,7 @@
       <x:c r="H180" s="1" t="str"/>
       <x:c r="I180"/>
       <x:c r="J180"/>
+      <x:c r="K180" s="5"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="1" t="str">
@@ -5392,6 +5623,7 @@
       <x:c r="H181" s="1" t="str"/>
       <x:c r="I181"/>
       <x:c r="J181"/>
+      <x:c r="K181" s="5"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="1" t="str">
@@ -5418,6 +5650,7 @@
       <x:c r="H182" s="1" t="str"/>
       <x:c r="I182"/>
       <x:c r="J182"/>
+      <x:c r="K182" s="5"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="1" t="str">
@@ -5444,6 +5677,7 @@
       <x:c r="H183" s="1" t="str"/>
       <x:c r="I183"/>
       <x:c r="J183"/>
+      <x:c r="K183" s="5"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="1" t="str">
@@ -5470,6 +5704,7 @@
       <x:c r="H184" s="1" t="str"/>
       <x:c r="I184"/>
       <x:c r="J184"/>
+      <x:c r="K184" s="5"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="1" t="str">
@@ -5498,6 +5733,7 @@
       </x:c>
       <x:c r="I185"/>
       <x:c r="J185"/>
+      <x:c r="K185" s="5"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="1" t="str">
@@ -5526,6 +5762,7 @@
       </x:c>
       <x:c r="I186"/>
       <x:c r="J186"/>
+      <x:c r="K186" s="5"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="1" t="str">
@@ -5552,6 +5789,7 @@
       <x:c r="H187" s="1" t="str"/>
       <x:c r="I187"/>
       <x:c r="J187"/>
+      <x:c r="K187" s="5"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="1" t="str">
@@ -5578,6 +5816,7 @@
       <x:c r="H188" s="1" t="str"/>
       <x:c r="I188"/>
       <x:c r="J188"/>
+      <x:c r="K188" s="5"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="1" t="str">
@@ -5606,6 +5845,7 @@
       </x:c>
       <x:c r="I189"/>
       <x:c r="J189"/>
+      <x:c r="K189" s="5"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="1" t="str">
@@ -5634,6 +5874,7 @@
       </x:c>
       <x:c r="I190"/>
       <x:c r="J190"/>
+      <x:c r="K190" s="5"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="1" t="str">
@@ -5662,6 +5903,7 @@
       </x:c>
       <x:c r="I191"/>
       <x:c r="J191"/>
+      <x:c r="K191" s="5"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="1" t="str">
@@ -5690,6 +5932,7 @@
       </x:c>
       <x:c r="I192"/>
       <x:c r="J192"/>
+      <x:c r="K192" s="5"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="1" t="str">
@@ -5716,6 +5959,7 @@
       <x:c r="H193" s="1" t="str"/>
       <x:c r="I193"/>
       <x:c r="J193"/>
+      <x:c r="K193" s="5"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="1" t="str">
@@ -5744,6 +5988,7 @@
       </x:c>
       <x:c r="I194"/>
       <x:c r="J194"/>
+      <x:c r="K194" s="5"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="1" t="str">
@@ -5770,6 +6015,7 @@
       <x:c r="H195" s="1" t="str"/>
       <x:c r="I195"/>
       <x:c r="J195"/>
+      <x:c r="K195" s="5"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="1"/>
@@ -5782,6 +6028,7 @@
       <x:c r="H196"/>
       <x:c r="I196"/>
       <x:c r="J196"/>
+      <x:c r="K196" s="5"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" t="str">
@@ -5810,6 +6057,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J197" t="str"/>
+      <x:c r="K197" s="5"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="1" t="str">
@@ -5838,6 +6086,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J198" t="str"/>
+      <x:c r="K198" s="5"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="1" t="str">
@@ -5868,6 +6117,7 @@
       <x:c r="J199" t="str">
         <x:v>transverse</x:v>
       </x:c>
+      <x:c r="K199" s="5"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="1" t="str">
@@ -5896,6 +6146,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J200" t="str"/>
+      <x:c r="K200" s="5"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="1" t="str">
@@ -5928,6 +6179,7 @@
       <x:c r="J201" t="str">
         <x:v>frontal, transverse</x:v>
       </x:c>
+      <x:c r="K201" s="5"/>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="1" t="str">
@@ -5958,6 +6210,7 @@
       <x:c r="J202" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K202" s="5"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="1" t="str">
@@ -5986,6 +6239,7 @@
       </x:c>
       <x:c r="I203"/>
       <x:c r="J203"/>
+      <x:c r="K203" s="5"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="1" t="str">
@@ -6012,6 +6266,7 @@
       <x:c r="H204" s="1" t="str"/>
       <x:c r="I204"/>
       <x:c r="J204"/>
+      <x:c r="K204" s="5"/>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="1" t="str">
@@ -6042,6 +6297,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J205" t="str"/>
+      <x:c r="K205" s="5"/>
     </x:row>
     <x:row r="206" ht="70" customHeight="1">
       <x:c r="A206" s="5" t="str">
@@ -6070,6 +6326,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J206" t="str"/>
+      <x:c r="K206" s="5"/>
     </x:row>
     <x:row r="207" ht="70" customHeight="1">
       <x:c r="A207" s="5" t="str">
@@ -6098,6 +6355,7 @@
       </x:c>
       <x:c r="I207"/>
       <x:c r="J207"/>
+      <x:c r="K207" s="5"/>
     </x:row>
     <x:row r="208" ht="70" customHeight="1">
       <x:c r="A208" s="5" t="str">
@@ -6126,6 +6384,7 @@
       </x:c>
       <x:c r="I208"/>
       <x:c r="J208"/>
+      <x:c r="K208" s="5"/>
     </x:row>
     <x:row r="209" ht="70" customHeight="1">
       <x:c r="A209" s="5" t="str">
@@ -6158,6 +6417,7 @@
       <x:c r="J209" t="str">
         <x:v>frontal, transverse</x:v>
       </x:c>
+      <x:c r="K209" s="5"/>
     </x:row>
     <x:row r="210" ht="70" customHeight="1">
       <x:c r="A210" s="5" t="str">
@@ -6190,6 +6450,7 @@
       <x:c r="J210" t="str">
         <x:v>frontal, transverse</x:v>
       </x:c>
+      <x:c r="K210" s="5"/>
     </x:row>
     <x:row r="211" ht="70" customHeight="1">
       <x:c r="A211" s="5" t="str">
@@ -6220,6 +6481,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J211" t="str"/>
+      <x:c r="K211" s="5"/>
     </x:row>
     <x:row r="212" ht="70" customHeight="1">
       <x:c r="A212" s="5" t="str">
@@ -6250,6 +6512,7 @@
       <x:c r="J212" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K212" s="5"/>
     </x:row>
     <x:row r="213" ht="70" customHeight="1">
       <x:c r="A213" s="5" t="str">
@@ -6280,6 +6543,7 @@
         <x:v>sagittal</x:v>
       </x:c>
       <x:c r="J213" t="str"/>
+      <x:c r="K213" s="5"/>
     </x:row>
     <x:row r="214" ht="70" customHeight="1">
       <x:c r="A214" s="5" t="str">
@@ -6312,6 +6576,7 @@
       <x:c r="J214" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K214" s="5"/>
     </x:row>
     <x:row r="215" ht="70" customHeight="1">
       <x:c r="A215" s="5" t="str">
@@ -6340,6 +6605,7 @@
       </x:c>
       <x:c r="I215"/>
       <x:c r="J215"/>
+      <x:c r="K215" s="5"/>
     </x:row>
     <x:row r="216" ht="70" customHeight="1">
       <x:c r="A216" s="5" t="str">
@@ -6368,6 +6634,7 @@
       </x:c>
       <x:c r="I216"/>
       <x:c r="J216"/>
+      <x:c r="K216" s="5"/>
     </x:row>
     <x:row r="217" ht="90" customHeight="1">
       <x:c r="A217" s="5" t="str">
@@ -6396,6 +6663,7 @@
       </x:c>
       <x:c r="I217"/>
       <x:c r="J217"/>
+      <x:c r="K217" s="5"/>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="5" t="str">
@@ -6424,6 +6692,7 @@
       </x:c>
       <x:c r="I218"/>
       <x:c r="J218"/>
+      <x:c r="K218" s="5"/>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="5" t="str">
@@ -6456,6 +6725,7 @@
       <x:c r="J219" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K219" s="5"/>
     </x:row>
     <x:row r="220" ht="72" customHeight="1">
       <x:c r="A220" s="5" t="str">
@@ -6488,6 +6758,7 @@
       <x:c r="J220" t="str">
         <x:v>sagittal</x:v>
       </x:c>
+      <x:c r="K220" s="5"/>
     </x:row>
     <x:row r="221" ht="72" customHeight="1">
       <x:c r="A221" s="5" t="str">
@@ -6520,6 +6791,7 @@
       <x:c r="J221" t="str">
         <x:v>frontal, transverse</x:v>
       </x:c>
+      <x:c r="K221" s="5"/>
     </x:row>
     <x:row r="222" ht="72" customHeight="1">
       <x:c r="A222" s="5" t="str">
@@ -6550,6 +6822,7 @@
         <x:v>transverse</x:v>
       </x:c>
       <x:c r="J222" s="5"/>
+      <x:c r="K222" s="5"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Exercise Master" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise Master" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -374,7 +374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K223"/>
+  <dimension ref="A1:K224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -468,7 +468,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHANGE LOG — Sam 2026-07-27: MetCon row DELETED (the conditioning ruling retiring the name wins); Single-Arm Pulldown row ADDED (Lats / Upper back, Midline / everyone); 3 casing typos corrected as authorised edits (Suitcase Carry + Skull Crushers 'Everyone' -&gt; 'everyone', Chin-Up Negative (Slow) secondary 'midline' -&gt; 'Midline'). CHANGE LOG — 2026-07-28 cue reconciliation: renamed from MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx; primaryCue/secondaryCue columns added, making this the single authored source for coaching cues. 175 rows carry Sam-authored cues as shipped; 23 conditioning rows read "PENDING — Stage B" (unruled, NOT blessed — Sam 2026-07-28). Muscle/experience cells are untouched. CHANGE LOG — 2026-09-01 identity merge: Single-Arm Pulldown retired as a current row and retained only as a legacy read alias; cues, equipment, progression and history resolve to Single-Arm Lat Pulldown. CHANGE LOG — 2026-09-01: Seated Good Morning (Barbell) retired as a current row and retained only as legacy saved-data ingress. Seated Good Morning is the one identity; bodyweight is available to everyone, while dumbbell and barbell variants require 1+ years.; Sam 2026-09-02: SL 45° Back Extension Hold and Swiss Ball Hamstring Curl moved from Hamstring (light) into Lower prehab; the separate authored pool was retired.</t>
+          <t>CHANGE LOG — Sam 2026-07-27: MetCon row DELETED (the conditioning ruling retiring the name wins); Single-Arm Pulldown row ADDED (Lats / Upper back, Midline / everyone); 3 casing typos corrected as authorised edits (Suitcase Carry + Skull Crushers 'Everyone' -&gt; 'everyone', Chin-Up Negative (Slow) secondary 'midline' -&gt; 'Midline'). CHANGE LOG — 2026-07-28 cue reconciliation: renamed from MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx; primaryCue/secondaryCue columns added, making this the single authored source for coaching cues. 175 rows carry Sam-authored cues as shipped; 23 conditioning rows read "PENDING — Stage B" (unruled, NOT blessed — Sam 2026-07-28). Muscle/experience cells are untouched. CHANGE LOG — 2026-09-01 identity merge: Single-Arm Pulldown retired as a current row and retained only as a legacy read alias; cues, equipment, progression and history resolve to Single-Arm Lat Pulldown. CHANGE LOG — 2026-09-01: Seated Good Morning (Barbell) retired as a current row and retained only as legacy saved-data ingress. Seated Good Morning is the one identity; bodyweight is available to everyone, while dumbbell and barbell variants require 1+ years.; Sam 2026-09-02: SL 45° Back Extension Hold and Swiss Ball Hamstring Curl moved from Hamstring (light) into Lower prehab; the separate authored pool was retired. CHANGE LOG — Sam 2026-09-04 (R-368): B-Stance RDL ADDED to Lower hinge — "add this into the exercise list as well - so we have another single leg hip dominant lift". Third member of the single-leg hip group, which held only Single-Leg RDL and SL 45° Back Extension. Intake: docs/EXERCISE_INTAKE_B_STANCE_RDL_2026-09-04.md.</t>
         </is>
       </c>
       <c r="K5" s="5" t="n"/>
@@ -1309,40 +1309,44 @@
       <c r="K23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Lower hinge</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>Hip Thrusts</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>Glutes</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>Hamstrings, Low back</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="str"/>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>Drive through the heels, squeeze at the top.</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="inlineStr">
-        <is>
-          <t>Ribs down, no overextending.</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>B-Stance RDL</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Hamstrings, Glutes</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Low back</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Single-leg hip-dominant. Rear foot is a kickstand for balance only; the front leg does the work. Barbell or dumbbell. Repetitions are per side. Same sets, repetitions, rest, loading and progression as Single-Leg RDL, and the same season and game-day restrictions. Automatic programming and manual Add/Swap wherever Single-Leg RDL is eligible.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Load the front leg and push your hips straight back.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Keep hips square; use the rear foot only for balance.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1350,7 +1354,11 @@
           <t>sagittal</t>
         </is>
       </c>
-      <c r="K24" s="5" t="n"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>frontal, transverse</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1360,33 +1368,33 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Kettlebell Swings</t>
+          <t>Hip Thrusts</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Hamstrings</t>
+          <t>Glutes</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>Midline, Low back</t>
+          <t>Hamstrings, Low back</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F25" s="1" t="str"/>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>Snap the hips, KB should come back down fast.</t>
+          <t>Drive through the heels, squeeze at the top.</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>Power from hips, don’t lift with arms.</t>
+          <t>Ribs down, no overextending.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1404,31 +1412,35 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>Glute Bridge</t>
+          <t>Kettlebell Swings</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>Glutes</t>
+          <t>Glutes, Hamstrings</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings</t>
+          <t>Midline, Low back</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F26" s="1" t="str"/>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>Keep spine neutral, don’t arch low back, lift hips, squeeze glutes, add weight to hips if you can.</t>
-        </is>
-      </c>
-      <c r="H26" s="1" t="str"/>
+          <t>Snap the hips, KB should come back down fast.</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>Power from hips, don’t lift with arms.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>sagittal</t>
@@ -1439,43 +1451,39 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Upper push horizontal</t>
+          <t>Lower hinge</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Glute Bridge</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Chest</t>
+          <t>Glutes</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Shoulders</t>
+          <t>Hamstrings</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone (regression)</t>
         </is>
       </c>
       <c r="F27" s="1" t="str"/>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>Shoulder blades pinched, bend bar like snapping a twig, feet planted.</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>Bar to chest, press hard to lockout.</t>
-        </is>
-      </c>
+          <t>Keep spine neutral, don’t arch low back, lift hips, squeeze glutes, add weight to hips if you can.</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="str"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>transverse</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K27" s="5" t="n"/>
@@ -1488,17 +1496,17 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Incline Bench</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Chest, Shoulders</t>
+          <t>Chest</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>Triceps</t>
+          <t>Triceps, Shoulders</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -1509,22 +1517,17 @@
       <c r="F28" s="1" t="str"/>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>Set the blades on the incline.</t>
+          <t>Shoulder blades pinched, bend bar like snapping a twig, feet planted.</t>
         </is>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>Press through the palms.</t>
+          <t>Bar to chest, press hard to lockout.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>transverse</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>sagittal</t>
         </is>
       </c>
       <c r="K28" s="5" t="n"/>
@@ -1537,17 +1540,17 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Close Grip Bench</t>
+          <t>Incline Bench</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Chest</t>
+          <t>Chest, Shoulders</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Triceps</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
@@ -1558,12 +1561,12 @@
       <c r="F29" s="1" t="str"/>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>Hands at or inside shoulder width, elbows tight.</t>
+          <t>Set the blades on the incline.</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>Triceps do the work.</t>
+          <t>Press through the palms.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1586,38 +1589,43 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>DB Bench Press</t>
+          <t>Close Grip Bench</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>Chest</t>
+          <t>Triceps, Chest</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Shoulders</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F30" s="1" t="str"/>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>Shoulder blades set on the bench.</t>
+          <t>Hands at or inside shoulder width, elbows tight.</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>Control the dumbbells down and drive.</t>
+          <t>Triceps do the work.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>transverse</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K30" s="5" t="n"/>
@@ -1630,17 +1638,17 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Incline DB Bench</t>
+          <t>DB Bench Press</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Chest, Shoulders</t>
+          <t>Chest</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>Triceps</t>
+          <t>Triceps, Shoulders</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
@@ -1651,22 +1659,17 @@
       <c r="F31" s="1" t="str"/>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>Elbows at 45 degrees, full stretch at the bottom.</t>
+          <t>Shoulder blades set on the bench.</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>Drive up and together.</t>
+          <t>Control the dumbbells down and drive.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>transverse</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>sagittal</t>
         </is>
       </c>
       <c r="K31" s="5" t="n"/>
@@ -1679,33 +1682,33 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Push-ups</t>
+          <t>Incline DB Bench</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Chest</t>
+          <t>Chest, Shoulders</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Shoulders, Midline</t>
+          <t>Triceps</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F32" s="1" t="str"/>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>Body in a straight line, elbows at 45.</t>
+          <t>Elbows at 45 degrees, full stretch at the bottom.</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>Chest to floor, full lockout.</t>
+          <t>Drive up and together.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1728,36 +1731,41 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>Dips</t>
+          <t>Push-ups</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Chest, Triceps</t>
+          <t>Chest</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Triceps, Shoulders, Midline</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone (regression)</t>
         </is>
       </c>
       <c r="F33" s="1" t="str"/>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>Lean slightly forward, elbows back.</t>
+          <t>Body in a straight line, elbows at 45.</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>Control the descent.</t>
+          <t>Chest to floor, full lockout.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
+        <is>
+          <t>transverse</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>sagittal</t>
         </is>
@@ -1772,42 +1780,38 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>Single-Arm DB Bench Press</t>
+          <t>Dips</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Chest</t>
+          <t>Chest, Triceps</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Midline</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>anti-rotation control under unilateral load; low stability + caution lateWeek in the source tags.</t>
-        </is>
-      </c>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="str"/>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>Fight the rotation.</t>
+          <t>Lean slightly forward, elbows back.</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>Brace hard through the midline.</t>
+          <t>Control the descent.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>transverse</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K34" s="5" t="n"/>
@@ -1820,37 +1824,37 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>Single-Arm DB Floor Press</t>
+          <t>Single-Arm DB Bench Press</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Chest, Triceps</t>
+          <t>Chest</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Triceps, Midline</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>⚑ shorter ROM protects the shoulder vs. the bench variant, so this may be gentler than the sibling above — could be 'everyone'.</t>
+          <t>anti-rotation control under unilateral load; low stability + caution lateWeek in the source tags.</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>Brace the midline, press from the floor.</t>
+          <t>Fight the rotation.</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>Don't let the torso rotate.</t>
+          <t>Brace hard through the midline.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1863,22 +1867,22 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Upper push vertical</t>
+          <t>Upper push horizontal</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>Overhead Press</t>
+          <t>Single-Arm DB Floor Press</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Chest, Triceps</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Midline, Traps</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1886,25 +1890,24 @@
           <t>1+ years</t>
         </is>
       </c>
-      <c r="F36" s="1" t="str"/>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>⚑ shorter ROM protects the shoulder vs. the bench variant, so this may be gentler than the sibling above — could be 'everyone'.</t>
+        </is>
+      </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>Ribs down, bar finishes over the ears.</t>
+          <t>Brace the midline, press from the floor.</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>Press hard and finish strong.</t>
+          <t>Don't let the torso rotate.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>frontal</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>sagittal</t>
+          <t>transverse</t>
         </is>
       </c>
       <c r="K36" s="5" t="n"/>
@@ -1917,17 +1920,17 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Landmine Press</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Chest</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>Triceps</t>
+          <t>Triceps, Midline, Traps</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
@@ -1935,29 +1938,25 @@
           <t>1+ years</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>⚑ SAFE injury profile suggests this could reasonably be 'everyone'; not in the app's own beginner curriculum, so left at 1+ years.</t>
-        </is>
-      </c>
+      <c r="F37" s="1" t="str"/>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>Split stance, press at an angle, follow the arc.</t>
+          <t>Ribs down, bar finishes over the ears.</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>Stable base, strong finish.</t>
+          <t>Press hard and finish strong.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>frontal</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>frontal</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K37" s="5" t="n"/>
@@ -1970,12 +1969,12 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>DB Shoulder Press</t>
+          <t>Landmine Press</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Shoulders, Chest</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -1988,25 +1987,29 @@
           <t>1+ years</t>
         </is>
       </c>
-      <c r="F38" s="1" t="str"/>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>⚑ SAFE injury profile suggests this could reasonably be 'everyone'; not in the app's own beginner curriculum, so left at 1+ years.</t>
+        </is>
+      </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>Start at the shoulders, press to lockout.</t>
+          <t>Split stance, press at an angle, follow the arc.</t>
         </is>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>No arching through the lower back.</t>
+          <t>Stable base, strong finish.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>frontal</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>sagittal</t>
         </is>
       </c>
       <c r="K38" s="5" t="n"/>
@@ -2019,7 +2022,7 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>Seated DB Press</t>
+          <t>DB Shoulder Press</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -2034,18 +2037,18 @@
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F39" s="1" t="str"/>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>Back flat against the pad, press to lockout.</t>
+          <t>Start at the shoulders, press to lockout.</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>Ribs down, control the descent.</t>
+          <t>No arching through the lower back.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2068,7 +2071,7 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>Half-Kneeling Single-Arm Overhead Press</t>
+          <t>Seated DB Press</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -2078,7 +2081,7 @@
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Midline</t>
+          <t>Triceps</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -2089,12 +2092,12 @@
       <c r="F40" s="1" t="str"/>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>Half-kneel, press straight overhead, knee on ground = arm overhead.</t>
+          <t>Back flat against the pad, press to lockout.</t>
         </is>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>Fight the rotation, ribs stay down.</t>
+          <t>Ribs down, control the descent.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2104,7 +2107,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>transverse</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K40" s="5" t="n"/>
@@ -2112,43 +2115,43 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Upper push vertical</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>Explosive Landmine Press</t>
+          <t>Half-Kneeling Single-Arm Overhead Press</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Chest</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>Triceps</t>
+          <t>Triceps, Midline</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F41" s="1" t="str"/>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>Split stance, drive hard into the bar.</t>
+          <t>Half-kneel, press straight overhead, knee on ground = arm overhead.</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>Full lockout, reset quickly.</t>
+          <t>Fight the rotation, ribs stay down.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>frontal</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2161,52 +2164,48 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Upper push vertical</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>Z-Press</t>
+          <t>Explosive Landmine Press</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Shoulders, Chest</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Midline</t>
+          <t>Triceps</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>⚑ no leg drive raises the midline/shoulder stability demand, but could be 1+ years.</t>
-        </is>
-      </c>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="str"/>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>Sit up tall, slight lean back when pressing.</t>
+          <t>Split stance, drive hard into the bar.</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>Stay tight through midline. Can be done seated on a bench, or with dumbbells.</t>
+          <t>Full lockout, reset quickly.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>frontal</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>transverse</t>
         </is>
       </c>
       <c r="K42" s="5" t="n"/>
@@ -2214,43 +2213,47 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Upper pull horizontal</t>
+          <t>Upper push vertical</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>Barbell Row</t>
+          <t>Z-Press</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Upper back, Lats</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>Biceps, Midline</t>
+          <t>Triceps, Midline</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="str"/>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>⚑ no leg drive raises the midline/shoulder stability demand, but could be 1+ years.</t>
+        </is>
+      </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>Hinge forward, pull to the belly.</t>
+          <t>Sit up tall, slight lean back when pressing.</t>
         </is>
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>Squeeze the shoulder blades at the top.</t>
+          <t>Stay tight through midline. Can be done seated on a bench, or with dumbbells.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>transverse</t>
+          <t>frontal</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2268,7 +2271,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>Chest Supported Row</t>
+          <t>Barbell Row</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -2278,27 +2281,23 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>Biceps</t>
+          <t>Biceps, Midline</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>⚑ not in the app's literal beginner list (Single-Arm DB Row is), but SAFE injury profile reads as beginner-friendly — could be 1+ years instead.</t>
-        </is>
-      </c>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="str"/>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>Chest on the pad, pull straight back.</t>
+          <t>Hinge forward, pull to the belly.</t>
         </is>
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>Retract and hold for a beat.</t>
+          <t>Squeeze the shoulder blades at the top.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2321,7 +2320,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>Single-Arm DB Row</t>
+          <t>Chest Supported Row</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -2331,7 +2330,7 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>Biceps, Midline</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -2339,15 +2338,19 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F45" s="1" t="str"/>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>⚑ not in the app's literal beginner list (Single-Arm DB Row is), but SAFE injury profile reads as beginner-friendly — could be 1+ years instead.</t>
+        </is>
+      </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>Elbow drives past the torso, pull to belly.</t>
+          <t>Chest on the pad, pull straight back.</t>
         </is>
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>Keep the hips and shoulders square.</t>
+          <t>Retract and hold for a beat.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2370,7 +2373,7 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>Seated Cable Row</t>
+          <t>Single-Arm DB Row</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -2380,7 +2383,7 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>Biceps</t>
+          <t>Biceps, Midline</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -2391,12 +2394,12 @@
       <c r="F46" s="1" t="str"/>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>Sit tall, pull to the sternum.</t>
+          <t>Elbow drives past the torso, pull to belly.</t>
         </is>
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>Slow on the return.</t>
+          <t>Keep the hips and shoulders square.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2419,17 +2422,17 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>Face Pull</t>
+          <t>Seated Cable Row</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Upper back</t>
+          <t>Upper back, Lats</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -2440,12 +2443,12 @@
       <c r="F47" s="1" t="str"/>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>Pull to the forehead, open the hands out.</t>
+          <t>Sit tall, pull to the sternum.</t>
         </is>
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>Squeeze the rear delts, slow return.</t>
+          <t>Slow on the return.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2455,14 +2458,10 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>frontal</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>pull</t>
-        </is>
-      </c>
+          <t>sagittal</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -2472,7 +2471,7 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>Rear Delt Fly</t>
+          <t>Face Pull</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -2493,17 +2492,22 @@
       <c r="F48" s="1" t="str"/>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>Rest on incline bench, pinch the shoulder blades.</t>
+          <t>Pull to the forehead, open the hands out.</t>
         </is>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>Light weight, feel the squeeze.</t>
+          <t>Squeeze the rear delts, slow return.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>transverse</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>frontal</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -2520,12 +2524,12 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>Band Pull-Apart</t>
+          <t>Rear Delt Fly</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Upper back, Shoulders</t>
+          <t>Shoulders, Upper back</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
@@ -2541,12 +2545,12 @@
       <c r="F49" s="1" t="str"/>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>Squeeze the shoulder blades together.</t>
+          <t>Rest on incline bench, pinch the shoulder blades.</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>Elbows straight, controlled return.</t>
+          <t>Light weight, feel the squeeze.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2563,51 +2567,50 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Upper pull vertical</t>
+          <t>Upper pull horizontal</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>Pull-Ups</t>
+          <t>Band Pull-Apart</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Lats, Upper back</t>
+          <t>Upper back, Shoulders</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>Biceps</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F50" s="1" t="str"/>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>Dead hang to chin over bar, any grip is fine.</t>
+          <t>Squeeze the shoulder blades together.</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>Initiate with the lats, not the arms. Add weight once bodyweight sets feel easy.</t>
+          <t>Elbows straight, controlled return.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>frontal</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>sagittal</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="n"/>
+          <t>transverse</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>pull</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -2617,17 +2620,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Chin-Ups</t>
+          <t>Pull-Ups</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>Lats, Biceps</t>
+          <t>Lats, Upper back</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
@@ -2638,22 +2641,22 @@
       <c r="F51" s="1" t="str"/>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>Palms facing you, full range.</t>
+          <t>Dead hang to chin over bar, any grip is fine.</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>Control the lowering.</t>
+          <t>Initiate with the lats, not the arms. Add weight once bodyweight sets feel easy.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>frontal</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>frontal</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K51" s="5" t="n"/>
@@ -2666,43 +2669,43 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>Lat Pulldown</t>
+          <t>Chin-Ups</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>Lats, Upper back</t>
+          <t>Lats, Biceps</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>Biceps</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F52" s="1" t="str"/>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>Pull to the collarbone, lean slightly back, push chest at bottom.</t>
+          <t>Palms facing you, full range.</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>Squeeze at the bottom, slow return.</t>
+          <t>Control the lowering.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>frontal</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>sagittal</t>
         </is>
       </c>
       <c r="K52" s="5" t="n"/>
@@ -2715,7 +2718,7 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>Neutral-Grip Pulldown</t>
+          <t>Lat Pulldown</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -2736,18 +2739,22 @@
       <c r="F53" s="1" t="str"/>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>Use V grip attachment, puff chest out as hands come down.</t>
-        </is>
-      </c>
-      <c r="H53" s="1" t="str"/>
+          <t>Pull to the collarbone, lean slightly back, push chest at bottom.</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
+        <is>
+          <t>Squeeze at the bottom, slow return.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>frontal</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>frontal</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K53" s="5" t="n"/>
@@ -2760,17 +2767,17 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>Single-Arm Lat Pulldown</t>
+          <t>Neutral-Grip Pulldown</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>Lats</t>
+          <t>Lats, Upper back</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>Biceps, Upper back, Midline</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -2778,21 +2785,13 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>Canonical identity; legacy records load through the read-ingress alias.</t>
-        </is>
-      </c>
+      <c r="F54" s="1" t="str"/>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>Pull the handle to the shoulder, lead with the lat, V grip attachment.</t>
-        </is>
-      </c>
-      <c r="H54" s="1" t="inlineStr">
-        <is>
-          <t>Stay tight through the midline; control the return to a full stretch.</t>
-        </is>
-      </c>
+          <t>Use V grip attachment, puff chest out as hands come down.</t>
+        </is>
+      </c>
+      <c r="H54" s="1" t="str"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>sagittal</t>
@@ -2808,22 +2807,22 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Lower plyometric</t>
+          <t>Upper pull vertical</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>Box Jumps</t>
+          <t>Single-Arm Lat Pulldown</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>Quads, Glutes</t>
+          <t>Lats</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Biceps, Upper back, Midline</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
@@ -2831,20 +2830,29 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F55" s="1" t="str"/>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>Canonical identity; legacy records load through the read-ingress alias.</t>
+        </is>
+      </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>Jump up, step down.</t>
+          <t>Pull the handle to the shoulder, lead with the lat, V grip attachment.</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>Land soft, absorb with the hips.</t>
+          <t>Stay tight through the midline; control the return to a full stretch.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>sagittal</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>frontal</t>
         </is>
       </c>
       <c r="K55" s="5" t="n"/>
@@ -2857,7 +2865,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>Broad Jumps</t>
+          <t>Box Jumps</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -2867,23 +2875,23 @@
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Calves</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F56" s="1" t="str"/>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>Drive forward, land balanced.</t>
+          <t>Jump up, step down.</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>Stick the landing.</t>
+          <t>Land soft, absorb with the hips.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2901,7 +2909,7 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>Jump Squats</t>
+          <t>Broad Jumps</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -2911,23 +2919,23 @@
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Hamstrings, Calves</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F57" s="1" t="str"/>
       <c r="G57" s="1" t="inlineStr">
         <is>
-          <t>Quarter squat, jump with intent.</t>
+          <t>Drive forward, land balanced.</t>
         </is>
       </c>
       <c r="H57" s="1" t="inlineStr">
         <is>
-          <t>Land soft, reset between reps.</t>
+          <t>Stick the landing.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2945,7 +2953,7 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>Lateral Bounds</t>
+          <t>Jump Squats</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2955,37 +2963,28 @@
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>Groin, Calves</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>⚑ adductor tagged 'avoid' (highest injury rating) for a unilateral lateral landing — genuinely borderline vs. advanced-only.</t>
-        </is>
-      </c>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="str"/>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>Push off outside leg.</t>
+          <t>Quarter squat, jump with intent.</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>Stick each landing before the next.</t>
+          <t>Land soft, reset between reps.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>frontal</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>transverse</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K58" s="5" t="n"/>
@@ -2998,7 +2997,7 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>Depth Jumps</t>
+          <t>Lateral Bounds</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -3008,37 +3007,37 @@
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>Calves, Hamstrings</t>
+          <t>Groin, Calves</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>advanced only</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>knee + ankle both tagged 'avoid'; classic high eccentric-overload drop-jump reserved for qualified athletes.</t>
+          <t>⚑ adductor tagged 'avoid' (highest injury rating) for a unilateral lateral landing — genuinely borderline vs. advanced-only.</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>Step off, explode off the ground.</t>
+          <t>Push off outside leg.</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>Minimum ground contact time.</t>
+          <t>Stick each landing before the next.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>frontal</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>frontal, transverse</t>
+          <t>transverse</t>
         </is>
       </c>
       <c r="K59" s="5" t="n"/>
@@ -3046,38 +3045,42 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Carries</t>
+          <t>Lower plyometric</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>Farmer Carry</t>
+          <t>Depth Jumps</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>Midline, Upper back</t>
+          <t>Quads, Glutes</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Calves, Hamstrings</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F60" s="1" t="str"/>
+          <t>advanced only</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>knee + ankle both tagged 'avoid'; classic high eccentric-overload drop-jump reserved for qualified athletes.</t>
+        </is>
+      </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>Shoulders packed, walk tall.</t>
+          <t>Step off, explode off the ground.</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>Breathe and keep moving. Weight shown is per hand.</t>
+          <t>Minimum ground contact time.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3100,7 +3103,7 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Bear Carry</t>
+          <t>Farmer Carry</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -3115,18 +3118,18 @@
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F61" s="1" t="str"/>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>Hug the load tight, ribs down.</t>
+          <t>Shoulders packed, walk tall.</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>Short steady steps, no leaning back.</t>
+          <t>Breathe and keep moving. Weight shown is per hand.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3136,7 +3139,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>transverse</t>
+          <t>frontal, transverse</t>
         </is>
       </c>
       <c r="K61" s="5" t="n"/>
@@ -3149,33 +3152,33 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>Suitcase Carry</t>
+          <t>Bear Carry</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Midline, Upper back</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>Upper back, Shoulders</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F62" s="1" t="str"/>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>Walk tall, don’t lean.</t>
+          <t>Hug the load tight, ribs down.</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>Don’t rest weight on thigh.</t>
+          <t>Short steady steps, no leaning back.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3185,7 +3188,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>frontal</t>
+          <t>transverse</t>
         </is>
       </c>
       <c r="K62" s="5" t="n"/>
@@ -3198,33 +3201,33 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>Overhead Carry</t>
+          <t>Suitcase Carry</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Midline</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Upper back, Shoulders</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F63" s="1" t="str"/>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>Stand tall, arms overhead, stay tight through midline.</t>
+          <t>Walk tall, don’t lean.</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>Weight shown is per hand.</t>
+          <t>Don’t rest weight on thigh.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3234,7 +3237,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>frontal, transverse</t>
+          <t>frontal</t>
         </is>
       </c>
       <c r="K63" s="5" t="n"/>
@@ -3242,50 +3245,51 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Accessories upper</t>
+          <t>Carries</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>Shrugs</t>
+          <t>Overhead Carry</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
+          <t>Shoulders, Midline</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
           <t>Upper back</t>
         </is>
       </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>Traps</t>
-        </is>
-      </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F64" s="1" t="str"/>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>Shoulders straight up to ears, no roll.</t>
+          <t>Stand tall, arms overhead, stay tight through midline.</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>Squeeze at the top, controlled lower.</t>
+          <t>Weight shown is per hand.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>frontal</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>pull</t>
-        </is>
-      </c>
+          <t>sagittal</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>frontal, transverse</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -3295,17 +3299,17 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>Skull Crushers</t>
+          <t>Shrugs</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>Triceps</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Traps</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
@@ -3313,29 +3317,25 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>elbow-strain-prone lockout under barbell load vs. the dumbbell version.</t>
-        </is>
-      </c>
+      <c r="F65" s="1" t="str"/>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>Lower to the sides of the head, press up, use straight or Z bar.</t>
+          <t>Shoulders straight up to ears, no roll.</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>Full range, elbows stay in place.</t>
+          <t>Squeeze at the top, controlled lower.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>frontal</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>pull</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>Bicep Curl (Barbell)</t>
+          <t>Skull Crushers</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>Biceps</t>
+          <t>Triceps</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
@@ -3365,15 +3365,19 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F66" s="1" t="str"/>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>elbow-strain-prone lockout under barbell load vs. the dumbbell version.</t>
+        </is>
+      </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>Elbows glued to the sides, full range.</t>
+          <t>Lower to the sides of the head, press up, use straight or Z bar.</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>No swinging, control the bar path.</t>
+          <t>Full range, elbows stay in place.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3383,7 +3387,7 @@
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>pull</t>
+          <t>push</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3399,7 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>Bicep Curl (Dumbbell)</t>
+          <t>Bicep Curl (Barbell)</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -3416,12 +3420,12 @@
       <c r="F67" s="1" t="str"/>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>Neutral start, supinate as you curl.</t>
+          <t>Elbows glued to the sides, full range.</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>Smooth tempo, squeeze at the top.</t>
+          <t>No swinging, control the bar path.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3443,7 +3447,7 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>Hammer Curl</t>
+          <t>Bicep Curl (Dumbbell)</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -3464,12 +3468,12 @@
       <c r="F68" s="1" t="str"/>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>Neutral grip, no swinging.</t>
+          <t>Neutral start, supinate as you curl.</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>Control both directions.</t>
+          <t>Smooth tempo, squeeze at the top.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3491,7 +3495,7 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>Incline Dumbbell Curl</t>
+          <t>Hammer Curl</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -3512,12 +3516,12 @@
       <c r="F69" s="1" t="str"/>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>Let the arm stretch at the bottom.</t>
+          <t>Neutral grip, no swinging.</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>Slow curl, squeeze at the top.</t>
+          <t>Control both directions.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3539,7 +3543,7 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>Lying Dumbbell Curl</t>
+          <t>Incline Dumbbell Curl</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -3560,12 +3564,12 @@
       <c r="F70" s="1" t="str"/>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>Lie flat, arms stretch at the bottom.</t>
+          <t>Let the arm stretch at the bottom.</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>Control both directions, no momentum.</t>
+          <t>Slow curl, squeeze at the top.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3587,7 +3591,7 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>Banded Bicep Curl</t>
+          <t>Lying Dumbbell Curl</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -3602,22 +3606,18 @@
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
-        </is>
-      </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>Regression per Sam 2026-07-25: above-beginner doesn't need banded curls</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="str"/>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>Elbows pinned, curl against the band.</t>
+          <t>Lie flat, arms stretch at the bottom.</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>Slow on the way down.</t>
+          <t>Control both directions, no momentum.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>Concentration Curl</t>
+          <t>Banded Bicep Curl</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -3654,18 +3654,22 @@
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F72" s="1" t="str"/>
+          <t>everyone (regression)</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="inlineStr">
+        <is>
+          <t>Regression per Sam 2026-07-25: above-beginner doesn't need banded curls</t>
+        </is>
+      </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>Elbow braced on the inner thigh.</t>
+          <t>Elbows pinned, curl against the band.</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>Strict curl, no body swing.</t>
+          <t>Slow on the way down.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3687,12 +3691,12 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>Tricep Pushdown</t>
+          <t>Concentration Curl</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>Triceps</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
@@ -3708,12 +3712,12 @@
       <c r="F73" s="1" t="str"/>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>Keep elbows pinned, press to full lockout.</t>
+          <t>Elbow braced on the inner thigh.</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>Constant tension, no jerking.</t>
+          <t>Strict curl, no body swing.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3723,7 +3727,7 @@
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>pull</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3739,7 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>Banded Tricep Pushdown</t>
+          <t>Tricep Pushdown</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -3756,12 +3760,12 @@
       <c r="F74" s="1" t="str"/>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>Lock the elbows, press to full extension.</t>
+          <t>Keep elbows pinned, press to full lockout.</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>Constant tension, no slack.</t>
+          <t>Constant tension, no jerking.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3783,7 +3787,7 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>Overhead Tricep Extension</t>
+          <t>Banded Tricep Pushdown</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -3804,12 +3808,12 @@
       <c r="F75" s="1" t="str"/>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>Full stretch at the bottom, press to lockout.</t>
+          <t>Lock the elbows, press to full extension.</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>Elbows stay pointed forward.</t>
+          <t>Constant tension, no slack.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3831,7 +3835,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>Dumbbell Skull Crusher</t>
+          <t>Overhead Tricep Extension</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -3849,19 +3853,15 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>same elbow lockout concern as the barbell version, lighter load.</t>
-        </is>
-      </c>
+      <c r="F76" s="1" t="str"/>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>Lower to the sides of the head, press up.</t>
+          <t>Full stretch at the bottom, press to lockout.</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>Elbows stay fixed in place.</t>
+          <t>Elbows stay pointed forward.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>Dumbbell Kickback</t>
+          <t>Dumbbell Skull Crusher</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -3901,15 +3901,19 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F77" s="1" t="str"/>
+      <c r="F77" s="1" t="inlineStr">
+        <is>
+          <t>same elbow lockout concern as the barbell version, lighter load.</t>
+        </is>
+      </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>One knee on bench, one hand on bench, extend to full lockout.</t>
+          <t>Lower to the sides of the head, press up.</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>Squeeze at the top, slow return.</t>
+          <t>Elbows stay fixed in place.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3931,7 +3935,7 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>Tricep Circuit (Dirty 30)</t>
+          <t>Dumbbell Kickback</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -3952,12 +3956,12 @@
       <c r="F78" s="1" t="str"/>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>Move through all three positions without rest.</t>
+          <t>One knee on bench, one hand on bench, extend to full lockout.</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>Empty the triceps by the final rep.</t>
+          <t>Squeeze at the top, slow return.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3979,12 +3983,12 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>Lateral Raise</t>
+          <t>Tricep Circuit (Dirty 30)</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Triceps</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
@@ -4000,17 +4004,17 @@
       <c r="F79" s="1" t="str"/>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>Light weight, lead with the elbows.</t>
+          <t>Move through all three positions without rest.</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>No momentum, strict form.</t>
+          <t>Empty the triceps by the final rep.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>frontal</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr">
@@ -4027,12 +4031,12 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>Incline Y Raise</t>
+          <t>Lateral Raise</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Upper back</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
@@ -4048,12 +4052,12 @@
       <c r="F80" s="1" t="str"/>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>Chest on the incline, arms to a Y.</t>
+          <t>Light weight, lead with the elbows.</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>Light weight, pause at the top.</t>
+          <t>No momentum, strict form.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4061,14 +4065,9 @@
           <t>frontal</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>sagittal</t>
-        </is>
-      </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>pull</t>
+          <t>push</t>
         </is>
       </c>
     </row>
@@ -4080,12 +4079,12 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>Single-Arm Shrug</t>
+          <t>Incline Y Raise</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Shoulders, Upper back</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
@@ -4101,17 +4100,22 @@
       <c r="F81" s="1" t="str"/>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>One side at a time, shoulder straight up.</t>
+          <t>Chest on the incline, arms to a Y.</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>Pause at the top, controlled lower.</t>
+          <t>Light weight, pause at the top.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>frontal</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
@@ -4123,17 +4127,17 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>Accessories lower</t>
+          <t>Accessories upper</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>Nordic Lower</t>
+          <t>Single-Arm Shrug</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
@@ -4143,30 +4147,30 @@
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>hamstring tagged 'avoid'; classic high-eccentric-overload movement — standard guidance is an eccentric-strength base before loading this.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="str"/>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>Lower as slow as you can.</t>
+          <t>One side at a time, shoulder straight up.</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>Fight gravity the whole way down.</t>
+          <t>Pause at the top, controlled lower.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>sagittal</t>
-        </is>
-      </c>
-      <c r="K82" s="5" t="n"/>
+          <t>frontal</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>pull</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -4176,7 +4180,7 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>Hamstring Curl</t>
+          <t>Nordic Lower</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -4191,16 +4195,24 @@
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="str"/>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="inlineStr">
+        <is>
+          <t>hamstring tagged 'avoid'; classic high-eccentric-overload movement — standard guidance is an eccentric-strength base before loading this.</t>
+        </is>
+      </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>Pad should be lower calf area, squeeze heels to butt.</t>
-        </is>
-      </c>
-      <c r="H83" s="1" t="str"/>
+          <t>Lower as slow as you can.</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="inlineStr">
+        <is>
+          <t>Fight gravity the whole way down.</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>sagittal</t>
@@ -4216,12 +4228,12 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>Leg Extension</t>
+          <t>Hamstring Curl</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>Quads</t>
+          <t>Hamstrings</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
@@ -4237,7 +4249,7 @@
       <c r="F84" s="1" t="str"/>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>Drive feet to ceiling, lean back slightly if possible.</t>
+          <t>Pad should be lower calf area, squeeze heels to butt.</t>
         </is>
       </c>
       <c r="H84" s="1" t="str"/>
@@ -4256,12 +4268,12 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>Calf Raises</t>
+          <t>Leg Extension</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Quads</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
@@ -4277,14 +4289,10 @@
       <c r="F85" s="1" t="str"/>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>Elevate balls of feet on step, full heel drop, rise onto the big toe.</t>
-        </is>
-      </c>
-      <c r="H85" s="1" t="inlineStr">
-        <is>
-          <t>Pause high, lower slowly.</t>
-        </is>
-      </c>
+          <t>Drive feet to ceiling, lean back slightly if possible.</t>
+        </is>
+      </c>
+      <c r="H85" s="1" t="str"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>sagittal</t>
@@ -4300,137 +4308,136 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
+          <t>Calf Raises</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>Calves</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="str"/>
+      <c r="G86" s="1" t="inlineStr">
+        <is>
+          <t>Elevate balls of feet on step, full heel drop, rise onto the big toe.</t>
+        </is>
+      </c>
+      <c r="H86" s="1" t="inlineStr">
+        <is>
+          <t>Pause high, lower slowly.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>Accessories lower</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
           <t>Tib Raises</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>Calves</t>
         </is>
       </c>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E86" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F86" s="1" t="inlineStr">
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="inlineStr">
         <is>
           <t>targets tibialis anterior (shin) specifically; 'Calves' is the closest plain-language bucket.</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr">
+      <c r="G87" s="1" t="inlineStr">
         <is>
           <t>Lean back against wall, lift toes to sky, can use a Tib bar if you have one.</t>
         </is>
       </c>
-      <c r="H86" s="1" t="inlineStr">
+      <c r="H87" s="1" t="inlineStr">
         <is>
           <t>Controlled reps, full range.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>sagittal</t>
-        </is>
-      </c>
-      <c r="K86" s="5" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>Accessories lower</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>T-Bar Tib Raises</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Calves</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>Tibialis anterior (shin). Requires a tib bar and compatible plates. Uses the Tib Raises dose: 2 × 15–20 reps with 30 seconds rest. Begin empty or light, record total external load, and retain full ankle range. Automatic progression from Tib Raises when available; manual Add/Swap. All phases; familiar light loading is suitable at G-1.</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Pull your toes toward your shins through the full range.</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Keep knees still, pause at the top, and lower under control.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>sagittal</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr">
-        <is>
-          <t>Accessories lower</t>
-        </is>
-      </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>Single-Leg Hip Thrust</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>Glutes</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>Hamstrings</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>everyone (regression)</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="str"/>
-      <c r="G88" s="1" t="inlineStr">
-        <is>
-          <t>Upper back on bench, add weight to hips, one leg up, drive hips to sky, squeeze glutes.</t>
-        </is>
-      </c>
-      <c r="H88" s="1" t="str"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>sagittal</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>frontal, transverse</t>
-        </is>
-      </c>
-      <c r="K88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -4440,32 +4447,28 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>Back Extension</t>
+          <t>Single-Leg Hip Thrust</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Glutes, Low back</t>
+          <t>Glutes</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Hamstrings</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>targets lower-back extensors specifically; 'Midline' is the closest plain-language bucket.</t>
-        </is>
-      </c>
+          <t>everyone (regression)</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="str"/>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>Squeeze glutes at top, round slightly at bottom.</t>
+          <t>Upper back on bench, add weight to hips, one leg up, drive hips to sky, squeeze glutes.</t>
         </is>
       </c>
       <c r="H89" s="1" t="str"/>
@@ -4474,161 +4477,161 @@
           <t>sagittal</t>
         </is>
       </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>frontal, transverse</t>
+        </is>
+      </c>
       <c r="K89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
+          <t>Accessories lower</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>Back Extension</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>Hamstrings, Glutes, Low back</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>Midline</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
+          <t>targets lower-back extensors specifically; 'Midline' is the closest plain-language bucket.</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>Squeeze glutes at top, round slightly at bottom.</t>
+        </is>
+      </c>
+      <c r="H90" s="1" t="str"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
           <t>Upper pull vertical</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
+      <c r="B91" s="1" t="inlineStr">
         <is>
           <t>Chin-Up Negative (Slow)</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>Lats, Biceps</t>
         </is>
       </c>
-      <c r="D90" s="1" t="inlineStr">
+      <c r="D91" s="1" t="inlineStr">
         <is>
           <t>Upper back, Midline</t>
         </is>
       </c>
-      <c r="E90" s="1" t="inlineStr">
+      <c r="E91" s="1" t="inlineStr">
         <is>
           <t>everyone (regression)</t>
         </is>
       </c>
-      <c r="F90" s="1" t="inlineStr">
+      <c r="F91" s="1" t="inlineStr">
         <is>
           <t>Moved per Sam from Arms—biceps (it lived in the biceps pool; now vertical pull).</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr">
+      <c r="G91" s="1" t="inlineStr">
         <is>
           <t>Jump to the top, lower slowly, can pull yourself up if you can.</t>
         </is>
       </c>
-      <c r="H90" s="1" t="inlineStr">
+      <c r="H91" s="1" t="inlineStr">
         <is>
           <t>Fight gravity the whole way.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>sagittal</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
         <is>
           <t>frontal</t>
         </is>
       </c>
-      <c r="K90" s="5" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="K91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>Shoulders</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>Cable Face Pull</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Shoulders, Upper back</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="G91" s="1" t="inlineStr">
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="inlineStr">
         <is>
           <t>Pull to the forehead, open the hands out.</t>
         </is>
       </c>
-      <c r="H91" s="1" t="inlineStr">
+      <c r="H92" s="1" t="inlineStr">
         <is>
           <t>Squeeze the rear delts.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>transverse</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>frontal</t>
         </is>
       </c>
-      <c r="K91" s="5" t="inlineStr">
+      <c r="K92" s="5" t="inlineStr">
         <is>
           <t>pull</t>
         </is>
       </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="inlineStr">
-        <is>
-          <t>Upper back</t>
-        </is>
-      </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>Chest-Supported DB Row</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>Upper back, Lats</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>Biceps</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="str"/>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>Chest on the pad, pull to the hips, can do on incline bench.</t>
-        </is>
-      </c>
-      <c r="H92" s="1" t="inlineStr">
-        <is>
-          <t>Squeeze the shoulder blades back.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>transverse</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>sagittal</t>
-        </is>
-      </c>
-      <c r="K92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -4638,7 +4641,7 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>Inverted Row (Bodyweight)</t>
+          <t>Chest-Supported DB Row</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
@@ -4653,18 +4656,18 @@
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F93" s="1" t="str"/>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>Straight body, pull chest to bar.</t>
+          <t>Chest on the pad, pull to the hips, can do on incline bench.</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>Scale with foot position.</t>
+          <t>Squeeze the shoulder blades back.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4682,48 +4685,48 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>Groin / adductors</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>Copenhagen Plank (Half)</t>
+          <t>Inverted Row (Bodyweight)</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>Upper back, Lats</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone (regression)</t>
         </is>
       </c>
       <c r="F94" s="1" t="str"/>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>Top leg on the bench, drive through the inner thigh.</t>
+          <t>Straight body, pull chest to bar.</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>Hold tension, no dropping.</t>
+          <t>Scale with foot position.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>frontal</t>
+          <t>transverse</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>transverse</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K94" s="5" t="n"/>
@@ -4736,7 +4739,7 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>Long-Lever Copenhagen</t>
+          <t>Copenhagen Plank (Half)</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -4751,18 +4754,18 @@
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F95" s="1" t="str"/>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>Top ankle supported, hips high.</t>
+          <t>Top leg on the bench, drive through the inner thigh.</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>Don’t let hips drop.</t>
+          <t>Hold tension, no dropping.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4785,7 +4788,7 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>Groin Squeeze</t>
+          <t>Long-Lever Copenhagen</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -4795,28 +4798,33 @@
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F96" s="1" t="str"/>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>Squeeze the ball between the knees — or your fists if no ball.</t>
+          <t>Top ankle supported, hips high.</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>Hold each squeeze for a beat.</t>
+          <t>Don’t let hips drop.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>frontal</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>transverse</t>
         </is>
       </c>
       <c r="K96" s="5" t="n"/>
@@ -4829,43 +4837,38 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>Cossack Squat</t>
+          <t>Groin Squeeze</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>Groin, Quads</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Hips</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F97" s="1" t="str"/>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>Wide stance, sit onto one leg, other leg straight.</t>
+          <t>Squeeze the ball between the knees — or your fists if no ball.</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>Heel down, chest up, push back through. Hold rack if needed.</t>
+          <t>Hold each squeeze for a beat.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>frontal</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>sagittal</t>
         </is>
       </c>
       <c r="K97" s="5" t="n"/>
@@ -4878,7 +4881,7 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>Lateral Lunge</t>
+          <t>Cossack Squat</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -4899,12 +4902,12 @@
       <c r="F98" s="1" t="str"/>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>Big step sideways, sit into that hip.</t>
+          <t>Wide stance, sit onto one leg, other leg straight.</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>Knee tracks over toes, drive back to standing.</t>
+          <t>Heel down, chest up, push back through. Hold rack if needed.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4922,48 +4925,48 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Groin / adductors</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>Single-Leg Calf Raise</t>
+          <t>Lateral Lunge</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Groin, Quads</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Glutes, Hips</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F99" s="1" t="str"/>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>Full drop at the bottom, pause, then rise.</t>
+          <t>Big step sideways, sit into that hip.</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>Three-second lowering.</t>
+          <t>Knee tracks over toes, drive back to standing.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>frontal</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>frontal</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K99" s="5" t="n"/>
@@ -4976,7 +4979,7 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>Seated Calf Raise</t>
+          <t>Single-Leg Calf Raise</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -4997,17 +5000,22 @@
       <c r="F100" s="1" t="str"/>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>Bent knee, full range top to bottom.</t>
+          <t>Full drop at the bottom, pause, then rise.</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>Slow tempo, no bouncing.</t>
+          <t>Three-second lowering.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>sagittal</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>frontal</t>
         </is>
       </c>
       <c r="K100" s="5" t="n"/>
@@ -5015,17 +5023,17 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>Lower prehab</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>Banded TKE</t>
+          <t>Seated Calf Raise</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>Quads, Knee</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
@@ -5041,10 +5049,14 @@
       <c r="F101" s="1" t="str"/>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>Band behind knee, step back for tension, straighten knee and squeeze quads.</t>
-        </is>
-      </c>
-      <c r="H101" s="1" t="str"/>
+          <t>Bent knee, full range top to bottom.</t>
+        </is>
+      </c>
+      <c r="H101" s="1" t="inlineStr">
+        <is>
+          <t>Slow tempo, no bouncing.</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>sagittal</t>
@@ -5060,12 +5072,12 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>Bosch Hold</t>
+          <t>Banded TKE</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Calves</t>
+          <t>Quads, Knee</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
@@ -5081,7 +5093,7 @@
       <c r="F102" s="1" t="str"/>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>Single or double leg, slight knee bend, drive heel into ground, keep hips high.</t>
+          <t>Band behind knee, step back for tension, straighten knee and squeeze quads.</t>
         </is>
       </c>
       <c r="H102" s="1" t="str"/>
@@ -5090,11 +5102,6 @@
           <t>sagittal</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>frontal, transverse</t>
-        </is>
-      </c>
       <c r="K102" s="5" t="n"/>
     </row>
     <row r="103">
@@ -5105,12 +5112,12 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>Spanish Squat Hold</t>
+          <t>Bosch Hold</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>Quads, Knee</t>
+          <t>Hamstrings, Calves</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
@@ -5126,7 +5133,7 @@
       <c r="F103" s="1" t="str"/>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>Band behind knees, tension on bands, sit back into a squat and hold.</t>
+          <t>Single or double leg, slight knee bend, drive heel into ground, keep hips high.</t>
         </is>
       </c>
       <c r="H103" s="1" t="str"/>
@@ -5135,6 +5142,11 @@
           <t>sagittal</t>
         </is>
       </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>frontal, transverse</t>
+        </is>
+      </c>
       <c r="K103" s="5" t="n"/>
     </row>
     <row r="104">
@@ -5145,7 +5157,7 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>Slant Board Step-Down</t>
+          <t>Spanish Squat Hold</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -5155,7 +5167,7 @@
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
@@ -5166,7 +5178,7 @@
       <c r="F104" s="1" t="str"/>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>Drive knee forward, tap opposite heel on ground, knee tracks over toes.</t>
+          <t>Band behind knees, tension on bands, sit back into a squat and hold.</t>
         </is>
       </c>
       <c r="H104" s="1" t="str"/>
@@ -5175,11 +5187,6 @@
           <t>sagittal</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>frontal</t>
-        </is>
-      </c>
       <c r="K104" s="5" t="n"/>
     </row>
     <row r="105">
@@ -5190,17 +5197,17 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>Crab Walks</t>
+          <t>Slant Board Step-Down</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Hips</t>
+          <t>Quads, Knee</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
@@ -5211,18 +5218,18 @@
       <c r="F105" s="1" t="str"/>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>Sit back into athletic position, band around feet, push off outside leg, keep knees slightly pointed out.</t>
+          <t>Drive knee forward, tap opposite heel on ground, knee tracks over toes.</t>
         </is>
       </c>
       <c r="H105" s="1" t="str"/>
       <c r="I105" t="inlineStr">
         <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
           <t>frontal</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>transverse</t>
         </is>
       </c>
       <c r="K105" s="5" t="n"/>
@@ -5230,17 +5237,17 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Lower prehab</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>Band Pallof Press</t>
+          <t>Crab Walks</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Glutes, Hips</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
@@ -5256,15 +5263,16 @@
       <c r="F106" s="1" t="str"/>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>Press out, resist the pull.</t>
-        </is>
-      </c>
-      <c r="H106" s="1" t="inlineStr">
-        <is>
-          <t>Hips stay square, slight knee and hip bend.</t>
-        </is>
-      </c>
+          <t>Sit back into athletic position, band around feet, push off outside leg, keep knees slightly pointed out.</t>
+        </is>
+      </c>
+      <c r="H106" s="1" t="str"/>
       <c r="I106" t="inlineStr">
+        <is>
+          <t>frontal</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
         <is>
           <t>transverse</t>
         </is>
@@ -5279,7 +5287,7 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>Dead Bug</t>
+          <t>Band Pallof Press</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -5294,27 +5302,23 @@
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>Regression confirmed by Sam: plain version — advanced get Banded/Weighted Dead Bug instead</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="str"/>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>Lower back stays flat on the floor.</t>
+          <t>Press out, resist the pull.</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>Opposite arm and leg, slow.</t>
+          <t>Hips stay square, slight knee and hip bend.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>transverse</t>
         </is>
       </c>
       <c r="K107" s="5" t="n"/>
@@ -5327,7 +5331,7 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>Banded Dead Bug</t>
+          <t>Dead Bug</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -5342,18 +5346,22 @@
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="str"/>
+          <t>everyone (regression)</t>
+        </is>
+      </c>
+      <c r="F108" s="1" t="inlineStr">
+        <is>
+          <t>Regression confirmed by Sam: plain version — advanced get Banded/Weighted Dead Bug instead</t>
+        </is>
+      </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>Band behind head, pull band with straight arms toward knees, ribs down.</t>
+          <t>Lower back stays flat on the floor.</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>Lower back stays glued to the floor.</t>
+          <t>Opposite arm and leg, slow.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5371,7 +5379,7 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>Weighted Dead Bug</t>
+          <t>Banded Dead Bug</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -5381,23 +5389,23 @@
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F109" s="1" t="str"/>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>Hold weight plate or dumbbells, extended arms overhead and feet out, low back pinned to ground.</t>
+          <t>Band behind head, pull band with straight arms toward knees, ribs down.</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>Slow extension, full exhale.</t>
+          <t>Lower back stays glued to the floor.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5415,7 +5423,7 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>McGill Sit Up</t>
+          <t>Weighted Dead Bug</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -5425,23 +5433,23 @@
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F110" s="1" t="str"/>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>Hands under the lower back, lift the shoulder blades only.</t>
+          <t>Hold weight plate or dumbbells, extended arms overhead and feet out, low back pinned to ground.</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>Drive low back into hands slightly.</t>
+          <t>Slow extension, full exhale.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5459,7 +5467,7 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>Ab Wheel</t>
+          <t>McGill Sit Up</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -5469,27 +5477,23 @@
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>⚑ progressive anti-extension skill move; pubalgia tagged 'avoid' — could arguably be 1+ years depending on how far the rollout range is regressed.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F111" s="1" t="str"/>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>Roll out only as far as you can control.</t>
+          <t>Hands under the lower back, lift the shoulder blades only.</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>Ribs down, slightly rounded back, no sagging at hips.</t>
+          <t>Drive low back into hands slightly.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5507,7 +5511,7 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>Hanging Leg Raise</t>
+          <t>Ab Wheel</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -5517,23 +5521,27 @@
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="str"/>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F112" s="1" t="inlineStr">
+        <is>
+          <t>⚑ progressive anti-extension skill move; pubalgia tagged 'avoid' — could arguably be 1+ years depending on how far the rollout range is regressed.</t>
+        </is>
+      </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>Stay tight through midline, breath.</t>
+          <t>Roll out only as far as you can control.</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>No swinging.</t>
+          <t>Ribs down, slightly rounded back, no sagging at hips.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5551,7 +5559,7 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>Bird Dog</t>
+          <t>Hanging Leg Raise</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -5561,37 +5569,28 @@
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>Glutes</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>Regression confirmed by Sam: foundational motor control — or does it belong in the flow?</t>
-        </is>
-      </c>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F113" s="1" t="str"/>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>Extend arm and opposite leg, no shift, tuck hips under you.</t>
+          <t>Stay tight through midline, breath.</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>Slow and controlled.</t>
+          <t>No swinging.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
           <t>sagittal</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>transverse</t>
         </is>
       </c>
       <c r="K113" s="5" t="n"/>
@@ -5604,7 +5603,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>Side Plank</t>
+          <t>Bird Dog</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -5614,28 +5613,32 @@
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Glutes</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="str"/>
+          <t>everyone (regression)</t>
+        </is>
+      </c>
+      <c r="F114" s="1" t="inlineStr">
+        <is>
+          <t>Regression confirmed by Sam: foundational motor control — or does it belong in the flow?</t>
+        </is>
+      </c>
       <c r="G114" s="1" t="inlineStr">
         <is>
-          <t>Stack the hips, straight line from head to feet, can add weight to top hip.</t>
+          <t>Extend arm and opposite leg, no shift, tuck hips under you.</t>
         </is>
       </c>
       <c r="H114" s="1" t="inlineStr">
         <is>
-          <t>Breathe behind the brace.</t>
+          <t>Slow and controlled.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>frontal</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -5653,7 +5656,7 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>Plank</t>
+          <t>Side Plank</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -5663,28 +5666,33 @@
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>Regression confirmed by Sam: plain plank — advanced get Stir the Pot / Side Plank Row / Ab Wheel</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F115" s="1" t="str"/>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>Keep spine neutral, brace midline, squeeze butt, breathe.</t>
-        </is>
-      </c>
-      <c r="H115" s="1" t="str"/>
+          <t>Stack the hips, straight line from head to feet, can add weight to top hip.</t>
+        </is>
+      </c>
+      <c r="H115" s="1" t="inlineStr">
+        <is>
+          <t>Breathe behind the brace.</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>frontal</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>transverse</t>
         </is>
       </c>
       <c r="K115" s="5" t="n"/>
@@ -5697,7 +5705,7 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>Hollow Hold</t>
+          <t>Plank</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -5707,18 +5715,22 @@
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="str"/>
+          <t>everyone (regression)</t>
+        </is>
+      </c>
+      <c r="F116" s="1" t="inlineStr">
+        <is>
+          <t>Regression confirmed by Sam: plain plank — advanced get Stir the Pot / Side Plank Row / Ab Wheel</t>
+        </is>
+      </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>Stay tight, remember to breathe, low back pinned to floor.</t>
+          <t>Keep spine neutral, brace midline, squeeze butt, breathe.</t>
         </is>
       </c>
       <c r="H116" s="1" t="str"/>
@@ -5737,7 +5749,7 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>Stir the Pot</t>
+          <t>Hollow Hold</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -5747,7 +5759,7 @@
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
@@ -5758,13 +5770,13 @@
       <c r="F117" s="1" t="str"/>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>Spine stays neutral, resist rotation through midline.</t>
+          <t>Stay tight, remember to breathe, low back pinned to floor.</t>
         </is>
       </c>
       <c r="H117" s="1" t="str"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>multiplanar</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K117" s="5" t="n"/>
@@ -5777,7 +5789,7 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>Dragon Flag</t>
+          <t>Stir the Pot</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -5792,23 +5804,19 @@
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>advanced only</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>lower back tagged 'avoid'; classic advanced core skill move, high eccentric demand through the full posterior chain.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="str"/>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>Control the way down, low back should be slightly rounded and roll over ground.</t>
+          <t>Spine stays neutral, resist rotation through midline.</t>
         </is>
       </c>
       <c r="H118" s="1" t="str"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>multiplanar</t>
         </is>
       </c>
       <c r="K118" s="5" t="n"/>
@@ -5821,7 +5829,7 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>Side Plank Row</t>
+          <t>Dragon Flag</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -5831,29 +5839,28 @@
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F119" s="1" t="str"/>
+          <t>advanced only</t>
+        </is>
+      </c>
+      <c r="F119" s="1" t="inlineStr">
+        <is>
+          <t>lower back tagged 'avoid'; classic advanced core skill move, high eccentric demand through the full posterior chain.</t>
+        </is>
+      </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>Side plank, row band to top of belly, resist rolling forward.</t>
+          <t>Control the way down, low back should be slightly rounded and roll over ground.</t>
         </is>
       </c>
       <c r="H119" s="1" t="str"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>frontal</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>transverse</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K119" s="5" t="n"/>
@@ -5866,7 +5873,7 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>Woodchop (Standing)</t>
+          <t>Side Plank Row</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -5876,7 +5883,7 @@
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
@@ -5887,22 +5894,18 @@
       <c r="F120" s="1" t="str"/>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>Rotate through the torso, not the arms.</t>
-        </is>
-      </c>
-      <c r="H120" s="1" t="inlineStr">
-        <is>
-          <t>Feet stay planted.</t>
-        </is>
-      </c>
+          <t>Side plank, row band to top of belly, resist rolling forward.</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="str"/>
       <c r="I120" t="inlineStr">
         <is>
+          <t>frontal</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
           <t>transverse</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>sagittal</t>
         </is>
       </c>
       <c r="K120" s="5" t="n"/>
@@ -5915,7 +5918,7 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>Woodchop (Half Kneeling)</t>
+          <t>Woodchop (Standing)</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
@@ -5936,12 +5939,12 @@
       <c r="F121" s="1" t="str"/>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>Drive with the midline, arms guide.</t>
+          <t>Rotate through the torso, not the arms.</t>
         </is>
       </c>
       <c r="H121" s="1" t="inlineStr">
         <is>
-          <t>Controlled rotation, not a throw.</t>
+          <t>Feet stay planted.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5959,22 +5962,22 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>Shoulder health</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>Banded External Rotation</t>
+          <t>Woodchop (Half Kneeling)</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
+          <t>Midline</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
           <t>Shoulders</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
@@ -5985,12 +5988,22 @@
       <c r="F122" s="1" t="str"/>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>Elbow at 90 degrees, rotate against the band.</t>
+          <t>Drive with the midline, arms guide.</t>
         </is>
       </c>
       <c r="H122" s="1" t="inlineStr">
         <is>
-          <t>Slow and controlled arc.</t>
+          <t>Controlled rotation, not a throw.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>transverse</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K122" s="5" t="n"/>
@@ -6003,7 +6016,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>Bottoms-Up KB Press</t>
+          <t>Banded External Rotation</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -6013,7 +6026,7 @@
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
@@ -6021,19 +6034,15 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>⚑ wrist/shoulder stabilisation demand is real even at light load — could be 1+ years.</t>
-        </is>
-      </c>
+      <c r="F123" s="1" t="str"/>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t>Bell vertical, wrist stacked.</t>
+          <t>Elbow at 90 degrees, rotate against the band.</t>
         </is>
       </c>
       <c r="H123" s="1" t="inlineStr">
         <is>
-          <t>Press smooth, keep ribs down.</t>
+          <t>Slow and controlled arc.</t>
         </is>
       </c>
       <c r="K123" s="5" t="n"/>
@@ -6046,12 +6055,12 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>Scap Push-Up</t>
+          <t>Bottoms-Up KB Press</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Upper back</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
@@ -6064,15 +6073,19 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F124" s="1" t="str"/>
+      <c r="F124" s="1" t="inlineStr">
+        <is>
+          <t>⚑ wrist/shoulder stabilisation demand is real even at light load — could be 1+ years.</t>
+        </is>
+      </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>Keep elbows locked, glide shoulder blades.</t>
+          <t>Bell vertical, wrist stacked.</t>
         </is>
       </c>
       <c r="H124" s="1" t="inlineStr">
         <is>
-          <t>Move slowly, no sagging hips.</t>
+          <t>Press smooth, keep ribs down.</t>
         </is>
       </c>
       <c r="K124" s="5" t="n"/>
@@ -6085,17 +6098,17 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>Scap Pull Ups</t>
+          <t>Scap Push-Up</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Upper back, Lats</t>
+          <t>Shoulders, Upper back</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
@@ -6106,18 +6119,12 @@
       <c r="F125" s="1" t="str"/>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>dead hang from bar and relax, pull yourself higher only using your shoulder blades, don't bend arms</t>
-        </is>
-      </c>
-      <c r="H125" s="1" t="str"/>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>frontal</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>sagittal</t>
+          <t>Keep elbows locked, glide shoulder blades.</t>
+        </is>
+      </c>
+      <c r="H125" s="1" t="inlineStr">
+        <is>
+          <t>Move slowly, no sagging hips.</t>
         </is>
       </c>
       <c r="K125" s="5" t="n"/>
@@ -6125,22 +6132,22 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>Lower prehab</t>
+          <t>Shoulder health</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>Swiss Ball Hamstring Curl</t>
+          <t>Scap Pull Ups</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings</t>
+          <t>Shoulders, Upper back, Lats</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
@@ -6151,15 +6158,16 @@
       <c r="F126" s="1" t="str"/>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>Keep hips high.</t>
-        </is>
-      </c>
-      <c r="H126" s="1" t="inlineStr">
-        <is>
-          <t>Curl heels into butt.</t>
-        </is>
-      </c>
+          <t>dead hang from bar and relax, pull yourself higher only using your shoulder blades, don't bend arms</t>
+        </is>
+      </c>
+      <c r="H126" s="1" t="str"/>
       <c r="I126" t="inlineStr">
+        <is>
+          <t>frontal</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
         <is>
           <t>sagittal</t>
         </is>
@@ -6169,22 +6177,22 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>Tissue quality</t>
+          <t>Lower prehab</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — Hip Flexor, Quad, Adductors</t>
+          <t>Swiss Ball Hamstring Curl</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>Quads, Groin</t>
+          <t>Hamstrings</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
@@ -6195,12 +6203,17 @@
       <c r="F127" s="1" t="str"/>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t>Work the full length, hold on knots.</t>
+          <t>Keep hips high.</t>
         </is>
       </c>
       <c r="H127" s="1" t="inlineStr">
         <is>
-          <t>Relax into the pressure.</t>
+          <t>Curl heels into butt.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K127" s="5" t="n"/>
@@ -6213,17 +6226,17 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — T-Spine</t>
+          <t>Foam Roll — Hip Flexor, Quad, Adductors</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Quads, Groin</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
@@ -6234,12 +6247,12 @@
       <c r="F128" s="1" t="str"/>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>Mid-back over the roller, support the head.</t>
+          <t>Work the full length, hold on knots.</t>
         </is>
       </c>
       <c r="H128" s="1" t="inlineStr">
         <is>
-          <t>Open the ribs and breathe.</t>
+          <t>Relax into the pressure.</t>
         </is>
       </c>
       <c r="K128" s="5" t="n"/>
@@ -6252,17 +6265,17 @@
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — IT Band</t>
+          <t>Foam Roll — T-Spine</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>Quads</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
@@ -6273,12 +6286,12 @@
       <c r="F129" s="1" t="str"/>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>Side-lying, slow passes from hip to knee.</t>
+          <t>Mid-back over the roller, support the head.</t>
         </is>
       </c>
       <c r="H129" s="1" t="inlineStr">
         <is>
-          <t>Stack the legs to dial pressure.</t>
+          <t>Open the ribs and breathe.</t>
         </is>
       </c>
       <c r="K129" s="5" t="n"/>
@@ -6291,17 +6304,17 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — Lats</t>
+          <t>Foam Roll — IT Band</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>Lats</t>
+          <t>Quads</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
@@ -6312,12 +6325,12 @@
       <c r="F130" s="1" t="str"/>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>Side-lying with arm overhead.</t>
+          <t>Side-lying, slow passes from hip to knee.</t>
         </is>
       </c>
       <c r="H130" s="1" t="inlineStr">
         <is>
-          <t>Roll under the armpit, breathe into it.</t>
+          <t>Stack the legs to dial pressure.</t>
         </is>
       </c>
       <c r="K130" s="5" t="n"/>
@@ -6330,12 +6343,12 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — Calves &amp; Outer Shins</t>
+          <t>Foam Roll — Lats</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Lats</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
@@ -6351,12 +6364,12 @@
       <c r="F131" s="1" t="str"/>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>Slow passes, pause on tender spots.</t>
+          <t>Side-lying with arm overhead.</t>
         </is>
       </c>
       <c r="H131" s="1" t="inlineStr">
         <is>
-          <t>Breathe through each hold.</t>
+          <t>Roll under the armpit, breathe into it.</t>
         </is>
       </c>
       <c r="K131" s="5" t="n"/>
@@ -6369,17 +6382,17 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>Lacrosse Ball Glute Release</t>
+          <t>Foam Roll — Calves &amp; Outer Shins</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>Glutes</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
@@ -6390,12 +6403,12 @@
       <c r="F132" s="1" t="str"/>
       <c r="G132" s="1" t="inlineStr">
         <is>
-          <t>Sit on the ball, shift to find the spot.</t>
+          <t>Slow passes, pause on tender spots.</t>
         </is>
       </c>
       <c r="H132" s="1" t="inlineStr">
         <is>
-          <t>Hold 30-60 seconds per side.</t>
+          <t>Breathe through each hold.</t>
         </is>
       </c>
       <c r="K132" s="5" t="n"/>
@@ -6403,22 +6416,22 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>Tissue quality</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>Hip 90/90 Stretch</t>
+          <t>Lacrosse Ball Glute Release</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
+          <t>Glutes</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="inlineStr">
+        <is>
           <t>Hips</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>Groin</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
@@ -6429,12 +6442,12 @@
       <c r="F133" s="1" t="str"/>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t>Front and back legs at 90 degrees.</t>
+          <t>Sit on the ball, shift to find the spot.</t>
         </is>
       </c>
       <c r="H133" s="1" t="inlineStr">
         <is>
-          <t>Stay tall, shift weight gently.</t>
+          <t>Hold 30-60 seconds per side.</t>
         </is>
       </c>
       <c r="K133" s="5" t="n"/>
@@ -6447,17 +6460,17 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>Cat-Cow</t>
+          <t>Hip 90/90 Stretch</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
@@ -6468,12 +6481,12 @@
       <c r="F134" s="1" t="str"/>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t>Round fully, then extend fully.</t>
+          <t>Front and back legs at 90 degrees.</t>
         </is>
       </c>
       <c r="H134" s="1" t="inlineStr">
         <is>
-          <t>Match each position to a breath.</t>
+          <t>Stay tall, shift weight gently.</t>
         </is>
       </c>
       <c r="K134" s="5" t="n"/>
@@ -6486,17 +6499,17 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>World's Greatest Stretch</t>
+          <t>Cat-Cow</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>Hips, Groin</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
@@ -6507,12 +6520,12 @@
       <c r="F135" s="1" t="str"/>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>Lunge deep, elbow to instep.</t>
+          <t>Round fully, then extend fully.</t>
         </is>
       </c>
       <c r="H135" s="1" t="inlineStr">
         <is>
-          <t>Then rotate and reach to the sky.</t>
+          <t>Match each position to a breath.</t>
         </is>
       </c>
       <c r="K135" s="5" t="n"/>
@@ -6525,7 +6538,7 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>Deep Squat Hold</t>
+          <t>World's Greatest Stretch</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -6535,7 +6548,7 @@
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
@@ -6546,12 +6559,12 @@
       <c r="F136" s="1" t="str"/>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t>Sit between the heels, chest up.</t>
+          <t>Lunge deep, elbow to instep.</t>
         </is>
       </c>
       <c r="H136" s="1" t="inlineStr">
         <is>
-          <t>Breathe and hold position.</t>
+          <t>Then rotate and reach to the sky.</t>
         </is>
       </c>
       <c r="K136" s="5" t="n"/>
@@ -6564,17 +6577,17 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>Couch Stretch</t>
+          <t>Deep Squat Hold</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>Quads, Hips</t>
+          <t>Hips, Groin</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
@@ -6585,12 +6598,12 @@
       <c r="F137" s="1" t="str"/>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t>Back knee to the wall, squeeze the glute.</t>
+          <t>Sit between the heels, chest up.</t>
         </is>
       </c>
       <c r="H137" s="1" t="inlineStr">
         <is>
-          <t>Tall through the midline, no arching.</t>
+          <t>Breathe and hold position.</t>
         </is>
       </c>
       <c r="K137" s="5" t="n"/>
@@ -6603,17 +6616,17 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>Open Book Thoracic Rotation</t>
+          <t>Couch Stretch</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Quads, Hips</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
@@ -6624,12 +6637,12 @@
       <c r="F138" s="1" t="str"/>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>Knees stacked, rotate through the upper back.</t>
+          <t>Back knee to the wall, squeeze the glute.</t>
         </is>
       </c>
       <c r="H138" s="1" t="inlineStr">
         <is>
-          <t>Follow the hand with the eyes.</t>
+          <t>Tall through the midline, no arching.</t>
         </is>
       </c>
       <c r="K138" s="5" t="n"/>
@@ -6642,17 +6655,17 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>Pigeon Stretch</t>
+          <t>Open Book Thoracic Rotation</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>Hips, Glutes</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
@@ -6663,12 +6676,12 @@
       <c r="F139" s="1" t="str"/>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>Front shin across bench, square the hips.</t>
+          <t>Knees stacked, rotate through the upper back.</t>
         </is>
       </c>
       <c r="H139" s="1" t="inlineStr">
         <is>
-          <t>Sink in and breathe.</t>
+          <t>Follow the hand with the eyes.</t>
         </is>
       </c>
       <c r="K139" s="5" t="n"/>
@@ -6681,17 +6694,17 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>Adductor Rockback</t>
+          <t>Pigeon Stretch</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
+          <t>Hips, Glutes</t>
+        </is>
+      </c>
+      <c r="D140" s="1" t="inlineStr">
+        <is>
           <t>Groin</t>
-        </is>
-      </c>
-      <c r="D140" s="1" t="inlineStr">
-        <is>
-          <t>Hips</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
@@ -6702,12 +6715,12 @@
       <c r="F140" s="1" t="str"/>
       <c r="G140" s="1" t="inlineStr">
         <is>
-          <t>Wide knees, one leg out straight to side, rock hips back to the heels.</t>
+          <t>Front shin across bench, square the hips.</t>
         </is>
       </c>
       <c r="H140" s="1" t="inlineStr">
         <is>
-          <t>Hold the end range, breathe.</t>
+          <t>Sink in and breathe.</t>
         </is>
       </c>
       <c r="K140" s="5" t="n"/>
@@ -6720,17 +6733,17 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>Chest / Pec Stretch (Doorway)</t>
+          <t>Adductor Rockback</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>Chest</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
@@ -6741,12 +6754,12 @@
       <c r="F141" s="1" t="str"/>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>Forearm on the doorframe, step the foot through.</t>
+          <t>Wide knees, one leg out straight to side, rock hips back to the heels.</t>
         </is>
       </c>
       <c r="H141" s="1" t="inlineStr">
         <is>
-          <t>Big stretch through the chest, breathe slow.</t>
+          <t>Hold the end range, breathe.</t>
         </is>
       </c>
       <c r="K141" s="5" t="n"/>
@@ -6759,12 +6772,12 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>Lat Stretch</t>
+          <t>Chest / Pec Stretch (Doorway)</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>Lats</t>
+          <t>Chest</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
@@ -6780,12 +6793,12 @@
       <c r="F142" s="1" t="str"/>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>Hold a rack or doorframe, hips back.</t>
+          <t>Forearm on the doorframe, step the foot through.</t>
         </is>
       </c>
       <c r="H142" s="1" t="inlineStr">
         <is>
-          <t>Sink the chest, breathe under the armpit, slight lean to one side.</t>
+          <t>Big stretch through the chest, breathe slow.</t>
         </is>
       </c>
       <c r="K142" s="5" t="n"/>
@@ -6798,17 +6811,17 @@
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>Dead Hang</t>
+          <t>Lat Stretch</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>Lats, Shoulders</t>
+          <t>Lats</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
@@ -6819,12 +6832,12 @@
       <c r="F143" s="1" t="str"/>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>Passive hang, shoulders open and relaxed.</t>
+          <t>Hold a rack or doorframe, hips back.</t>
         </is>
       </c>
       <c r="H143" s="1" t="inlineStr">
         <is>
-          <t>Breathe - let the spine decompress.</t>
+          <t>Sink the chest, breathe under the armpit, slight lean to one side.</t>
         </is>
       </c>
       <c r="K143" s="5" t="n"/>
@@ -6837,12 +6850,12 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>Toe Stretch</t>
+          <t>Dead Hang</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>Calves, Feet</t>
+          <t>Lats, Shoulders</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
@@ -6855,19 +6868,15 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F144" s="1" t="inlineStr">
-        <is>
-          <t>targets the foot/ankle specifically; 'Calves' is the closest plain-language bucket.</t>
-        </is>
-      </c>
+      <c r="F144" s="1" t="str"/>
       <c r="G144" s="1" t="inlineStr">
         <is>
-          <t>Tuck toes under, sit back into the heels.</t>
+          <t>Passive hang, shoulders open and relaxed.</t>
         </is>
       </c>
       <c r="H144" s="1" t="inlineStr">
         <is>
-          <t>Build tolerance gradually.</t>
+          <t>Breathe - let the spine decompress.</t>
         </is>
       </c>
       <c r="K144" s="5" t="n"/>
@@ -6880,12 +6889,12 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>Calf Stretch</t>
+          <t>Toe Stretch</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Calves, Feet</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
@@ -6898,15 +6907,19 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F145" s="1" t="str"/>
+      <c r="F145" s="1" t="inlineStr">
+        <is>
+          <t>targets the foot/ankle specifically; 'Calves' is the closest plain-language bucket.</t>
+        </is>
+      </c>
       <c r="G145" s="1" t="inlineStr">
         <is>
-          <t>Heel down, drive knee toward the wall.</t>
+          <t>Tuck toes under, sit back into the heels.</t>
         </is>
       </c>
       <c r="H145" s="1" t="inlineStr">
         <is>
-          <t>Switch to bent-knee for the soleus.</t>
+          <t>Build tolerance gradually.</t>
         </is>
       </c>
       <c r="K145" s="5" t="n"/>
@@ -6919,12 +6932,12 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>QL Back Extension</t>
+          <t>Calf Stretch</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
@@ -6937,17 +6950,17 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F146" s="1" t="inlineStr">
-        <is>
-          <t>targets the quadratus lumborum (side of lower back) specifically; 'Midline' is the closest plain-language bucket.</t>
-        </is>
-      </c>
+      <c r="F146" s="1" t="str"/>
       <c r="G146" s="1" t="inlineStr">
         <is>
-          <t>Pin legs in 45 deg hyper, bend sideways slowly, don’t push too far, just enough to feel tension.</t>
-        </is>
-      </c>
-      <c r="H146" s="1" t="str"/>
+          <t>Heel down, drive knee toward the wall.</t>
+        </is>
+      </c>
+      <c r="H146" s="1" t="inlineStr">
+        <is>
+          <t>Switch to bent-knee for the soleus.</t>
+        </is>
+      </c>
       <c r="K146" s="5" t="n"/>
     </row>
     <row r="147">
@@ -6958,17 +6971,17 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>ATG Split Squat</t>
+          <t>QL Back Extension</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>Quads, Hips</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>Groin, Calves</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
@@ -6978,12 +6991,12 @@
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>⚑ deep ankle/hip mobility demand — some athletes may need to regress the range; could be 1+ years.</t>
+          <t>targets the quadratus lumborum (side of lower back) specifically; 'Midline' is the closest plain-language bucket.</t>
         </is>
       </c>
       <c r="G147" s="1" t="inlineStr">
         <is>
-          <t>Elevate front foot, body stays upright, drive hips to front heel, go slow and pause at bottom.</t>
+          <t>Pin legs in 45 deg hyper, bend sideways slowly, don’t push too far, just enough to feel tension.</t>
         </is>
       </c>
       <c r="H147" s="1" t="str"/>
@@ -6997,17 +7010,17 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>Elephant Walks</t>
+          <t>ATG Split Squat</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings</t>
+          <t>Quads, Hips</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Groin, Calves</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
@@ -7015,10 +7028,14 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F148" s="1" t="str"/>
+      <c r="F148" s="1" t="inlineStr">
+        <is>
+          <t>⚑ deep ankle/hip mobility demand — some athletes may need to regress the range; could be 1+ years.</t>
+        </is>
+      </c>
       <c r="G148" s="1" t="inlineStr">
         <is>
-          <t>Place blocks at level you’re comfortable with, fold forward, bend and straight one leg at a time, slowly.</t>
+          <t>Elevate front foot, body stays upright, drive hips to front heel, go slow and pause at bottom.</t>
         </is>
       </c>
       <c r="H148" s="1" t="str"/>
@@ -7032,17 +7049,17 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>Butterfly Stretch</t>
+          <t>Elephant Walks</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>Groin, Hips</t>
+          <t>Hamstrings</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
@@ -7053,7 +7070,7 @@
       <c r="F149" s="1" t="str"/>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t>Upper back and butt against wall, feet together, knees towards ground, add weight to knee if too easy</t>
+          <t>Place blocks at level you’re comfortable with, fold forward, bend and straight one leg at a time, slowly.</t>
         </is>
       </c>
       <c r="H149" s="1" t="str"/>
@@ -7067,12 +7084,12 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>Pissing Dog Against Wall</t>
+          <t>Butterfly Stretch</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Hips</t>
+          <t>Groin, Hips</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
@@ -7088,7 +7105,7 @@
       <c r="F150" s="1" t="str"/>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t>Keep back neutral, lift outside leg out and up, can use bent leg to start</t>
+          <t>Upper back and butt against wall, feet together, knees towards ground, add weight to knee if too easy</t>
         </is>
       </c>
       <c r="H150" s="1" t="str"/>
@@ -7102,12 +7119,12 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>Jefferson Curl</t>
+          <t>Pissing Dog Against Wall</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>Upper back, Low back, Hamstrings</t>
+          <t>Glutes, Hips</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
@@ -7123,7 +7140,7 @@
       <c r="F151" s="1" t="str"/>
       <c r="G151" s="1" t="inlineStr">
         <is>
-          <t>Tuck your chin and slowly roll down one segment at a time. Add small weight when easy</t>
+          <t>Keep back neutral, lift outside leg out and up, can use bent leg to start</t>
         </is>
       </c>
       <c r="H151" s="1" t="str"/>
@@ -7137,12 +7154,12 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>Dumbbell Pullovers</t>
+          <t>Jefferson Curl</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>Upper back, Shoulders</t>
+          <t>Upper back, Low back, Hamstrings</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
@@ -7158,7 +7175,7 @@
       <c r="F152" s="1" t="str"/>
       <c r="G152" s="1" t="inlineStr">
         <is>
-          <t>Rest upper back on bench, dumbbell over, don't allow ribs to flare up, pause at end range</t>
+          <t>Tuck your chin and slowly roll down one segment at a time. Add small weight when easy</t>
         </is>
       </c>
       <c r="H152" s="1" t="str"/>
@@ -7167,17 +7184,17 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>Easy cardio (zone 1)</t>
+          <t>Mobility</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>Light Walk or Stationary Bike</t>
+          <t>Dumbbell Pullovers</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Upper back, Shoulders</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
@@ -7193,14 +7210,10 @@
       <c r="F153" s="1" t="str"/>
       <c r="G153" s="1" t="inlineStr">
         <is>
-          <t>Conversational effort, keep moving.</t>
-        </is>
-      </c>
-      <c r="H153" s="1" t="inlineStr">
-        <is>
-          <t>This is blood flow, not training.</t>
-        </is>
-      </c>
+          <t>Rest upper back on bench, dumbbell over, don't allow ribs to flare up, pause at end range</t>
+        </is>
+      </c>
+      <c r="H153" s="1" t="str"/>
       <c r="K153" s="5" t="n"/>
     </row>
     <row r="154">
@@ -7211,7 +7224,7 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>Incline Treadmill Walk</t>
+          <t>Light Walk or Stationary Bike</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -7232,12 +7245,12 @@
       <c r="F154" s="1" t="str"/>
       <c r="G154" s="1" t="inlineStr">
         <is>
-          <t>Moderate incline, steady pace.</t>
+          <t>Conversational effort, keep moving.</t>
         </is>
       </c>
       <c r="H154" s="1" t="inlineStr">
         <is>
-          <t>No holding the rails.</t>
+          <t>This is blood flow, not training.</t>
         </is>
       </c>
       <c r="K154" s="5" t="n"/>
@@ -7250,7 +7263,7 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>Outdoor Walk</t>
+          <t>Incline Treadmill Walk</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -7271,12 +7284,12 @@
       <c r="F155" s="1" t="str"/>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t>Easy pace, arms swinging naturally.</t>
+          <t>Moderate incline, steady pace.</t>
         </is>
       </c>
       <c r="H155" s="1" t="inlineStr">
         <is>
-          <t>Get outside and move.</t>
+          <t>No holding the rails.</t>
         </is>
       </c>
       <c r="K155" s="5" t="n"/>
@@ -7284,12 +7297,12 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>Breathing reset</t>
+          <t>Easy cardio (zone 1)</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>90/90 Breathing</t>
+          <t>Outdoor Walk</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -7310,12 +7323,12 @@
       <c r="F156" s="1" t="str"/>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t>Knees and hips at 90, exhale fully.</t>
+          <t>Easy pace, arms swinging naturally.</t>
         </is>
       </c>
       <c r="H156" s="1" t="inlineStr">
         <is>
-          <t>Pause at the bottom of each breath.</t>
+          <t>Get outside and move.</t>
         </is>
       </c>
       <c r="K156" s="5" t="n"/>
@@ -7328,7 +7341,7 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>Crocodile Breathing</t>
+          <t>90/90 Breathing</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -7349,12 +7362,12 @@
       <c r="F157" s="1" t="str"/>
       <c r="G157" s="1" t="inlineStr">
         <is>
-          <t>Face down, breathe into the belly.</t>
+          <t>Knees and hips at 90, exhale fully.</t>
         </is>
       </c>
       <c r="H157" s="1" t="inlineStr">
         <is>
-          <t>Feel the floor push back on the exhale.</t>
+          <t>Pause at the bottom of each breath.</t>
         </is>
       </c>
       <c r="K157" s="5" t="n"/>
@@ -7367,7 +7380,7 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>Box Breathing</t>
+          <t>Crocodile Breathing</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -7388,12 +7401,12 @@
       <c r="F158" s="1" t="str"/>
       <c r="G158" s="1" t="inlineStr">
         <is>
-          <t>Four counts in, hold, out, hold.</t>
+          <t>Face down, breathe into the belly.</t>
         </is>
       </c>
       <c r="H158" s="1" t="inlineStr">
         <is>
-          <t>Stay relaxed, find the rhythm.</t>
+          <t>Feel the floor push back on the exhale.</t>
         </is>
       </c>
       <c r="K158" s="5" t="n"/>
@@ -7406,7 +7419,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>Child's Pose with Breathing</t>
+          <t>Box Breathing</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -7427,12 +7440,12 @@
       <c r="F159" s="1" t="str"/>
       <c r="G159" s="1" t="inlineStr">
         <is>
-          <t>Sink back onto the heels, arms long.</t>
+          <t>Four counts in, hold, out, hold.</t>
         </is>
       </c>
       <c r="H159" s="1" t="inlineStr">
         <is>
-          <t>Slow breaths into the back.</t>
+          <t>Stay relaxed, find the rhythm.</t>
         </is>
       </c>
       <c r="K159" s="5" t="n"/>
@@ -7440,12 +7453,12 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>Conditioning</t>
+          <t>Breathing reset</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>Sprint Intervals</t>
+          <t>Child's Pose with Breathing</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -7460,22 +7473,18 @@
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F160" s="1" t="inlineStr">
-        <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F160" s="1" t="str"/>
       <c r="G160" s="1" t="inlineStr">
         <is>
-          <t>Drive through the ground, arms straight.</t>
+          <t>Sink back onto the heels, arms long.</t>
         </is>
       </c>
       <c r="H160" s="1" t="inlineStr">
         <is>
-          <t>Full recovery between efforts.</t>
+          <t>Slow breaths into the back.</t>
         </is>
       </c>
       <c r="K160" s="5" t="n"/>
@@ -7488,7 +7497,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>Hill Sprints</t>
+          <t>Sprint Intervals</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -7513,12 +7522,12 @@
       </c>
       <c r="G161" s="1" t="inlineStr">
         <is>
-          <t>Drive the knees, lean into the hill.</t>
+          <t>Drive through the ground, arms straight.</t>
         </is>
       </c>
       <c r="H161" s="1" t="inlineStr">
         <is>
-          <t>Walk back for full recovery.</t>
+          <t>Full recovery between efforts.</t>
         </is>
       </c>
       <c r="K161" s="5" t="n"/>
@@ -7531,7 +7540,7 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>Quality Sprints</t>
+          <t>Hill Sprints</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -7556,12 +7565,12 @@
       </c>
       <c r="G162" s="1" t="inlineStr">
         <is>
-          <t>Max intent every rep, full recovery between.</t>
+          <t>Drive the knees, lean into the hill.</t>
         </is>
       </c>
       <c r="H162" s="1" t="inlineStr">
         <is>
-          <t>If speed drops, the set is done.</t>
+          <t>Walk back for full recovery.</t>
         </is>
       </c>
       <c r="K162" s="5" t="n"/>
@@ -7574,7 +7583,7 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>MAS Training</t>
+          <t>Quality Sprints</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -7599,10 +7608,14 @@
       </c>
       <c r="G163" s="1" t="inlineStr">
         <is>
-          <t>PENDING — Stage B</t>
-        </is>
-      </c>
-      <c r="H163" s="1" t="str"/>
+          <t>Max intent every rep, full recovery between.</t>
+        </is>
+      </c>
+      <c r="H163" s="1" t="inlineStr">
+        <is>
+          <t>If speed drops, the set is done.</t>
+        </is>
+      </c>
       <c r="K163" s="5" t="n"/>
     </row>
     <row r="164">
@@ -7613,7 +7626,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>Flying Sprints</t>
+          <t>MAS Training</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -7633,7 +7646,7 @@
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
       <c r="G164" s="1" t="inlineStr">
@@ -7652,7 +7665,7 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>MAS 15:15 Blocks</t>
+          <t>Flying Sprints</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -7691,7 +7704,7 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>Tabata Intervals</t>
+          <t>MAS 15:15 Blocks</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -7706,12 +7719,12 @@
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
       <c r="G166" s="1" t="inlineStr">
@@ -7730,7 +7743,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>Inverse Tabata</t>
+          <t>Tabata Intervals</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -7769,7 +7782,7 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>Max Effort Sprint Accumulation</t>
+          <t>Inverse Tabata</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -7808,7 +7821,7 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>Free Sprint Session</t>
+          <t>Max Effort Sprint Accumulation</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -7823,12 +7836,12 @@
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
       <c r="G169" s="1" t="inlineStr">
@@ -7847,7 +7860,7 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>Long Run</t>
+          <t>Free Sprint Session</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -7862,24 +7875,20 @@
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
       <c r="G170" s="1" t="inlineStr">
         <is>
-          <t>Steady aerobic pace, find your rhythm.</t>
-        </is>
-      </c>
-      <c r="H170" s="1" t="inlineStr">
-        <is>
-          <t>Settle in, breathe steadily.</t>
-        </is>
-      </c>
+          <t>PENDING — Stage B</t>
+        </is>
+      </c>
+      <c r="H170" s="1" t="str"/>
       <c r="K170" s="5" t="n"/>
     </row>
     <row r="171">
@@ -7890,7 +7899,7 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>6x1km</t>
+          <t>Long Run</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -7915,10 +7924,14 @@
       </c>
       <c r="G171" s="1" t="inlineStr">
         <is>
-          <t>PENDING — Stage B</t>
-        </is>
-      </c>
-      <c r="H171" s="1" t="str"/>
+          <t>Steady aerobic pace, find your rhythm.</t>
+        </is>
+      </c>
+      <c r="H171" s="1" t="inlineStr">
+        <is>
+          <t>Settle in, breathe steadily.</t>
+        </is>
+      </c>
       <c r="K171" s="5" t="n"/>
     </row>
     <row r="172">
@@ -7929,7 +7942,7 @@
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>1km Repeat Intervals</t>
+          <t>6x1km</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -7968,7 +7981,7 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>4x4 VO2</t>
+          <t>1km Repeat Intervals</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -8007,7 +8020,7 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>200m/400m Repeat Runs</t>
+          <t>4x4 VO2</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -8022,12 +8035,12 @@
       </c>
       <c r="E174" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F174" s="1" t="inlineStr">
         <is>
-          <t>⚑ sprint-adjacent speed endurance at high impact — the training-age ladder is a rough fit for a session format.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
       <c r="G174" s="1" t="inlineStr">
@@ -8046,7 +8059,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>Footy Fartlek</t>
+          <t>200m/400m Repeat Runs</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -8061,12 +8074,12 @@
       </c>
       <c r="E175" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F175" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ sprint-adjacent speed endurance at high impact — the training-age ladder is a rough fit for a session format.</t>
         </is>
       </c>
       <c r="G175" s="1" t="inlineStr">
@@ -8085,7 +8098,7 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>Hard Row Intervals</t>
+          <t>Footy Fartlek</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -8124,7 +8137,7 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>Hard SkiErg Intervals</t>
+          <t>Hard Row Intervals</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -8163,7 +8176,7 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>Hard Assault Bike Intervals</t>
+          <t>Hard SkiErg Intervals</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -8202,7 +8215,7 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>Erg EMOM</t>
+          <t>Hard Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -8227,7 +8240,7 @@
       </c>
       <c r="G179" s="1" t="inlineStr">
         <is>
-          <t>Hit X number of calories every minute, the faster you do them the more rest you get.</t>
+          <t>PENDING — Stage B</t>
         </is>
       </c>
       <c r="H179" s="1" t="str"/>
@@ -8241,7 +8254,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>Tempo Run</t>
+          <t>Erg EMOM</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -8266,14 +8279,10 @@
       </c>
       <c r="G180" s="1" t="inlineStr">
         <is>
-          <t>Hold the pace, settle into the rhythm.</t>
-        </is>
-      </c>
-      <c r="H180" s="1" t="inlineStr">
-        <is>
-          <t>Controlled breathing throughout.</t>
-        </is>
-      </c>
+          <t>Hit X number of calories every minute, the faster you do them the more rest you get.</t>
+        </is>
+      </c>
+      <c r="H180" s="1" t="str"/>
       <c r="K180" s="5" t="n"/>
     </row>
     <row r="181">
@@ -8284,7 +8293,7 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>Long Nasal Run</t>
+          <t>Tempo Run</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -8309,10 +8318,14 @@
       </c>
       <c r="G181" s="1" t="inlineStr">
         <is>
-          <t>PENDING — Stage B</t>
-        </is>
-      </c>
-      <c r="H181" s="1" t="str"/>
+          <t>Hold the pace, settle into the rhythm.</t>
+        </is>
+      </c>
+      <c r="H181" s="1" t="inlineStr">
+        <is>
+          <t>Controlled breathing throughout.</t>
+        </is>
+      </c>
       <c r="K181" s="5" t="n"/>
     </row>
     <row r="182">
@@ -8323,7 +8336,7 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>30:30 Tempo Blocks</t>
+          <t>Long Nasal Run</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -8362,7 +8375,7 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>Tempo Intervals (1min on / 1min easy)</t>
+          <t>30:30 Tempo Blocks</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -8401,7 +8414,7 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>Cruise Intervals</t>
+          <t>Tempo Intervals (1min on / 1min easy)</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -8440,7 +8453,7 @@
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>Bike/Row/Ski Tempo Intervals</t>
+          <t>Cruise Intervals</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -8479,7 +8492,7 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>Air Bike Sprints</t>
+          <t>Bike/Row/Ski Tempo Intervals</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -8504,14 +8517,10 @@
       </c>
       <c r="G186" s="1" t="inlineStr">
         <is>
-          <t>Explosive effort.</t>
-        </is>
-      </c>
-      <c r="H186" s="1" t="inlineStr">
-        <is>
-          <t>Recover fully between sprints.</t>
-        </is>
-      </c>
+          <t>PENDING — Stage B</t>
+        </is>
+      </c>
+      <c r="H186" s="1" t="str"/>
       <c r="K186" s="5" t="n"/>
     </row>
     <row r="187">
@@ -8522,7 +8531,7 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>Row Intervals</t>
+          <t>Air Bike Sprints</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -8547,12 +8556,12 @@
       </c>
       <c r="G187" s="1" t="inlineStr">
         <is>
-          <t>Full catch, explosive drive.</t>
+          <t>Explosive effort.</t>
         </is>
       </c>
       <c r="H187" s="1" t="inlineStr">
         <is>
-          <t>Maintain power, recover completely.</t>
+          <t>Recover fully between sprints.</t>
         </is>
       </c>
       <c r="K187" s="5" t="n"/>
@@ -8565,7 +8574,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>SkiErg Intervals</t>
+          <t>Row Intervals</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -8590,10 +8599,14 @@
       </c>
       <c r="G188" s="1" t="inlineStr">
         <is>
-          <t>PENDING — Stage B</t>
-        </is>
-      </c>
-      <c r="H188" s="1" t="str"/>
+          <t>Full catch, explosive drive.</t>
+        </is>
+      </c>
+      <c r="H188" s="1" t="inlineStr">
+        <is>
+          <t>Maintain power, recover completely.</t>
+        </is>
+      </c>
       <c r="K188" s="5" t="n"/>
     </row>
     <row r="189">
@@ -8604,7 +8617,7 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>Assault Bike Intervals</t>
+          <t>SkiErg Intervals</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -8643,7 +8656,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>Flush Run</t>
+          <t>Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -8668,14 +8681,10 @@
       </c>
       <c r="G190" s="1" t="inlineStr">
         <is>
-          <t>Easy jog, nothing above zone one or two.</t>
-        </is>
-      </c>
-      <c r="H190" s="1" t="inlineStr">
-        <is>
-          <t>Move and loosen up.</t>
-        </is>
-      </c>
+          <t>PENDING — Stage B</t>
+        </is>
+      </c>
+      <c r="H190" s="1" t="str"/>
       <c r="K190" s="5" t="n"/>
     </row>
     <row r="191">
@@ -8686,7 +8695,7 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>Easy Bike</t>
+          <t>Flush Run</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -8711,12 +8720,12 @@
       </c>
       <c r="G191" s="1" t="inlineStr">
         <is>
-          <t>Conversational pace, legs turning over.</t>
+          <t>Easy jog, nothing above zone one or two.</t>
         </is>
       </c>
       <c r="H191" s="1" t="inlineStr">
         <is>
-          <t>This is recovery, not training.</t>
+          <t>Move and loosen up.</t>
         </is>
       </c>
       <c r="K191" s="5" t="n"/>
@@ -8729,7 +8738,7 @@
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>Easy Row</t>
+          <t>Easy Bike</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -8754,12 +8763,12 @@
       </c>
       <c r="G192" s="1" t="inlineStr">
         <is>
-          <t>Controlled rhythm, long strokes.</t>
+          <t>Conversational pace, legs turning over.</t>
         </is>
       </c>
       <c r="H192" s="1" t="inlineStr">
         <is>
-          <t>This is active recovery, not training.</t>
+          <t>This is recovery, not training.</t>
         </is>
       </c>
       <c r="K192" s="5" t="n"/>
@@ -8772,7 +8781,7 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>Easy Ski</t>
+          <t>Easy Row</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -8797,12 +8806,12 @@
       </c>
       <c r="G193" s="1" t="inlineStr">
         <is>
-          <t>Smooth technique, conversational pace.</t>
+          <t>Controlled rhythm, long strokes.</t>
         </is>
       </c>
       <c r="H193" s="1" t="inlineStr">
         <is>
-          <t>Focus on form, not intensity.</t>
+          <t>This is active recovery, not training.</t>
         </is>
       </c>
       <c r="K193" s="5" t="n"/>
@@ -8815,7 +8824,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>Easy Swim</t>
+          <t>Easy Ski</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -8840,10 +8849,14 @@
       </c>
       <c r="G194" s="1" t="inlineStr">
         <is>
-          <t>PENDING — Stage B</t>
-        </is>
-      </c>
-      <c r="H194" s="1" t="str"/>
+          <t>Smooth technique, conversational pace.</t>
+        </is>
+      </c>
+      <c r="H194" s="1" t="inlineStr">
+        <is>
+          <t>Focus on form, not intensity.</t>
+        </is>
+      </c>
       <c r="K194" s="5" t="n"/>
     </row>
     <row r="195">
@@ -8854,7 +8867,7 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>Light Circuits</t>
+          <t>Easy Swim</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -8879,14 +8892,10 @@
       </c>
       <c r="G195" s="1" t="inlineStr">
         <is>
-          <t>Low intensity rounds, controlled transitions.</t>
-        </is>
-      </c>
-      <c r="H195" s="1" t="inlineStr">
-        <is>
-          <t>This is recovery, not intensity.</t>
-        </is>
-      </c>
+          <t>PENDING — Stage B</t>
+        </is>
+      </c>
+      <c r="H195" s="1" t="str"/>
       <c r="K195" s="5" t="n"/>
     </row>
     <row r="196">
@@ -8897,127 +8906,126 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
+          <t>Light Circuits</t>
+        </is>
+      </c>
+      <c r="C196" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E196" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F196" s="1" t="inlineStr">
+        <is>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
+        </is>
+      </c>
+      <c r="G196" s="1" t="inlineStr">
+        <is>
+          <t>Low intensity rounds, controlled transitions.</t>
+        </is>
+      </c>
+      <c r="H196" s="1" t="inlineStr">
+        <is>
+          <t>This is recovery, not intensity.</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="B197" s="1" t="inlineStr">
+        <is>
           <t>2km Time Trial</t>
         </is>
       </c>
-      <c r="C196" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D196" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E196" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F196" s="1" t="inlineStr">
+      <c r="C197" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D197" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E197" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F197" s="1" t="inlineStr">
         <is>
           <t>session format, not an individual movement — no meaningful muscle group. A TEST, not a dose (Sam, D14 2026-07-29): it lives outside the 55 conditioning rows and has no conditioning-sheet entry.</t>
         </is>
       </c>
-      <c r="G196" s="1" t="inlineStr">
+      <c r="G197" s="1" t="inlineStr">
         <is>
           <t>Try to run this at the same pace for the entire 2km</t>
         </is>
       </c>
-      <c r="H196" s="1" t="str"/>
-      <c r="K196" s="5" t="n"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="1" t="n"/>
-      <c r="B197" s="1" t="n"/>
-      <c r="C197" s="1" t="n"/>
-      <c r="D197" s="1" t="n"/>
-      <c r="E197" s="1" t="n"/>
-      <c r="F197" s="1" t="n"/>
-      <c r="G197" s="1" t="n"/>
+      <c r="H197" s="1" t="str"/>
       <c r="K197" s="5" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="1" t="n"/>
+      <c r="B198" s="1" t="n"/>
+      <c r="C198" s="1" t="n"/>
+      <c r="D198" s="1" t="n"/>
+      <c r="E198" s="1" t="n"/>
+      <c r="F198" s="1" t="n"/>
+      <c r="G198" s="1" t="n"/>
+      <c r="K198" s="5" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>Vertical Jump</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="C199" t="inlineStr">
         <is>
           <t>Glutes, Quads, Calves</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>Hamstrings, Midline</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
         <is>
           <t>Every rep fast and sharp. Land soft in athletic stance.</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
+      <c r="H199" t="inlineStr">
         <is>
           <t>Stop if reps get slow.</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>sagittal</t>
-        </is>
-      </c>
-      <c r="K198" s="5" t="n"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="1" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="B199" s="1" t="inlineStr">
-        <is>
-          <t>Pogo Hops</t>
-        </is>
-      </c>
-      <c r="C199" s="1" t="inlineStr">
-        <is>
-          <t>Calves</t>
-        </is>
-      </c>
-      <c r="D199" s="1" t="inlineStr">
-        <is>
-          <t>Quads, Midline</t>
-        </is>
-      </c>
-      <c r="E199" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F199" s="1" t="inlineStr">
-        <is>
-          <t>takes over when lower niggle (your spec)</t>
-        </is>
-      </c>
-      <c r="G199" s="1" t="inlineStr">
-        <is>
-          <t>Stand tall, jump and then bounce off the balls of your feet.</t>
-        </is>
-      </c>
-      <c r="H199" s="1" t="str"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>sagittal</t>
@@ -9033,17 +9041,17 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>Lateral Jump</t>
+          <t>Pogo Hops</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Outer hip</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t>Quads, Calves, Midline</t>
+          <t>Quads, Midline</t>
         </is>
       </c>
       <c r="E200" s="1" t="inlineStr">
@@ -9053,23 +9061,18 @@
       </c>
       <c r="F200" s="1" t="inlineStr">
         <is>
-          <t>your spec: beginner friendly</t>
+          <t>takes over when lower niggle (your spec)</t>
         </is>
       </c>
       <c r="G200" s="1" t="inlineStr">
         <is>
-          <t>Jump off outside leg to the side, turn in air and land in a squat.</t>
+          <t>Stand tall, jump and then bounce off the balls of your feet.</t>
         </is>
       </c>
       <c r="H200" s="1" t="str"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>frontal</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>transverse</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K200" s="5" t="n"/>
@@ -9082,38 +9085,43 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>Kneeling Jump</t>
+          <t>Lateral Jump</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Quads</t>
+          <t>Glutes, Outer hip</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Midline</t>
+          <t>Quads, Calves, Midline</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F201" s="1" t="inlineStr">
         <is>
-          <t>your spec: consistent+</t>
+          <t>your spec: beginner friendly</t>
         </is>
       </c>
       <c r="G201" s="1" t="inlineStr">
         <is>
-          <t>Start in kneeling position, jump onto feet, land in a squat.</t>
+          <t>Jump off outside leg to the side, turn in air and land in a squat.</t>
         </is>
       </c>
       <c r="H201" s="1" t="str"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>frontal</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>transverse</t>
         </is>
       </c>
       <c r="K201" s="5" t="n"/>
@@ -9126,17 +9134,17 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>RFE Split Squat Jump</t>
+          <t>Kneeling Jump</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>Quads, Glutes</t>
+          <t>Glutes, Quads</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Calves, Midline</t>
+          <t>Hamstrings, Midline</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
@@ -9146,27 +9154,18 @@
       </c>
       <c r="F202" s="1" t="inlineStr">
         <is>
-          <t>Auto lower power. Bench; 2+ years. Not in-season or near games.</t>
+          <t>your spec: consistent+</t>
         </is>
       </c>
       <c r="G202" s="1" t="inlineStr">
         <is>
-          <t>Back foot on bench, slight lean forward, jump straight up off the front leg.</t>
-        </is>
-      </c>
-      <c r="H202" s="1" t="inlineStr">
-        <is>
-          <t>Land soft and controlled.</t>
-        </is>
-      </c>
+          <t>Start in kneeling position, jump onto feet, land in a squat.</t>
+        </is>
+      </c>
+      <c r="H202" s="1" t="str"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>sagittal</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>frontal, transverse</t>
         </is>
       </c>
       <c r="K202" s="5" t="n"/>
@@ -9179,43 +9178,47 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>Explosive Push-up</t>
+          <t>RFE Split Squat Jump</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>Chest, Triceps</t>
+          <t>Quads, Glutes</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Midline</t>
+          <t>Hamstrings, Calves, Midline</t>
         </is>
       </c>
       <c r="E203" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="str"/>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F203" s="1" t="inlineStr">
+        <is>
+          <t>Auto lower power. Bench; 2+ years. Not in-season or near games.</t>
+        </is>
+      </c>
       <c r="G203" s="1" t="inlineStr">
         <is>
-          <t>Explode up, hands leave the floor. Land soft.</t>
+          <t>Back foot on bench, slight lean forward, jump straight up off the front leg.</t>
         </is>
       </c>
       <c r="H203" s="1" t="inlineStr">
         <is>
-          <t>Stop when reps slow. Sore wrists? Elevate hands on box.</t>
+          <t>Land soft and controlled.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>transverse</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>frontal, transverse</t>
         </is>
       </c>
       <c r="K203" s="5" t="n"/>
@@ -9228,7 +9231,7 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>Speed Bench</t>
+          <t>Explosive Push-up</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
@@ -9238,27 +9241,33 @@
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Lats</t>
+          <t>Shoulders, Midline</t>
         </is>
       </c>
       <c r="E204" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F204" s="1" t="inlineStr">
-        <is>
-          <t>FLAG — gate proposed, confirm</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="str"/>
       <c r="G204" s="1" t="inlineStr">
         <is>
-          <t>Light load, explosive intent, pause at chest.</t>
+          <t>Explode up, hands leave the floor. Land soft.</t>
         </is>
       </c>
       <c r="H204" s="1" t="inlineStr">
         <is>
-          <t>Drive hard, fast lockout.</t>
+          <t>Stop when reps slow. Sore wrists? Elevate hands on box.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>transverse</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K204" s="5" t="n"/>
@@ -9271,17 +9280,17 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>Speed Trap Bar Deadlift</t>
+          <t>Speed Bench</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Hamstrings</t>
+          <t>Chest, Triceps</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr">
         <is>
-          <t>Quads, Upper back, Grip</t>
+          <t>Shoulders, Lats</t>
         </is>
       </c>
       <c r="E205" s="1" t="inlineStr">
@@ -9289,104 +9298,103 @@
           <t>2+ years</t>
         </is>
       </c>
-      <c r="F205" s="3" t="inlineStr">
+      <c r="F205" s="1" t="inlineStr">
         <is>
           <t>FLAG — gate proposed, confirm</t>
         </is>
       </c>
       <c r="G205" s="1" t="inlineStr">
         <is>
-          <t>Wrap band around each side of bar, stand on band, get tight, explode up, control down.</t>
-        </is>
-      </c>
-      <c r="H205" s="1" t="str"/>
+          <t>Light load, explosive intent, pause at chest.</t>
+        </is>
+      </c>
+      <c r="H205" s="1" t="inlineStr">
+        <is>
+          <t>Drive hard, fast lockout.</t>
+        </is>
+      </c>
       <c r="K205" s="5" t="n"/>
     </row>
     <row r="206" ht="70" customHeight="1">
       <c r="A206" s="1" t="inlineStr">
         <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B206" s="1" t="inlineStr">
+        <is>
+          <t>Speed Trap Bar Deadlift</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="inlineStr">
+        <is>
+          <t>Glutes, Hamstrings</t>
+        </is>
+      </c>
+      <c r="D206" s="1" t="inlineStr">
+        <is>
+          <t>Quads, Upper back, Grip</t>
+        </is>
+      </c>
+      <c r="E206" s="1" t="inlineStr">
+        <is>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>FLAG — gate proposed, confirm</t>
+        </is>
+      </c>
+      <c r="G206" s="1" t="inlineStr">
+        <is>
+          <t>Wrap band around each side of bar, stand on band, get tight, explode up, control down.</t>
+        </is>
+      </c>
+      <c r="H206" s="1" t="str"/>
+      <c r="K206" s="5" t="n"/>
+    </row>
+    <row r="207" ht="70" customHeight="1">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
           <t>Lower prehab</t>
         </is>
       </c>
-      <c r="B206" s="1" t="inlineStr">
+      <c r="B207" s="1" t="inlineStr">
         <is>
           <t>Seated Single-Leg Pike Lift</t>
         </is>
       </c>
-      <c r="C206" s="1" t="inlineStr">
+      <c r="C207" s="1" t="inlineStr">
         <is>
           <t>Hip flexors</t>
         </is>
       </c>
-      <c r="D206" s="1" t="inlineStr">
+      <c r="D207" s="1" t="inlineStr">
         <is>
           <t>Quads, Midline</t>
         </is>
       </c>
-      <c r="E206" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F206" s="3" t="inlineStr">
+      <c r="E207" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
         <is>
           <t>Hold each rep for 2 seconds. Bodyweight.</t>
         </is>
       </c>
-      <c r="G206" s="1" t="inlineStr">
+      <c r="G207" s="1" t="inlineStr">
         <is>
           <t>Lean slightly forward, lock the knee, and lift the heel.</t>
         </is>
       </c>
-      <c r="H206" s="1" t="inlineStr">
+      <c r="H207" s="1" t="inlineStr">
         <is>
           <t>Pause at the top.</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>sagittal</t>
-        </is>
-      </c>
-      <c r="K206" s="5" t="n"/>
-    </row>
-    <row r="207" ht="70" customHeight="1">
-      <c r="A207" s="5" t="inlineStr">
-        <is>
-          <t>Lower prehab</t>
-        </is>
-      </c>
-      <c r="B207" s="5" t="inlineStr">
-        <is>
-          <t>Standing Knee Extension</t>
-        </is>
-      </c>
-      <c r="C207" s="5" t="inlineStr">
-        <is>
-          <t>Quads, Hip flexors</t>
-        </is>
-      </c>
-      <c r="D207" s="5" t="inlineStr">
-        <is>
-          <t>Midline, Glutes</t>
-        </is>
-      </c>
-      <c r="E207" s="5" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F207" s="5" t="inlineStr">
-        <is>
-          <t>Squeeze for 5 seconds each rep. Bodyweight.</t>
-        </is>
-      </c>
-      <c r="G207" s="5" t="inlineStr">
-        <is>
-          <t>Stand tall, lift one knee to 90 degrees, then straighten your leg.</t>
-        </is>
-      </c>
-      <c r="H207" s="5" t="str"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>sagittal</t>
@@ -9397,22 +9405,22 @@
     <row r="208" ht="70" customHeight="1">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>Lower prehab</t>
         </is>
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>Crab Hold</t>
+          <t>Standing Knee Extension</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>Shoulders, Glutes, Triceps</t>
+          <t>Quads, Hip flexors</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>Hamstrings, Chest, Upper back, Midline</t>
+          <t>Midline, Glutes</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -9422,17 +9430,18 @@
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>Hold with an open chest. Bodyweight. Familiar and pain-free near games.</t>
+          <t>Squeeze for 5 seconds each rep. Bodyweight.</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>Press through hands and feet, then lift the hips high.</t>
-        </is>
-      </c>
-      <c r="H208" s="5" t="inlineStr">
-        <is>
-          <t>Keep the chest open and hold.</t>
+          <t>Stand tall, lift one knee to 90 degrees, then straighten your leg.</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="str"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K208" s="5" t="n"/>
@@ -9445,17 +9454,17 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>Seated Good Morning</t>
+          <t>Crab Hold</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>Low back, Groin</t>
+          <t>Shoulders, Glutes, Triceps</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>Hamstrings, Glutes, Midline, Upper back</t>
+          <t>Hamstrings, Chest, Upper back, Midline</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
@@ -9465,17 +9474,17 @@
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>Lower for 5 seconds. Bodyweight for everyone; dumbbell and barbell variants require 1+ years. Log total external load. Mobility only; never a main lift.</t>
+          <t>Hold with an open chest. Bodyweight. Familiar and pain-free near games.</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>Sit wide, brace, and hinge forward from the hips.</t>
+          <t>Press through hands and feet, then lift the hips high.</t>
         </is>
       </c>
       <c r="H209" s="5" t="inlineStr">
         <is>
-          <t>Don't round the spine.</t>
+          <t>Keep the chest open and hold.</t>
         </is>
       </c>
       <c r="K209" s="5" t="n"/>
@@ -9483,52 +9492,42 @@
     <row r="210" ht="70" customHeight="1">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>Lower hinge</t>
+          <t>Mobility</t>
         </is>
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>SL 45° Back Extension</t>
+          <t>Seated Good Morning</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>Glutes, Hamstrings</t>
+          <t>Low back, Groin</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>Low back, Midline</t>
+          <t>Hamstrings, Glutes, Midline, Upper back</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>Start with bodyweight. Optional plate or dumbbell at chest; log total external load. Caution two days before a game.</t>
+          <t>Lower for 5 seconds. Bodyweight for everyone; dumbbell and barbell variants require 1+ years. Log total external load. Mobility only; never a main lift.</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>Hinge over the pad, then drive through the working hip.</t>
+          <t>Sit wide, brace, and hinge forward from the hips.</t>
         </is>
       </c>
       <c r="H210" s="5" t="inlineStr">
         <is>
-          <t>Keep the hips square and finish without arching the lower back.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>sagittal</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>frontal, transverse</t>
+          <t>Don't round the spine.</t>
         </is>
       </c>
       <c r="K210" s="5" t="n"/>
@@ -9536,17 +9535,17 @@
     <row r="211" ht="70" customHeight="1">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>Lower prehab</t>
+          <t>Lower hinge</t>
         </is>
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>SL 45° Back Extension Hold</t>
+          <t>SL 45° Back Extension</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>Hamstrings, Glutes</t>
+          <t>Glutes, Hamstrings</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
@@ -9561,17 +9560,17 @@
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>Short submaximal holds near games; never maximum duration. Start bodyweight; optional plate or dumbbell at chest, total external load.</t>
+          <t>Start with bodyweight. Optional plate or dumbbell at chest; log total external load. Caution two days before a game.</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>Hold a straight line using the glute and hamstring.</t>
+          <t>Hinge over the pad, then drive through the working hip.</t>
         </is>
       </c>
       <c r="H211" s="5" t="inlineStr">
         <is>
-          <t>Keep the hips square and avoid hanging through the lower back.</t>
+          <t>Keep the hips square and finish without arching the lower back.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -9594,17 +9593,17 @@
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>Reverse Nordic Curl</t>
+          <t>SL 45° Back Extension Hold</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>Quads</t>
+          <t>Hamstrings, Glutes</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Low back, Midline</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
@@ -9614,22 +9613,27 @@
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>Lower for 5 seconds. Bodyweight; beginners use shallow range or band assistance. External loading not yet specified.</t>
+          <t>Short submaximal holds near games; never maximum duration. Start bodyweight; optional plate or dumbbell at chest, total external load.</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>Squeeze the glutes and lean back from the knees.</t>
+          <t>Hold a straight line using the glute and hamstring.</t>
         </is>
       </c>
       <c r="H212" s="5" t="inlineStr">
         <is>
-          <t>Keep knees, hips, and shoulders in one straight line.</t>
+          <t>Keep the hips square and avoid hanging through the lower back.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
           <t>sagittal</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>frontal, transverse</t>
         </is>
       </c>
       <c r="K212" s="5" t="n"/>
@@ -9637,22 +9641,22 @@
     <row r="213" ht="70" customHeight="1">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Lower prehab</t>
         </is>
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>Rotational Medicine-Ball Throw</t>
+          <t>Reverse Nordic Curl</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>Midline, Glutes, Hips</t>
+          <t>Quads</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>Chest, Shoulders, Triceps, Calves</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
@@ -9662,21 +9666,20 @@
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>Use a wall-throw ball. Start around 2–4 kg; log total ball weight. Fast reps with complete recovery.</t>
+          <t>Lower for 5 seconds. Bodyweight; beginners use shallow range or band assistance. External loading not yet specified.</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Load the outside hip, rotate hard, and throw through the wall.</t>
-        </is>
-      </c>
-      <c r="H213" s="5" t="str"/>
+          <t>Squeeze the glutes and lean back from the knees.</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="inlineStr">
+        <is>
+          <t>Keep knees, hips, and shoulders in one straight line.</t>
+        </is>
+      </c>
       <c r="I213" t="inlineStr">
-        <is>
-          <t>transverse</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
         <is>
           <t>sagittal</t>
         </is>
@@ -9691,40 +9694,41 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>Medicine-Ball Slam</t>
+          <t>Rotational Medicine-Ball Throw</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>Lats, Midline, Shoulders</t>
+          <t>Midline, Glutes, Hips</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Triceps, Glutes, Quads, Hamstrings, Calves</t>
+          <t>Chest, Shoulders, Triceps, Calves</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>Start around 3–6 kg; log total ball weight. Low-volume power only near games. Stop if speed drops.</t>
+          <t>Use a wall-throw ball. Start around 2–4 kg; log total ball weight. Fast reps with complete recovery.</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Reach tall onto toes and slam the ball straight down.</t>
-        </is>
-      </c>
-      <c r="H214" s="5" t="inlineStr">
-        <is>
-          <t>Finish athletically with the hips and knees softly bent.</t>
-        </is>
-      </c>
+          <t>Load the outside hip, rotate hard, and throw through the wall.</t>
+        </is>
+      </c>
+      <c r="H214" s="5" t="str"/>
       <c r="I214" t="inlineStr">
+        <is>
+          <t>transverse</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
         <is>
           <t>sagittal</t>
         </is>
@@ -9739,45 +9743,40 @@
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>Rotational Medicine-Ball Slam</t>
+          <t>Medicine-Ball Slam</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>Midline, Lats, Glutes</t>
+          <t>Lats, Midline, Shoulders</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>Shoulders, Triceps, Hips, Quads, Calves</t>
+          <t>Triceps, Glutes, Quads, Hamstrings, Calves</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>Start around 3–6 kg; log total ball weight. Reset each rep. Low-volume power only near games; stop if speed drops.</t>
+          <t>Start around 3–6 kg; log total ball weight. Low-volume power only near games. Stop if speed drops.</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>Reach tall onto toes, rotate hard, and slam outside the foot.</t>
+          <t>Reach tall onto toes and slam the ball straight down.</t>
         </is>
       </c>
       <c r="H215" s="5" t="inlineStr">
         <is>
-          <t>Reset before each explosive repetition.</t>
+          <t>Finish athletically with the hips and knees softly bent.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
-        <is>
-          <t>transverse</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
         <is>
           <t>sagittal</t>
         </is>
@@ -9787,42 +9786,52 @@
     <row r="216" ht="70" customHeight="1">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>Horse Stance Hold</t>
+          <t>Rotational Medicine-Ball Slam</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>Groin, Quads, Glutes</t>
+          <t>Midline, Lats, Glutes</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Shoulders, Triceps, Hips, Quads, Calves</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>2 × 60-second total holds. Bodyweight; use a higher or narrower stance as the beginner regression. Progress depth, stance width or duration before optional dumbbell load.</t>
+          <t>Start around 3–6 kg; log total ball weight. Reset each rep. Low-volume power only near games; stop if speed drops.</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Take a wide stance and sink straight down between your feet.</t>
+          <t>Reach tall onto toes, rotate hard, and slam outside the foot.</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
         <is>
-          <t>Push knees over toes and keep your torso tall.</t>
+          <t>Reset before each explosive repetition.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>transverse</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K216" s="5" t="n"/>
@@ -9835,17 +9844,17 @@
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>Bench Thoracic Extension</t>
+          <t>Horse Stance Hold</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>Lats, Upper back</t>
+          <t>Groin, Quads, Glutes</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>Triceps, Chest, Midline</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
@@ -9855,17 +9864,17 @@
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>Slow reps. Pause 3 seconds at the bottom. Bodyweight only; use a comfortable range near games.</t>
+          <t>2 × 60-second total holds. Bodyweight; use a higher or narrower stance as the beginner regression. Progress depth, stance width or duration before optional dumbbell load.</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Place elbows on the bench and sit your hips back.</t>
+          <t>Take a wide stance and sink straight down between your feet.</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
         <is>
-          <t>Sink your chest without arching through the lower back.</t>
+          <t>Push knees over toes and keep your torso tall.</t>
         </is>
       </c>
       <c r="K217" s="5" t="n"/>
@@ -9878,17 +9887,17 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>Sleeper Stretch</t>
+          <t>Bench Thoracic Extension</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Lats, Upper back</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Triceps, Chest, Midline</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
@@ -9898,17 +9907,17 @@
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>Gentle pressure from the opposite hand; no external loading or bouncing. Use short, comfortable holds near games and avoid aggressive holds before throwing, pressing or contact.</t>
+          <t>Slow reps. Pause 3 seconds at the bottom. Bodyweight only; use a comfortable range near games.</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Lie on the target shoulder and gently lower the forearm.</t>
+          <t>Place elbows on the bench and sit your hips back.</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
         <is>
-          <t>Stop at a mild stretch behind the shoulder, never the front.</t>
+          <t>Sink your chest without arching through the lower back.</t>
         </is>
       </c>
       <c r="K218" s="5" t="n"/>
@@ -9921,17 +9930,17 @@
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>Foam Roller Thoracic Extension</t>
+          <t>Sleeper Stretch</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>Lats, Upper back</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Chest, Triceps, Shoulders, Midline</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
@@ -9941,17 +9950,17 @@
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>Pause 5 seconds overhead. Foam roller required. Hold one light dumbbell or weight plate in both hands; record total load. Beginners may use no weight. Mobility only; the weight assists the stretch.</t>
+          <t>Gentle pressure from the opposite hand; no external loading or bouncing. Use short, comfortable holds near games and avoid aggressive holds before throwing, pressing or contact.</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Reach the weight overhead as your upper back extends.</t>
+          <t>Lie on the target shoulder and gently lower the forearm.</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
         <is>
-          <t>Keep ribs tucked and avoid arching through the lower back.</t>
+          <t>Stop at a mild stretch behind the shoulder, never the front.</t>
         </is>
       </c>
       <c r="K219" s="5" t="n"/>
@@ -9959,52 +9968,42 @@
     <row r="220" ht="72" customHeight="1">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>Upper pull vertical</t>
+          <t>Mobility</t>
         </is>
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>Band-Assisted Pull-Up</t>
+          <t>Foam Roller Thoracic Extension</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>Lats, Biceps, Upper back</t>
+          <t>Lats, Upper back</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Shoulders, Grip, Midline</t>
+          <t>Chest, Triceps, Shoulders, Midline</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>Automatic regression and manual Swap from Pull-Ups only. Eligible for all complete beginners and female athletes at 1–2 years. Requires a resistance band plus a rack or pull-up bar. Record band strength or colour and support height; reduce assistance to progress. Inherits Pull-Up sets, reps and role. All phases; suitable near games.</t>
+          <t>Pause 5 seconds overhead. Foam roller required. Hold one light dumbbell or weight plate in both hands; record total load. Beginners may use no weight. Mobility only; the weight assists the stretch.</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Stand firmly on the band and pull your chest toward the bar.</t>
+          <t>Reach the weight overhead as your upper back extends.</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
         <is>
-          <t>Lower under control until your elbows fully straighten.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>frontal</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>sagittal</t>
+          <t>Keep ribs tucked and avoid arching through the lower back.</t>
         </is>
       </c>
       <c r="K220" s="5" t="n"/>
@@ -10012,22 +10011,22 @@
     <row r="221" ht="72" customHeight="1">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>Upper push horizontal</t>
+          <t>Upper pull vertical</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>Incline Push-Up</t>
+          <t>Band-Assisted Pull-Up</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>Chest, Triceps, Shoulders</t>
+          <t>Lats, Biceps, Upper back</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>Midline, Glutes</t>
+          <t>Shoulders, Grip, Midline</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
@@ -10037,22 +10036,22 @@
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>Automatic regression and manual Swap from Push-ups only. Eligible for all complete beginners and female athletes at 1–2 years. Requires a bench or plyo box. Bodyweight only; record support height in the session note and lower it to progress. Inherits Push-ups sets, reps and role. All phases; suitable near games.</t>
+          <t>Automatic regression and manual Swap from Pull-Ups only. Eligible for all complete beginners and female athletes at 1–2 years. Requires a resistance band plus a rack or pull-up bar. Record band strength or colour and support height; reduce assistance to progress. Inherits Pull-Up sets, reps and role. All phases; suitable near games.</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>Keep a straight body line and lower your chest to the support.</t>
+          <t>Stand firmly on the band and pull your chest toward the bar.</t>
         </is>
       </c>
       <c r="H221" s="5" t="inlineStr">
         <is>
-          <t>Press away without letting your hips sag or shoulders shrug.</t>
+          <t>Lower under control until your elbows fully straighten.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>transverse</t>
+          <t>frontal</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -10065,52 +10064,52 @@
     <row r="222" ht="72" customHeight="1">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Upper push horizontal</t>
         </is>
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>Single-Leg Hop and Stick</t>
+          <t>Incline Push-Up</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>Glutes, Quads, Calves</t>
+          <t>Chest, Triceps, Shoulders</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Hamstrings, Groin, Midline, Feet</t>
+          <t>Midline, Glutes</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>everyone (regression)</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Automatic lower power and manual Add/Swap for 2+ years only. Bodyweight; 2 × 5 per side with 120 seconds rest. All phases and in-season at low volume; never automatic at G-1. Progress hop distance only while the landing stays controlled.</t>
+          <t>Automatic regression and manual Swap from Push-ups only. Eligible for all complete beginners and female athletes at 1–2 years. Requires a bench or plyo box. Bodyweight only; record support height in the session note and lower it to progress. Inherits Push-ups sets, reps and role. All phases; suitable near games.</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>Hop forward from one leg and freeze the landing.</t>
+          <t>Keep a straight body line and lower your chest to the support.</t>
         </is>
       </c>
       <c r="H222" s="5" t="inlineStr">
         <is>
-          <t>Land quietly, absorb through the hip, and hold your balance.</t>
+          <t>Press away without letting your hips sag or shoulders shrug.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>sagittal</t>
+          <t>transverse</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>frontal, transverse</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="K222" s="5" t="n"/>
@@ -10118,51 +10117,104 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>Single-Leg Hop and Stick</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>Glutes, Quads, Calves</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>Hamstrings, Groin, Midline, Feet</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>Automatic lower power and manual Add/Swap for 2+ years only. Bodyweight; 2 × 5 per side with 120 seconds rest. All phases and in-season at low volume; never automatic at G-1. Progress hop distance only while the landing stays controlled.</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr">
+        <is>
+          <t>Hop forward from one leg and freeze the landing.</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="inlineStr">
+        <is>
+          <t>Land quietly, absorb through the hip, and hold your balance.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>frontal, transverse</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="inlineStr">
+        <is>
           <t>Shoulder health</t>
         </is>
       </c>
-      <c r="B223" s="5" t="inlineStr">
+      <c r="B224" s="5" t="inlineStr">
         <is>
           <t>Banded 90/90 External Rotation</t>
         </is>
       </c>
-      <c r="C223" s="5" t="inlineStr">
+      <c r="C224" s="5" t="inlineStr">
         <is>
           <t>Shoulders</t>
         </is>
       </c>
-      <c r="D223" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E223" s="5" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F223" s="5" t="inlineStr">
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F224" s="5" t="inlineStr">
         <is>
           <t>Band resistance. 2 × 15–20 per arm with 20 seconds rest. Automatic in Shoulder health and upper-body warm-up slots; manual Add/Swap; not automatic in Primer. All phases and suitable at G-1 when pain-free.</t>
         </is>
       </c>
-      <c r="G223" s="5" t="inlineStr">
+      <c r="G224" s="5" t="inlineStr">
         <is>
           <t>Keep your elbow level with your shoulder and rotate your forearm upward.</t>
         </is>
       </c>
-      <c r="H223" s="5" t="inlineStr">
+      <c r="H224" s="5" t="inlineStr">
         <is>
           <t>Keep ribs down; avoid shrugging or forcing the range.</t>
         </is>
       </c>
-      <c r="I223" s="5" t="inlineStr">
+      <c r="I224" s="5" t="inlineStr">
         <is>
           <t>transverse</t>
         </is>
       </c>
-      <c r="J223" s="5" t="n"/>
-      <c r="K223" s="5" t="n"/>
+      <c r="J224" s="5" t="n"/>
+      <c r="K224" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
+++ b/docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx
@@ -468,7 +468,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHANGE LOG — Sam 2026-07-27: MetCon row DELETED (the conditioning ruling retiring the name wins); Single-Arm Pulldown row ADDED (Lats / Upper back, Midline / everyone); 3 casing typos corrected as authorised edits (Suitcase Carry + Skull Crushers 'Everyone' -&gt; 'everyone', Chin-Up Negative (Slow) secondary 'midline' -&gt; 'Midline'). CHANGE LOG — 2026-07-28 cue reconciliation: renamed from MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx; primaryCue/secondaryCue columns added, making this the single authored source for coaching cues. 175 rows carry Sam-authored cues as shipped; 23 conditioning rows read "PENDING — Stage B" (unruled, NOT blessed — Sam 2026-07-28). Muscle/experience cells are untouched. CHANGE LOG — 2026-09-01 identity merge: Single-Arm Pulldown retired as a current row and retained only as a legacy read alias; cues, equipment, progression and history resolve to Single-Arm Lat Pulldown. CHANGE LOG — 2026-09-01: Seated Good Morning (Barbell) retired as a current row and retained only as legacy saved-data ingress. Seated Good Morning is the one identity; bodyweight is available to everyone, while dumbbell and barbell variants require 1+ years.; Sam 2026-09-02: SL 45° Back Extension Hold and Swiss Ball Hamstring Curl moved from Hamstring (light) into Lower prehab; the separate authored pool was retired. CHANGE LOG — Sam 2026-09-04 (R-368): B-Stance RDL ADDED to Lower hinge — "add this into the exercise list as well - so we have another single leg hip dominant lift". Third member of the single-leg hip group, which held only Single-Leg RDL and SL 45° Back Extension. Intake: docs/EXERCISE_INTAKE_B_STANCE_RDL_2026-09-04.md.</t>
+          <t>CHANGE LOG — Sam 2026-07-27: MetCon row DELETED (the conditioning ruling retiring the name wins); Single-Arm Pulldown row ADDED (Lats / Upper back, Midline / everyone); 3 casing typos corrected as authorised edits (Suitcase Carry + Skull Crushers 'Everyone' -&gt; 'everyone', Chin-Up Negative (Slow) secondary 'midline' -&gt; 'Midline'). CHANGE LOG — 2026-07-28 cue reconciliation: renamed from MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx; primaryCue/secondaryCue columns added, making this the single authored source for coaching cues. 175 rows carry Sam-authored cues as shipped; 23 conditioning rows read "PENDING — Stage B" (unruled, NOT blessed — Sam 2026-07-28). Muscle/experience cells are untouched. CHANGE LOG — 2026-09-01 identity merge: Single-Arm Pulldown retired as a current row and retained only as a legacy read alias; cues, equipment, progression and history resolve to Single-Arm Lat Pulldown. CHANGE LOG — 2026-09-01: Seated Good Morning (Barbell) retired as a current row and retained only as legacy saved-data ingress. Seated Good Morning is the one identity; bodyweight is available to everyone, while dumbbell and barbell variants require 1+ years.; Sam 2026-09-02: SL 45° Back Extension Hold and Swiss Ball Hamstring Curl moved from Hamstring (light) into Lower prehab; the separate authored pool was retired. CHANGE LOG — Sam 2026-09-04 (R-368): B-Stance RDL ADDED to Lower hinge — "add this into the exercise list as well - so we have another single leg hip dominant lift". Third member of the single-leg hip group, which held only Single-Leg RDL and SL 45° Back Extension. Intake: docs/EXERCISE_INTAKE_B_STANCE_RDL_2026-09-04.md. CHANGE LOG - Sam 2026-09-04 (R-372): Barbell Row RENAMED to Bent Row and widened to barbell OR dumbbells - "you should be able to do bent DB rows with 2 hands ... so it is just bent row and can use bb or db". Cues rewritten to say two hands and name no implement. Barbell Row is retained as a legacy read alias so logged history follows.</t>
         </is>
       </c>
       <c r="K5" s="5" t="n"/>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>Barbell Row</t>
+          <t>Bent Row</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -2292,12 +2292,12 @@
       <c r="F44" s="1" t="str"/>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>Hinge forward, pull to the belly.</t>
+          <t>Hinge forward, flat back, pull the bar or dumbbells to your belly.</t>
         </is>
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>Squeeze the shoulder blades at the top.</t>
+          <t>Both hands together. Squeeze the shoulder blades at the top.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
